--- a/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
+++ b/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
@@ -30,7 +30,153 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="V1" authorId="0">
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מזהה כללי, מתאים לכל כלי ניטור שיוחלט עליו </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">למשל שם </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">environment </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">או מזהה של דופק</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">). </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">עוד לא הוחלט על הכלי</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>70</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>11</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מחיר בפועל פחות עלות חומרה ופחות עלות חשמלאי. לא כולל שכר עצמי ועלויות כלים חודשיות </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(R2, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ניטור</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">).</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>70</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="AA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +208,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">2–6 (5 הלקוחות הראשונים).</t>
+          <t xml:space="preserve">2–6.</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -78,8 +224,148 @@
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">סכום כל השעות של הלקוח בלשונית שעות, חוץ מהשלב "תמיכה (ריטיינר)" (זה נספר בעמודה נפרדת)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>70</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">סוף יום העסקים ה</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">-N </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">אחרי הפתיחה (ימי עסקים א׳–ה׳, בלי חגים): קריטי = יום </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1, אזהרה = 3 ימים. "בקשה" ללא SLA. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">לפי </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">PRD 1, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">סעיף </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">E.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>55</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-178</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>10</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -92,7 +378,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="155">
   <si>
     <t xml:space="preserve">OneHome — גיליון מעקב לקוחות (קובץ דוגמה)</t>
   </si>
@@ -109,19 +395,19 @@
     <t xml:space="preserve">הלשוניות</t>
   </si>
   <si>
-    <t xml:space="preserve">לקוחות — שורה לכל לקוח. נוסחאות מוכנות עד שורה 21. שדות ה-IP, MAC, גרסת HA, R2 ו-Sentry הם אלה ש-PRD 4 (כלי ניהול פנימי) יצטרך, כך שבהמשך אפשר לייבא אותם.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checklist — עמודה לכל לקוח, נמשכת אוטומטית מלשונית לקוחות (5 הלקוחות הראשונים). מבוסס על PRD 3, סעיפים B ו-D. "לא רלוונטי" לא נספר באחוז ההתקדמות.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שעות — שורה לכל שלב עבודה. זה המדד "שעות בפועל לכל שלב" מ-PRD 3, והבסיס לחישוב הכנסה לשעה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פניות — יומן פניות אחרי המסירה. רמות החומרה כאן (קריטית/רגילה) הן הצעה — להתאים לרמות ה-SLA המדויקות ב-PRD 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חבילות — מחירי ההתקנה והריטיינר (מקור: PRD 1, 16/09/2026) וסיכום קצר: לקוחות פעילים, הכנסה חודשית וסה"כ פניות פתוחות.</t>
+    <t xml:space="preserve">לקוחות — שורה לכל לקוח. נוסחאות מוכנות עד שורה 21. כולל מחיר בפועל, עלות חומרה וחשמלאי, רווח לשעה, שעות תמיכה ומזהה ניטור. שדות ה-IP, MAC, R2 ומזהה הניטור הם אלה ש-PRD 4 (כלי ניהול פנימי) יצטרך, כך שבהמשך אפשר לייבא אותם.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist — עמודה לכל לקוח, נמשכת אוטומטית מלשונית לקוחות (5 הלקוחות הראשונים). מבוסס על PRD 3, סעיפים B ו-D. "לא רלוונטי" לא נספר באחוז ההתקנה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שעות — שורה לכל שלב עבודה, כולל "נסיעות". השלב "תמיכה (ריטיינר)" נספר בנפרד, כדי לראות כמה תמיכה כל לקוח באמת צורך מול הריטיינר שלו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פניות — יומן פניות אחרי המסירה. חומרה לפי PRD 1: קריטי (תגובה עד יום עסקים), אזהרה (עד 3 ימי עסקים), בקשה (ללא SLA). "מידע" לא נרשם, כי גיא לא מעורב.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חבילות — מחירי ההתקנה והריטיינר (מקור: PRD 1, 16/09/2026) וסיכום: לקוחות פעילים, הכנסה חודשית, פניות פתוחות, אירועים קריטיים מעבר ל-SLA ושעות עבודה.</t>
   </si>
   <si>
     <t xml:space="preserve">כללים חשובים</t>
@@ -133,12 +419,18 @@
     <t xml:space="preserve">2. לא לשמור את הקובץ האמיתי ב-repo של smart-home או ב-plan-site (האתר ב-GitHub Pages עלול להיות נגיש ברשת) ולא בחשבון OneDrive של המעסיק.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. "הכנסת התקנה לשעה" היא מחיר ההתקנה חלקי שעות העבודה, לפני עלות החומרה והחשמלאי — זה לא רווח.</t>
+    <t xml:space="preserve">3. "רווח התקנה" = מחיר בפועל − עלות חומרה − עלות חשמלאי. "רווח לשעה" = רווח התקנה ÷ שעות התקנה (כולל נסיעות). שניהם לפני שכר עצמי ולפני עלויות כלים חודשיות (R2, ניטור).</t>
   </si>
   <si>
     <t xml:space="preserve">4. תחילת ריטיינר = תאריך אישור קבלה חתום (החלטה ב-PRD 3, סעיף B).</t>
   </si>
   <si>
+    <t xml:space="preserve">5. "מזהה ניטור" הוא עמודה כללית — עוד לא הוחלט איזה כלי ניטור ישמש (Sentry, דופק או אחר).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. בדיקת ה-SLA מניחה ימי עסקים א׳–ה׳ בלי חגים, והיעד הוא סוף יום העסקים ה-N אחרי פתיחת הפנייה. אם שישי נחשב יום עסקים, לתקן את הנוסחה בעמודה "יעד SLA".</t>
+  </si>
+  <si>
     <t xml:space="preserve">מזהה לקוח</t>
   </si>
   <si>
@@ -154,12 +446,18 @@
     <t xml:space="preserve">חבילה</t>
   </si>
   <si>
-    <t xml:space="preserve">מחיר התקנה</t>
+    <t xml:space="preserve">מחיר חבילה</t>
   </si>
   <si>
     <t xml:space="preserve">ריטיינר חודשי</t>
   </si>
   <si>
+    <t xml:space="preserve">תוספות / הנחה (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחיר בפועל</t>
+  </si>
+  <si>
     <t xml:space="preserve">תאריך סקר בית</t>
   </si>
   <si>
@@ -193,7 +491,7 @@
     <t xml:space="preserve">שם bucket ב-R2</t>
   </si>
   <si>
-    <t xml:space="preserve">environment ב-Sentry</t>
+    <t xml:space="preserve">מזהה ניטור</t>
   </si>
   <si>
     <t xml:space="preserve">עבודת חשמל</t>
@@ -202,13 +500,25 @@
     <t xml:space="preserve">חשמלאי</t>
   </si>
   <si>
+    <t xml:space="preserve">עלות חומרה (כולל מע"מ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עלות חשמלאי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רווח התקנה (לפני שכר עצמי)</t>
+  </si>
+  <si>
     <t xml:space="preserve">התקדמות checklist</t>
   </si>
   <si>
-    <t xml:space="preserve">סה"כ שעות התקנה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הכנסת התקנה לשעה (לפני חומרה)</t>
+    <t xml:space="preserve">שעות התקנה (כולל נסיעות)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רווח התקנה לשעה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שעות תמיכה (ריטיינר)</t>
   </si>
   <si>
     <t xml:space="preserve">פניות פתוחות</t>
@@ -397,7 +707,7 @@
     <t xml:space="preserve">הערה</t>
   </si>
   <si>
-    <t xml:space="preserve">שורה לכל שלב עבודה. הסכום לכל לקוח מוצג בלשונית לקוחות.</t>
+    <t xml:space="preserve">שורה לכל שלב עבודה. הסכום לכל לקוח מוצג בלשונית לקוחות. השלב "תמיכה (ריטיינר)" נספר בנפרד משעות ההתקנה.</t>
   </si>
   <si>
     <t xml:space="preserve">פגישת מכירה</t>
@@ -406,6 +716,9 @@
     <t xml:space="preserve">פגישה ראשונה בבית הלקוח</t>
   </si>
   <si>
+    <t xml:space="preserve">נסיעות</t>
+  </si>
+  <si>
     <t xml:space="preserve">סקר בית</t>
   </si>
   <si>
@@ -430,6 +743,15 @@
     <t xml:space="preserve">מסירה והדרכה</t>
   </si>
   <si>
+    <t xml:space="preserve">תמיכה (ריטיינר)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פנייה P001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פנייה P002</t>
+  </si>
+  <si>
     <t xml:space="preserve">מזהה פנייה</t>
   </si>
   <si>
@@ -442,19 +764,28 @@
     <t xml:space="preserve">חומרה</t>
   </si>
   <si>
+    <t xml:space="preserve">תגובה ראשונה</t>
+  </si>
+  <si>
     <t xml:space="preserve">תאריך פתרון</t>
   </si>
   <si>
     <t xml:space="preserve">זמן פתרון (שעות)</t>
   </si>
   <si>
+    <t xml:space="preserve">יעד SLA לתגובה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עמד ב-SLA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">P001</t>
   </si>
   <si>
     <t xml:space="preserve">התראת הצפה לא הגיעה לטלפון של בת הזוג</t>
   </si>
   <si>
-    <t xml:space="preserve">קריטית</t>
+    <t xml:space="preserve">קריטי</t>
   </si>
   <si>
     <t xml:space="preserve">סגורה</t>
@@ -469,7 +800,7 @@
     <t xml:space="preserve">שאלה על הוספת מנורה לדשבורד</t>
   </si>
   <si>
-    <t xml:space="preserve">רגילה</t>
+    <t xml:space="preserve">בקשה</t>
   </si>
   <si>
     <t xml:space="preserve">פתוחה</t>
@@ -505,22 +836,29 @@
     <t xml:space="preserve">סה"כ פניות פתוחות</t>
   </si>
   <si>
-    <t xml:space="preserve">סה"כ שעות התקנה שנרשמו</t>
+    <t xml:space="preserve">אירועים קריטיים מעבר ל-SLA (יעד: 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ שעות התקנה (ללא תמיכה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ שעות תמיכה</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₪&quot;"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy\ hh:mm"/>
-    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot; ₪&quot;;[RED]\-#,##0&quot; ₪&quot;"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="General"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="172" formatCode="0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -682,7 +1020,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -711,6 +1049,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -728,6 +1070,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -751,7 +1097,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -759,11 +1105,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -783,7 +1137,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -791,7 +1145,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1070,7 +1424,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1117,17 +1471,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1150,7 +1504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -1158,6 +1512,16 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1176,129 +1540,152 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F2" s="6" t="n">
         <f aca="false">IF($E2="","",IFERROR(INDEX(חבילות!$B$2:$B$4,MATCH($E2,חבילות!$A$2:$A$4,0)),""))</f>
@@ -1309,69 +1696,90 @@
         <v>220</v>
       </c>
       <c r="H2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <f aca="false">IF(OR($A2="",$F2=""),"",$F2+N($H2))</f>
+        <v>8700</v>
+      </c>
+      <c r="J2" s="8" t="n">
         <v>46300</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="K2" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="L2" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <f aca="false">IF($J2="","",$J2)</f>
+      <c r="M2" s="9" t="n">
+        <f aca="false">IF($L2="","",$L2)</f>
         <v>46314</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="N2" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="Y2" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="Z2" s="10" t="n">
+        <f aca="false">IF(OR($A2="",$I2="",$X2=""),"",$I2-$X2-N($Y2))</f>
+        <v>3700</v>
+      </c>
+      <c r="AA2" s="11" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A2,Checklist!$C$1:$G$1,0)),""))</f>
         <v>1</v>
       </c>
-      <c r="W2" s="10" t="n">
-        <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2))</f>
-        <v>15.5</v>
-      </c>
-      <c r="X2" s="6" t="n">
-        <f aca="false">IF($A2="","",IFERROR($F2/$W2,""))</f>
-        <v>561.290322580645</v>
-      </c>
-      <c r="Y2" s="11" t="n">
+      <c r="AB2" s="12" t="n">
+        <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v>18.5</v>
+      </c>
+      <c r="AC2" s="10" t="n">
+        <f aca="false">IF($A2="","",IFERROR($Z2/$AB2,""))</f>
+        <v>200</v>
+      </c>
+      <c r="AD2" s="12" t="n">
+        <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v>1.5</v>
+      </c>
+      <c r="AE2" s="13" t="n">
         <f aca="false">IF($A2="","",COUNTIFS(פניות!$B$2:$B$500,$A2,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v>1</v>
       </c>
-      <c r="Z2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>58</v>
+      <c r="AF2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1389,14 +1797,17 @@
         <v/>
       </c>
       <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8" t="str">
-        <f aca="false">IF($J3="","",$J3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="I3" s="6" t="str">
+        <f aca="false">IF(OR($A3="",$F3=""),"",$F3+N($H3))</f>
+        <v/>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="9" t="str">
+        <f aca="false">IF($L3="","",$L3)</f>
+        <v/>
+      </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -1405,24 +1816,36 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="9" t="str">
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="10" t="str">
+        <f aca="false">IF(OR($A3="",$I3="",$X3=""),"",$I3-$X3-N($Y3))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="11" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A3,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W3" s="10" t="str">
-        <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3))</f>
-        <v/>
-      </c>
-      <c r="X3" s="6" t="str">
-        <f aca="false">IF($A3="","",IFERROR($F3/$W3,""))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="11" t="str">
+      <c r="AB3" s="12" t="str">
+        <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="10" t="str">
+        <f aca="false">IF($A3="","",IFERROR($Z3/$AB3,""))</f>
+        <v/>
+      </c>
+      <c r="AD3" s="12" t="str">
+        <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="13" t="str">
         <f aca="false">IF($A3="","",COUNTIFS(פניות!$B$2:$B$500,$A3,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
@@ -1439,14 +1862,17 @@
         <v/>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="str">
-        <f aca="false">IF($J4="","",$J4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="I4" s="6" t="str">
+        <f aca="false">IF(OR($A4="",$F4=""),"",$F4+N($H4))</f>
+        <v/>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9" t="str">
+        <f aca="false">IF($L4="","",$L4)</f>
+        <v/>
+      </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -1455,24 +1881,36 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="9" t="str">
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="10" t="str">
+        <f aca="false">IF(OR($A4="",$I4="",$X4=""),"",$I4-$X4-N($Y4))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="11" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A4,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W4" s="10" t="str">
-        <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4))</f>
-        <v/>
-      </c>
-      <c r="X4" s="6" t="str">
-        <f aca="false">IF($A4="","",IFERROR($F4/$W4,""))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="11" t="str">
+      <c r="AB4" s="12" t="str">
+        <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="10" t="str">
+        <f aca="false">IF($A4="","",IFERROR($Z4/$AB4,""))</f>
+        <v/>
+      </c>
+      <c r="AD4" s="12" t="str">
+        <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="13" t="str">
         <f aca="false">IF($A4="","",COUNTIFS(פניות!$B$2:$B$500,$A4,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -1489,14 +1927,17 @@
         <v/>
       </c>
       <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8" t="str">
-        <f aca="false">IF($J5="","",$J5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="I5" s="6" t="str">
+        <f aca="false">IF(OR($A5="",$F5=""),"",$F5+N($H5))</f>
+        <v/>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="9" t="str">
+        <f aca="false">IF($L5="","",$L5)</f>
+        <v/>
+      </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -1505,24 +1946,36 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
-      <c r="V5" s="9" t="str">
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="10" t="str">
+        <f aca="false">IF(OR($A5="",$I5="",$X5=""),"",$I5-$X5-N($Y5))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="11" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A5,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W5" s="10" t="str">
-        <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5))</f>
-        <v/>
-      </c>
-      <c r="X5" s="6" t="str">
-        <f aca="false">IF($A5="","",IFERROR($F5/$W5,""))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="11" t="str">
+      <c r="AB5" s="12" t="str">
+        <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="10" t="str">
+        <f aca="false">IF($A5="","",IFERROR($Z5/$AB5,""))</f>
+        <v/>
+      </c>
+      <c r="AD5" s="12" t="str">
+        <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="13" t="str">
         <f aca="false">IF($A5="","",COUNTIFS(פניות!$B$2:$B$500,$A5,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -1539,14 +1992,17 @@
         <v/>
       </c>
       <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8" t="str">
-        <f aca="false">IF($J6="","",$J6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="I6" s="6" t="str">
+        <f aca="false">IF(OR($A6="",$F6=""),"",$F6+N($H6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="9" t="str">
+        <f aca="false">IF($L6="","",$L6)</f>
+        <v/>
+      </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
@@ -1555,24 +2011,36 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="9" t="str">
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="10" t="str">
+        <f aca="false">IF(OR($A6="",$I6="",$X6=""),"",$I6-$X6-N($Y6))</f>
+        <v/>
+      </c>
+      <c r="AA6" s="11" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A6,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W6" s="10" t="str">
-        <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6))</f>
-        <v/>
-      </c>
-      <c r="X6" s="6" t="str">
-        <f aca="false">IF($A6="","",IFERROR($F6/$W6,""))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="11" t="str">
+      <c r="AB6" s="12" t="str">
+        <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC6" s="10" t="str">
+        <f aca="false">IF($A6="","",IFERROR($Z6/$AB6,""))</f>
+        <v/>
+      </c>
+      <c r="AD6" s="12" t="str">
+        <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="13" t="str">
         <f aca="false">IF($A6="","",COUNTIFS(פניות!$B$2:$B$500,$A6,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -1589,14 +2057,17 @@
         <v/>
       </c>
       <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8" t="str">
-        <f aca="false">IF($J7="","",$J7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="I7" s="6" t="str">
+        <f aca="false">IF(OR($A7="",$F7=""),"",$F7+N($H7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="9" t="str">
+        <f aca="false">IF($L7="","",$L7)</f>
+        <v/>
+      </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
@@ -1605,24 +2076,36 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
-      <c r="V7" s="9" t="str">
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="10" t="str">
+        <f aca="false">IF(OR($A7="",$I7="",$X7=""),"",$I7-$X7-N($Y7))</f>
+        <v/>
+      </c>
+      <c r="AA7" s="11" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A7,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W7" s="10" t="str">
-        <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7))</f>
-        <v/>
-      </c>
-      <c r="X7" s="6" t="str">
-        <f aca="false">IF($A7="","",IFERROR($F7/$W7,""))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="11" t="str">
+      <c r="AB7" s="12" t="str">
+        <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="10" t="str">
+        <f aca="false">IF($A7="","",IFERROR($Z7/$AB7,""))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="12" t="str">
+        <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="13" t="str">
         <f aca="false">IF($A7="","",COUNTIFS(פניות!$B$2:$B$500,$A7,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -1639,14 +2122,17 @@
         <v/>
       </c>
       <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8" t="str">
-        <f aca="false">IF($J8="","",$J8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="I8" s="6" t="str">
+        <f aca="false">IF(OR($A8="",$F8=""),"",$F8+N($H8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9" t="str">
+        <f aca="false">IF($L8="","",$L8)</f>
+        <v/>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -1655,24 +2141,36 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
-      <c r="V8" s="9" t="str">
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="10" t="str">
+        <f aca="false">IF(OR($A8="",$I8="",$X8=""),"",$I8-$X8-N($Y8))</f>
+        <v/>
+      </c>
+      <c r="AA8" s="11" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A8,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W8" s="10" t="str">
-        <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8))</f>
-        <v/>
-      </c>
-      <c r="X8" s="6" t="str">
-        <f aca="false">IF($A8="","",IFERROR($F8/$W8,""))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="11" t="str">
+      <c r="AB8" s="12" t="str">
+        <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="10" t="str">
+        <f aca="false">IF($A8="","",IFERROR($Z8/$AB8,""))</f>
+        <v/>
+      </c>
+      <c r="AD8" s="12" t="str">
+        <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="13" t="str">
         <f aca="false">IF($A8="","",COUNTIFS(פניות!$B$2:$B$500,$A8,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -1689,14 +2187,17 @@
         <v/>
       </c>
       <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8" t="str">
-        <f aca="false">IF($J9="","",$J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="I9" s="6" t="str">
+        <f aca="false">IF(OR($A9="",$F9=""),"",$F9+N($H9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="9" t="str">
+        <f aca="false">IF($L9="","",$L9)</f>
+        <v/>
+      </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -1705,24 +2206,36 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
-      <c r="V9" s="9" t="str">
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="10" t="str">
+        <f aca="false">IF(OR($A9="",$I9="",$X9=""),"",$I9-$X9-N($Y9))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="11" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A9,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W9" s="10" t="str">
-        <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9))</f>
-        <v/>
-      </c>
-      <c r="X9" s="6" t="str">
-        <f aca="false">IF($A9="","",IFERROR($F9/$W9,""))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="11" t="str">
+      <c r="AB9" s="12" t="str">
+        <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="10" t="str">
+        <f aca="false">IF($A9="","",IFERROR($Z9/$AB9,""))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="12" t="str">
+        <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="13" t="str">
         <f aca="false">IF($A9="","",COUNTIFS(פניות!$B$2:$B$500,$A9,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -1739,14 +2252,17 @@
         <v/>
       </c>
       <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8" t="str">
-        <f aca="false">IF($J10="","",$J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="I10" s="6" t="str">
+        <f aca="false">IF(OR($A10="",$F10=""),"",$F10+N($H10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="9" t="str">
+        <f aca="false">IF($L10="","",$L10)</f>
+        <v/>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -1755,24 +2271,36 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
-      <c r="V10" s="9" t="str">
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="10" t="str">
+        <f aca="false">IF(OR($A10="",$I10="",$X10=""),"",$I10-$X10-N($Y10))</f>
+        <v/>
+      </c>
+      <c r="AA10" s="11" t="str">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A10,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W10" s="10" t="str">
-        <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10))</f>
-        <v/>
-      </c>
-      <c r="X10" s="6" t="str">
-        <f aca="false">IF($A10="","",IFERROR($F10/$W10,""))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="11" t="str">
+      <c r="AB10" s="12" t="str">
+        <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="10" t="str">
+        <f aca="false">IF($A10="","",IFERROR($Z10/$AB10,""))</f>
+        <v/>
+      </c>
+      <c r="AD10" s="12" t="str">
+        <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="13" t="str">
         <f aca="false">IF($A10="","",COUNTIFS(פניות!$B$2:$B$500,$A10,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -1789,14 +2317,17 @@
         <v/>
       </c>
       <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8" t="str">
-        <f aca="false">IF($J11="","",$J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="I11" s="6" t="str">
+        <f aca="false">IF(OR($A11="",$F11=""),"",$F11+N($H11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="9" t="str">
+        <f aca="false">IF($L11="","",$L11)</f>
+        <v/>
+      </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -1805,24 +2336,36 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
-      <c r="V11" s="9" t="str">
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="10" t="str">
+        <f aca="false">IF(OR($A11="",$I11="",$X11=""),"",$I11-$X11-N($Y11))</f>
+        <v/>
+      </c>
+      <c r="AA11" s="11" t="str">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A11,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W11" s="10" t="str">
-        <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11))</f>
-        <v/>
-      </c>
-      <c r="X11" s="6" t="str">
-        <f aca="false">IF($A11="","",IFERROR($F11/$W11,""))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="11" t="str">
+      <c r="AB11" s="12" t="str">
+        <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="10" t="str">
+        <f aca="false">IF($A11="","",IFERROR($Z11/$AB11,""))</f>
+        <v/>
+      </c>
+      <c r="AD11" s="12" t="str">
+        <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="13" t="str">
         <f aca="false">IF($A11="","",COUNTIFS(פניות!$B$2:$B$500,$A11,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -1839,14 +2382,17 @@
         <v/>
       </c>
       <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8" t="str">
-        <f aca="false">IF($J12="","",$J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="I12" s="6" t="str">
+        <f aca="false">IF(OR($A12="",$F12=""),"",$F12+N($H12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9" t="str">
+        <f aca="false">IF($L12="","",$L12)</f>
+        <v/>
+      </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -1855,24 +2401,36 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
-      <c r="V12" s="9" t="str">
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="10" t="str">
+        <f aca="false">IF(OR($A12="",$I12="",$X12=""),"",$I12-$X12-N($Y12))</f>
+        <v/>
+      </c>
+      <c r="AA12" s="11" t="str">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A12,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W12" s="10" t="str">
-        <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12))</f>
-        <v/>
-      </c>
-      <c r="X12" s="6" t="str">
-        <f aca="false">IF($A12="","",IFERROR($F12/$W12,""))</f>
-        <v/>
-      </c>
-      <c r="Y12" s="11" t="str">
+      <c r="AB12" s="12" t="str">
+        <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC12" s="10" t="str">
+        <f aca="false">IF($A12="","",IFERROR($Z12/$AB12,""))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="12" t="str">
+        <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="13" t="str">
         <f aca="false">IF($A12="","",COUNTIFS(פניות!$B$2:$B$500,$A12,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -1889,14 +2447,17 @@
         <v/>
       </c>
       <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8" t="str">
-        <f aca="false">IF($J13="","",$J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="I13" s="6" t="str">
+        <f aca="false">IF(OR($A13="",$F13=""),"",$F13+N($H13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="9" t="str">
+        <f aca="false">IF($L13="","",$L13)</f>
+        <v/>
+      </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -1905,24 +2466,36 @@
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
-      <c r="V13" s="9" t="str">
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="10" t="str">
+        <f aca="false">IF(OR($A13="",$I13="",$X13=""),"",$I13-$X13-N($Y13))</f>
+        <v/>
+      </c>
+      <c r="AA13" s="11" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A13,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W13" s="10" t="str">
-        <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13))</f>
-        <v/>
-      </c>
-      <c r="X13" s="6" t="str">
-        <f aca="false">IF($A13="","",IFERROR($F13/$W13,""))</f>
-        <v/>
-      </c>
-      <c r="Y13" s="11" t="str">
+      <c r="AB13" s="12" t="str">
+        <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC13" s="10" t="str">
+        <f aca="false">IF($A13="","",IFERROR($Z13/$AB13,""))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="12" t="str">
+        <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="13" t="str">
         <f aca="false">IF($A13="","",COUNTIFS(פניות!$B$2:$B$500,$A13,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -1939,14 +2512,17 @@
         <v/>
       </c>
       <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8" t="str">
-        <f aca="false">IF($J14="","",$J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="I14" s="6" t="str">
+        <f aca="false">IF(OR($A14="",$F14=""),"",$F14+N($H14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="9" t="str">
+        <f aca="false">IF($L14="","",$L14)</f>
+        <v/>
+      </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -1955,24 +2531,36 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
-      <c r="V14" s="9" t="str">
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="10" t="str">
+        <f aca="false">IF(OR($A14="",$I14="",$X14=""),"",$I14-$X14-N($Y14))</f>
+        <v/>
+      </c>
+      <c r="AA14" s="11" t="str">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A14,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W14" s="10" t="str">
-        <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14))</f>
-        <v/>
-      </c>
-      <c r="X14" s="6" t="str">
-        <f aca="false">IF($A14="","",IFERROR($F14/$W14,""))</f>
-        <v/>
-      </c>
-      <c r="Y14" s="11" t="str">
+      <c r="AB14" s="12" t="str">
+        <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC14" s="10" t="str">
+        <f aca="false">IF($A14="","",IFERROR($Z14/$AB14,""))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="12" t="str">
+        <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="13" t="str">
         <f aca="false">IF($A14="","",COUNTIFS(פניות!$B$2:$B$500,$A14,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -1989,14 +2577,17 @@
         <v/>
       </c>
       <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="8" t="str">
-        <f aca="false">IF($J15="","",$J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="I15" s="6" t="str">
+        <f aca="false">IF(OR($A15="",$F15=""),"",$F15+N($H15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="9" t="str">
+        <f aca="false">IF($L15="","",$L15)</f>
+        <v/>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -2005,24 +2596,36 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
-      <c r="V15" s="9" t="str">
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="10" t="str">
+        <f aca="false">IF(OR($A15="",$I15="",$X15=""),"",$I15-$X15-N($Y15))</f>
+        <v/>
+      </c>
+      <c r="AA15" s="11" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A15,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W15" s="10" t="str">
-        <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15))</f>
-        <v/>
-      </c>
-      <c r="X15" s="6" t="str">
-        <f aca="false">IF($A15="","",IFERROR($F15/$W15,""))</f>
-        <v/>
-      </c>
-      <c r="Y15" s="11" t="str">
+      <c r="AB15" s="12" t="str">
+        <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC15" s="10" t="str">
+        <f aca="false">IF($A15="","",IFERROR($Z15/$AB15,""))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="12" t="str">
+        <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="13" t="str">
         <f aca="false">IF($A15="","",COUNTIFS(פניות!$B$2:$B$500,$A15,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -2039,14 +2642,17 @@
         <v/>
       </c>
       <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="8" t="str">
-        <f aca="false">IF($J16="","",$J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
+      <c r="I16" s="6" t="str">
+        <f aca="false">IF(OR($A16="",$F16=""),"",$F16+N($H16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="9" t="str">
+        <f aca="false">IF($L16="","",$L16)</f>
+        <v/>
+      </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -2055,24 +2661,36 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
-      <c r="V16" s="9" t="str">
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="10" t="str">
+        <f aca="false">IF(OR($A16="",$I16="",$X16=""),"",$I16-$X16-N($Y16))</f>
+        <v/>
+      </c>
+      <c r="AA16" s="11" t="str">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A16,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W16" s="10" t="str">
-        <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16))</f>
-        <v/>
-      </c>
-      <c r="X16" s="6" t="str">
-        <f aca="false">IF($A16="","",IFERROR($F16/$W16,""))</f>
-        <v/>
-      </c>
-      <c r="Y16" s="11" t="str">
+      <c r="AB16" s="12" t="str">
+        <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC16" s="10" t="str">
+        <f aca="false">IF($A16="","",IFERROR($Z16/$AB16,""))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="12" t="str">
+        <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="13" t="str">
         <f aca="false">IF($A16="","",COUNTIFS(פניות!$B$2:$B$500,$A16,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z16" s="5"/>
-      <c r="AA16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -2089,14 +2707,17 @@
         <v/>
       </c>
       <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8" t="str">
-        <f aca="false">IF($J17="","",$J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="I17" s="6" t="str">
+        <f aca="false">IF(OR($A17="",$F17=""),"",$F17+N($H17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="9" t="str">
+        <f aca="false">IF($L17="","",$L17)</f>
+        <v/>
+      </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
@@ -2105,24 +2726,36 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
-      <c r="V17" s="9" t="str">
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="10" t="str">
+        <f aca="false">IF(OR($A17="",$I17="",$X17=""),"",$I17-$X17-N($Y17))</f>
+        <v/>
+      </c>
+      <c r="AA17" s="11" t="str">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A17,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W17" s="10" t="str">
-        <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17))</f>
-        <v/>
-      </c>
-      <c r="X17" s="6" t="str">
-        <f aca="false">IF($A17="","",IFERROR($F17/$W17,""))</f>
-        <v/>
-      </c>
-      <c r="Y17" s="11" t="str">
+      <c r="AB17" s="12" t="str">
+        <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC17" s="10" t="str">
+        <f aca="false">IF($A17="","",IFERROR($Z17/$AB17,""))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="12" t="str">
+        <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="13" t="str">
         <f aca="false">IF($A17="","",COUNTIFS(פניות!$B$2:$B$500,$A17,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -2139,14 +2772,17 @@
         <v/>
       </c>
       <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="8" t="str">
-        <f aca="false">IF($J18="","",$J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="I18" s="6" t="str">
+        <f aca="false">IF(OR($A18="",$F18=""),"",$F18+N($H18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="9" t="str">
+        <f aca="false">IF($L18="","",$L18)</f>
+        <v/>
+      </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -2155,24 +2791,36 @@
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
-      <c r="V18" s="9" t="str">
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="10" t="str">
+        <f aca="false">IF(OR($A18="",$I18="",$X18=""),"",$I18-$X18-N($Y18))</f>
+        <v/>
+      </c>
+      <c r="AA18" s="11" t="str">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A18,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W18" s="10" t="str">
-        <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18))</f>
-        <v/>
-      </c>
-      <c r="X18" s="6" t="str">
-        <f aca="false">IF($A18="","",IFERROR($F18/$W18,""))</f>
-        <v/>
-      </c>
-      <c r="Y18" s="11" t="str">
+      <c r="AB18" s="12" t="str">
+        <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC18" s="10" t="str">
+        <f aca="false">IF($A18="","",IFERROR($Z18/$AB18,""))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="12" t="str">
+        <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="13" t="str">
         <f aca="false">IF($A18="","",COUNTIFS(פניות!$B$2:$B$500,$A18,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -2189,14 +2837,17 @@
         <v/>
       </c>
       <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8" t="str">
-        <f aca="false">IF($J19="","",$J19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="I19" s="6" t="str">
+        <f aca="false">IF(OR($A19="",$F19=""),"",$F19+N($H19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="9" t="str">
+        <f aca="false">IF($L19="","",$L19)</f>
+        <v/>
+      </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -2205,24 +2856,36 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
-      <c r="V19" s="9" t="str">
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="10" t="str">
+        <f aca="false">IF(OR($A19="",$I19="",$X19=""),"",$I19-$X19-N($Y19))</f>
+        <v/>
+      </c>
+      <c r="AA19" s="11" t="str">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A19,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W19" s="10" t="str">
-        <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19))</f>
-        <v/>
-      </c>
-      <c r="X19" s="6" t="str">
-        <f aca="false">IF($A19="","",IFERROR($F19/$W19,""))</f>
-        <v/>
-      </c>
-      <c r="Y19" s="11" t="str">
+      <c r="AB19" s="12" t="str">
+        <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC19" s="10" t="str">
+        <f aca="false">IF($A19="","",IFERROR($Z19/$AB19,""))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="12" t="str">
+        <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="13" t="str">
         <f aca="false">IF($A19="","",COUNTIFS(פניות!$B$2:$B$500,$A19,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -2239,14 +2902,17 @@
         <v/>
       </c>
       <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="8" t="str">
-        <f aca="false">IF($J20="","",$J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="I20" s="6" t="str">
+        <f aca="false">IF(OR($A20="",$F20=""),"",$F20+N($H20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="9" t="str">
+        <f aca="false">IF($L20="","",$L20)</f>
+        <v/>
+      </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -2255,24 +2921,36 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
-      <c r="V20" s="9" t="str">
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="10" t="str">
+        <f aca="false">IF(OR($A20="",$I20="",$X20=""),"",$I20-$X20-N($Y20))</f>
+        <v/>
+      </c>
+      <c r="AA20" s="11" t="str">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A20,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W20" s="10" t="str">
-        <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20))</f>
-        <v/>
-      </c>
-      <c r="X20" s="6" t="str">
-        <f aca="false">IF($A20="","",IFERROR($F20/$W20,""))</f>
-        <v/>
-      </c>
-      <c r="Y20" s="11" t="str">
+      <c r="AB20" s="12" t="str">
+        <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC20" s="10" t="str">
+        <f aca="false">IF($A20="","",IFERROR($Z20/$AB20,""))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="12" t="str">
+        <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="13" t="str">
         <f aca="false">IF($A20="","",COUNTIFS(פניות!$B$2:$B$500,$A20,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -2289,14 +2967,17 @@
         <v/>
       </c>
       <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8" t="str">
-        <f aca="false">IF($J21="","",$J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="I21" s="6" t="str">
+        <f aca="false">IF(OR($A21="",$F21=""),"",$F21+N($H21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="9" t="str">
+        <f aca="false">IF($L21="","",$L21)</f>
+        <v/>
+      </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
@@ -2305,24 +2986,36 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
-      <c r="V21" s="9" t="str">
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="10" t="str">
+        <f aca="false">IF(OR($A21="",$I21="",$X21=""),"",$I21-$X21-N($Y21))</f>
+        <v/>
+      </c>
+      <c r="AA21" s="11" t="str">
         <f aca="false">IF($A21="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A21,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="W21" s="10" t="str">
-        <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21))</f>
-        <v/>
-      </c>
-      <c r="X21" s="6" t="str">
-        <f aca="false">IF($A21="","",IFERROR($F21/$W21,""))</f>
-        <v/>
-      </c>
-      <c r="Y21" s="11" t="str">
+      <c r="AB21" s="12" t="str">
+        <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AC21" s="10" t="str">
+        <f aca="false">IF($A21="","",IFERROR($Z21/$AB21,""))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="12" t="str">
+        <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="13" t="str">
         <f aca="false">IF($A21="","",COUNTIFS(פניות!$B$2:$B$500,$A21,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2330,15 +3023,15 @@
       <formula1>חבילות!$A$2:$A$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N21" type="list">
       <formula1>"ליד,סקר בית,הצעה נשלחה,הזמנת ציוד,התקנה,בדיקות קבלה,פעיל,מושהה,הופסק"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="T2:T21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="V2:V21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2367,12 +3060,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C1" s="4" t="str">
         <f aca="false">IF(לקוחות!$A2="","",לקוחות!$A2)</f>
@@ -2396,447 +3089,447 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="A3" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="A4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="A5" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="A6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="A7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="A25" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+      <c r="B25" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
+      <c r="A26" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
+      <c r="A27" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="A28" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
+      <c r="A29" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="17" t="n">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="19" t="n">
         <f aca="false">IF(C$1="","",COUNTIF(C2:C29,"✓")/MAX(1,ROWS(C2:C29)-COUNTIF(C2:C29,"לא רלוונטי")))</f>
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="str">
+      <c r="D30" s="19" t="str">
         <f aca="false">IF(D$1="","",COUNTIF(D2:D29,"✓")/MAX(1,ROWS(D2:D29)-COUNTIF(D2:D29,"לא רלוונטי")))</f>
         <v/>
       </c>
-      <c r="E30" s="17" t="str">
+      <c r="E30" s="19" t="str">
         <f aca="false">IF(E$1="","",COUNTIF(E2:E29,"✓")/MAX(1,ROWS(E2:E29)-COUNTIF(E2:E29,"לא רלוונטי")))</f>
         <v/>
       </c>
-      <c r="F30" s="17" t="str">
+      <c r="F30" s="19" t="str">
         <f aca="false">IF(F$1="","",COUNTIF(F2:F29,"✓")/MAX(1,ROWS(F2:F29)-COUNTIF(F2:F29,"לא רלוונטי")))</f>
         <v/>
       </c>
-      <c r="G30" s="17" t="str">
+      <c r="G30" s="19" t="str">
         <f aca="false">IF(G$1="","",COUNTIF(G2:G29,"✓")/MAX(1,ROWS(G2:G29)-COUNTIF(G2:G29,"לא רלוונטי")))</f>
         <v/>
       </c>
@@ -2881,795 +3574,839 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>101</v>
+        <v>108</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="21" t="n">
         <v>1.5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>46300</v>
-      </c>
-      <c r="D3" s="19" t="n">
-        <v>2</v>
+        <v>112</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>46303</v>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>106</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>108</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>46314</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>46314</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>5</v>
+      </c>
       <c r="E9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="19"/>
+      <c r="A10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="19"/>
+      <c r="A11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>1</v>
+      </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="5"/>
+      <c r="A12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="5"/>
+      <c r="A13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>46328</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="19"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="19"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="19"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="19"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="19"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="19"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="19"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="19"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="19"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="19"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="19"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="19"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="19"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="19"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="19"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="19"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="19"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="19"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="19"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="19"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="19"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="19"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="19"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="19"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="19"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="19"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="19"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="19"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="19"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="19"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="19"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="19"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="19"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="19"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="19"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="19"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="19"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="19"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="19"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="19"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="19"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="19"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="19"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="19"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="19"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="19"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="19"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="19"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="21"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="19"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="21"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="19"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="19"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="19"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="19"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="19"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="19"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="19"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="19"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="19"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="19"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="19"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="19"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="19"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="19"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="21"/>
       <c r="E76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="19"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="21"/>
       <c r="E77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="19"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="21"/>
       <c r="E78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="19"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="19"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="21"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="19"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="21"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="19"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="21"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="19"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="21"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="19"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="21"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="19"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="21"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="19"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="21"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="19"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="21"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="19"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="19"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="21"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="19"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="21"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="19"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="21"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="19"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="21"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="19"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="21"/>
       <c r="E93" s="5"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="19"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="21"/>
       <c r="E94" s="5"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="19"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="21"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="19"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="21"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="19"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="21"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="19"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="21"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="19"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="21"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="19"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="21"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="19"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="21"/>
       <c r="E101" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B101" type="list">
-      <formula1>"פגישת מכירה,סקר בית,הצעה וחתימה,הכנה אצל גיא,עבודת חשמל (ליווי),התקנה ורשת,בדיקות קבלה,מסירה והדרכה,מעקב אחרי מסירה"</formula1>
+      <formula1>"פגישת מכירה,סקר בית,הצעה וחתימה,הכנה אצל גיא,עבודת חשמל (ליווי),נסיעות,התקנה ורשת,בדיקות קבלה,מסירה והדרכה,תמיכה (ריטיינר)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3688,1481 +4425,2402 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>41</v>
+        <v>130</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" s="22" t="n">
         <v>46316.3819444445</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G2" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="G2" s="22" t="n">
+        <v>46316.4027777778</v>
+      </c>
+      <c r="H2" s="22" t="n">
         <v>46316.4861111111</v>
       </c>
-      <c r="H2" s="10" t="n">
-        <f aca="false">IF(OR($C2="",$G2=""),"",ROUND(($G2-$C2)*24,1))</f>
+      <c r="I2" s="12" t="n">
+        <f aca="false">IF(OR($C2="",$H2=""),"",ROUND(($H2-$C2)*24,1))</f>
         <v>2.5</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>122</v>
+      <c r="J2" s="23" t="n">
+        <f aca="false">IF(OR($C2="",$E2="",$E2="בקשה"),"",WORKDAY.INTL(INT($C2),IF($E2="קריטי",1,3),7)+1-1/1440)</f>
+        <v>46317.9993055556</v>
+      </c>
+      <c r="K2" s="24" t="str">
+        <f aca="false">IF($J2="","",IF($G2="","טרם נענה",IF($G2&lt;=$J2,"✓","✗")))</f>
+        <v>✓</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" s="22" t="n">
         <v>46328.75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="10" t="str">
-        <f aca="false">IF(OR($C3="",$G3=""),"",ROUND(($G3-$C3)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>127</v>
+        <v>141</v>
+      </c>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="12" t="str">
+        <f aca="false">IF(OR($C3="",$H3=""),"",ROUND(($H3-$C3)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J3" s="23" t="str">
+        <f aca="false">IF(OR($C3="",$E3="",$E3="בקשה"),"",WORKDAY.INTL(INT($C3),IF($E3="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K3" s="24" t="str">
+        <f aca="false">IF($J3="","",IF($G3="","טרם נענה",IF($G3&lt;=$J3,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="20"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="10" t="str">
-        <f aca="false">IF(OR($C4="",$G4=""),"",ROUND(($G4-$C4)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I4" s="5"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="12" t="str">
+        <f aca="false">IF(OR($C4="",$H4=""),"",ROUND(($H4-$C4)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J4" s="23" t="str">
+        <f aca="false">IF(OR($C4="",$E4="",$E4="בקשה"),"",WORKDAY.INTL(INT($C4),IF($E4="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K4" s="24" t="str">
+        <f aca="false">IF($J4="","",IF($G4="","טרם נענה",IF($G4&lt;=$J4,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="20"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="10" t="str">
-        <f aca="false">IF(OR($C5="",$G5=""),"",ROUND(($G5-$C5)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I5" s="5"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="12" t="str">
+        <f aca="false">IF(OR($C5="",$H5=""),"",ROUND(($H5-$C5)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J5" s="23" t="str">
+        <f aca="false">IF(OR($C5="",$E5="",$E5="בקשה"),"",WORKDAY.INTL(INT($C5),IF($E5="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K5" s="24" t="str">
+        <f aca="false">IF($J5="","",IF($G5="","טרם נענה",IF($G5&lt;=$J5,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="20"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="10" t="str">
-        <f aca="false">IF(OR($C6="",$G6=""),"",ROUND(($G6-$C6)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I6" s="5"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="12" t="str">
+        <f aca="false">IF(OR($C6="",$H6=""),"",ROUND(($H6-$C6)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J6" s="23" t="str">
+        <f aca="false">IF(OR($C6="",$E6="",$E6="בקשה"),"",WORKDAY.INTL(INT($C6),IF($E6="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K6" s="24" t="str">
+        <f aca="false">IF($J6="","",IF($G6="","טרם נענה",IF($G6&lt;=$J6,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="10" t="str">
-        <f aca="false">IF(OR($C7="",$G7=""),"",ROUND(($G7-$C7)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I7" s="5"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="12" t="str">
+        <f aca="false">IF(OR($C7="",$H7=""),"",ROUND(($H7-$C7)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J7" s="23" t="str">
+        <f aca="false">IF(OR($C7="",$E7="",$E7="בקשה"),"",WORKDAY.INTL(INT($C7),IF($E7="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K7" s="24" t="str">
+        <f aca="false">IF($J7="","",IF($G7="","טרם נענה",IF($G7&lt;=$J7,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="10" t="str">
-        <f aca="false">IF(OR($C8="",$G8=""),"",ROUND(($G8-$C8)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I8" s="5"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="12" t="str">
+        <f aca="false">IF(OR($C8="",$H8=""),"",ROUND(($H8-$C8)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J8" s="23" t="str">
+        <f aca="false">IF(OR($C8="",$E8="",$E8="בקשה"),"",WORKDAY.INTL(INT($C8),IF($E8="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K8" s="24" t="str">
+        <f aca="false">IF($J8="","",IF($G8="","טרם נענה",IF($G8&lt;=$J8,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="20"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="10" t="str">
-        <f aca="false">IF(OR($C9="",$G9=""),"",ROUND(($G9-$C9)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I9" s="5"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="12" t="str">
+        <f aca="false">IF(OR($C9="",$H9=""),"",ROUND(($H9-$C9)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J9" s="23" t="str">
+        <f aca="false">IF(OR($C9="",$E9="",$E9="בקשה"),"",WORKDAY.INTL(INT($C9),IF($E9="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K9" s="24" t="str">
+        <f aca="false">IF($J9="","",IF($G9="","טרם נענה",IF($G9&lt;=$J9,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
-      <c r="C10" s="20"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="10" t="str">
-        <f aca="false">IF(OR($C10="",$G10=""),"",ROUND(($G10-$C10)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I10" s="5"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="12" t="str">
+        <f aca="false">IF(OR($C10="",$H10=""),"",ROUND(($H10-$C10)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J10" s="23" t="str">
+        <f aca="false">IF(OR($C10="",$E10="",$E10="בקשה"),"",WORKDAY.INTL(INT($C10),IF($E10="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K10" s="24" t="str">
+        <f aca="false">IF($J10="","",IF($G10="","טרם נענה",IF($G10&lt;=$J10,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="10" t="str">
-        <f aca="false">IF(OR($C11="",$G11=""),"",ROUND(($G11-$C11)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I11" s="5"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="12" t="str">
+        <f aca="false">IF(OR($C11="",$H11=""),"",ROUND(($H11-$C11)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J11" s="23" t="str">
+        <f aca="false">IF(OR($C11="",$E11="",$E11="בקשה"),"",WORKDAY.INTL(INT($C11),IF($E11="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K11" s="24" t="str">
+        <f aca="false">IF($J11="","",IF($G11="","טרם נענה",IF($G11&lt;=$J11,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="20"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="10" t="str">
-        <f aca="false">IF(OR($C12="",$G12=""),"",ROUND(($G12-$C12)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I12" s="5"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="12" t="str">
+        <f aca="false">IF(OR($C12="",$H12=""),"",ROUND(($H12-$C12)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J12" s="23" t="str">
+        <f aca="false">IF(OR($C12="",$E12="",$E12="בקשה"),"",WORKDAY.INTL(INT($C12),IF($E12="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K12" s="24" t="str">
+        <f aca="false">IF($J12="","",IF($G12="","טרם נענה",IF($G12&lt;=$J12,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="20"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="10" t="str">
-        <f aca="false">IF(OR($C13="",$G13=""),"",ROUND(($G13-$C13)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I13" s="5"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="12" t="str">
+        <f aca="false">IF(OR($C13="",$H13=""),"",ROUND(($H13-$C13)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J13" s="23" t="str">
+        <f aca="false">IF(OR($C13="",$E13="",$E13="בקשה"),"",WORKDAY.INTL(INT($C13),IF($E13="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K13" s="24" t="str">
+        <f aca="false">IF($J13="","",IF($G13="","טרם נענה",IF($G13&lt;=$J13,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="20"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="10" t="str">
-        <f aca="false">IF(OR($C14="",$G14=""),"",ROUND(($G14-$C14)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I14" s="5"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="12" t="str">
+        <f aca="false">IF(OR($C14="",$H14=""),"",ROUND(($H14-$C14)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J14" s="23" t="str">
+        <f aca="false">IF(OR($C14="",$E14="",$E14="בקשה"),"",WORKDAY.INTL(INT($C14),IF($E14="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K14" s="24" t="str">
+        <f aca="false">IF($J14="","",IF($G14="","טרם נענה",IF($G14&lt;=$J14,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="20"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="10" t="str">
-        <f aca="false">IF(OR($C15="",$G15=""),"",ROUND(($G15-$C15)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I15" s="5"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="12" t="str">
+        <f aca="false">IF(OR($C15="",$H15=""),"",ROUND(($H15-$C15)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J15" s="23" t="str">
+        <f aca="false">IF(OR($C15="",$E15="",$E15="בקשה"),"",WORKDAY.INTL(INT($C15),IF($E15="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K15" s="24" t="str">
+        <f aca="false">IF($J15="","",IF($G15="","טרם נענה",IF($G15&lt;=$J15,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="20"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="10" t="str">
-        <f aca="false">IF(OR($C16="",$G16=""),"",ROUND(($G16-$C16)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I16" s="5"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="12" t="str">
+        <f aca="false">IF(OR($C16="",$H16=""),"",ROUND(($H16-$C16)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J16" s="23" t="str">
+        <f aca="false">IF(OR($C16="",$E16="",$E16="בקשה"),"",WORKDAY.INTL(INT($C16),IF($E16="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K16" s="24" t="str">
+        <f aca="false">IF($J16="","",IF($G16="","טרם נענה",IF($G16&lt;=$J16,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="20"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="10" t="str">
-        <f aca="false">IF(OR($C17="",$G17=""),"",ROUND(($G17-$C17)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I17" s="5"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="12" t="str">
+        <f aca="false">IF(OR($C17="",$H17=""),"",ROUND(($H17-$C17)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J17" s="23" t="str">
+        <f aca="false">IF(OR($C17="",$E17="",$E17="בקשה"),"",WORKDAY.INTL(INT($C17),IF($E17="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K17" s="24" t="str">
+        <f aca="false">IF($J17="","",IF($G17="","טרם נענה",IF($G17&lt;=$J17,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="20"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="10" t="str">
-        <f aca="false">IF(OR($C18="",$G18=""),"",ROUND(($G18-$C18)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I18" s="5"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="12" t="str">
+        <f aca="false">IF(OR($C18="",$H18=""),"",ROUND(($H18-$C18)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J18" s="23" t="str">
+        <f aca="false">IF(OR($C18="",$E18="",$E18="בקשה"),"",WORKDAY.INTL(INT($C18),IF($E18="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K18" s="24" t="str">
+        <f aca="false">IF($J18="","",IF($G18="","טרם נענה",IF($G18&lt;=$J18,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="20"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="10" t="str">
-        <f aca="false">IF(OR($C19="",$G19=""),"",ROUND(($G19-$C19)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I19" s="5"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="12" t="str">
+        <f aca="false">IF(OR($C19="",$H19=""),"",ROUND(($H19-$C19)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J19" s="23" t="str">
+        <f aca="false">IF(OR($C19="",$E19="",$E19="בקשה"),"",WORKDAY.INTL(INT($C19),IF($E19="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K19" s="24" t="str">
+        <f aca="false">IF($J19="","",IF($G19="","טרם נענה",IF($G19&lt;=$J19,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="20"/>
+      <c r="C20" s="22"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="10" t="str">
-        <f aca="false">IF(OR($C20="",$G20=""),"",ROUND(($G20-$C20)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I20" s="5"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="12" t="str">
+        <f aca="false">IF(OR($C20="",$H20=""),"",ROUND(($H20-$C20)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J20" s="23" t="str">
+        <f aca="false">IF(OR($C20="",$E20="",$E20="בקשה"),"",WORKDAY.INTL(INT($C20),IF($E20="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K20" s="24" t="str">
+        <f aca="false">IF($J20="","",IF($G20="","טרם נענה",IF($G20&lt;=$J20,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="20"/>
+      <c r="C21" s="22"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="10" t="str">
-        <f aca="false">IF(OR($C21="",$G21=""),"",ROUND(($G21-$C21)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I21" s="5"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="12" t="str">
+        <f aca="false">IF(OR($C21="",$H21=""),"",ROUND(($H21-$C21)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J21" s="23" t="str">
+        <f aca="false">IF(OR($C21="",$E21="",$E21="בקשה"),"",WORKDAY.INTL(INT($C21),IF($E21="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K21" s="24" t="str">
+        <f aca="false">IF($J21="","",IF($G21="","טרם נענה",IF($G21&lt;=$J21,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="20"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="10" t="str">
-        <f aca="false">IF(OR($C22="",$G22=""),"",ROUND(($G22-$C22)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I22" s="5"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="12" t="str">
+        <f aca="false">IF(OR($C22="",$H22=""),"",ROUND(($H22-$C22)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J22" s="23" t="str">
+        <f aca="false">IF(OR($C22="",$E22="",$E22="בקשה"),"",WORKDAY.INTL(INT($C22),IF($E22="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K22" s="24" t="str">
+        <f aca="false">IF($J22="","",IF($G22="","טרם נענה",IF($G22&lt;=$J22,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="20"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="10" t="str">
-        <f aca="false">IF(OR($C23="",$G23=""),"",ROUND(($G23-$C23)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I23" s="5"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="12" t="str">
+        <f aca="false">IF(OR($C23="",$H23=""),"",ROUND(($H23-$C23)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J23" s="23" t="str">
+        <f aca="false">IF(OR($C23="",$E23="",$E23="בקשה"),"",WORKDAY.INTL(INT($C23),IF($E23="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K23" s="24" t="str">
+        <f aca="false">IF($J23="","",IF($G23="","טרם נענה",IF($G23&lt;=$J23,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="20"/>
+      <c r="C24" s="22"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="10" t="str">
-        <f aca="false">IF(OR($C24="",$G24=""),"",ROUND(($G24-$C24)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I24" s="5"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="12" t="str">
+        <f aca="false">IF(OR($C24="",$H24=""),"",ROUND(($H24-$C24)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J24" s="23" t="str">
+        <f aca="false">IF(OR($C24="",$E24="",$E24="בקשה"),"",WORKDAY.INTL(INT($C24),IF($E24="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K24" s="24" t="str">
+        <f aca="false">IF($J24="","",IF($G24="","טרם נענה",IF($G24&lt;=$J24,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="20"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="10" t="str">
-        <f aca="false">IF(OR($C25="",$G25=""),"",ROUND(($G25-$C25)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I25" s="5"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="12" t="str">
+        <f aca="false">IF(OR($C25="",$H25=""),"",ROUND(($H25-$C25)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J25" s="23" t="str">
+        <f aca="false">IF(OR($C25="",$E25="",$E25="בקשה"),"",WORKDAY.INTL(INT($C25),IF($E25="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K25" s="24" t="str">
+        <f aca="false">IF($J25="","",IF($G25="","טרם נענה",IF($G25&lt;=$J25,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="20"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="10" t="str">
-        <f aca="false">IF(OR($C26="",$G26=""),"",ROUND(($G26-$C26)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I26" s="5"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="12" t="str">
+        <f aca="false">IF(OR($C26="",$H26=""),"",ROUND(($H26-$C26)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J26" s="23" t="str">
+        <f aca="false">IF(OR($C26="",$E26="",$E26="בקשה"),"",WORKDAY.INTL(INT($C26),IF($E26="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K26" s="24" t="str">
+        <f aca="false">IF($J26="","",IF($G26="","טרם נענה",IF($G26&lt;=$J26,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="20"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="10" t="str">
-        <f aca="false">IF(OR($C27="",$G27=""),"",ROUND(($G27-$C27)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I27" s="5"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="12" t="str">
+        <f aca="false">IF(OR($C27="",$H27=""),"",ROUND(($H27-$C27)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J27" s="23" t="str">
+        <f aca="false">IF(OR($C27="",$E27="",$E27="בקשה"),"",WORKDAY.INTL(INT($C27),IF($E27="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K27" s="24" t="str">
+        <f aca="false">IF($J27="","",IF($G27="","טרם נענה",IF($G27&lt;=$J27,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="20"/>
+      <c r="C28" s="22"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="10" t="str">
-        <f aca="false">IF(OR($C28="",$G28=""),"",ROUND(($G28-$C28)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I28" s="5"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="12" t="str">
+        <f aca="false">IF(OR($C28="",$H28=""),"",ROUND(($H28-$C28)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J28" s="23" t="str">
+        <f aca="false">IF(OR($C28="",$E28="",$E28="בקשה"),"",WORKDAY.INTL(INT($C28),IF($E28="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K28" s="24" t="str">
+        <f aca="false">IF($J28="","",IF($G28="","טרם נענה",IF($G28&lt;=$J28,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="20"/>
+      <c r="C29" s="22"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="10" t="str">
-        <f aca="false">IF(OR($C29="",$G29=""),"",ROUND(($G29-$C29)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I29" s="5"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="12" t="str">
+        <f aca="false">IF(OR($C29="",$H29=""),"",ROUND(($H29-$C29)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J29" s="23" t="str">
+        <f aca="false">IF(OR($C29="",$E29="",$E29="בקשה"),"",WORKDAY.INTL(INT($C29),IF($E29="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K29" s="24" t="str">
+        <f aca="false">IF($J29="","",IF($G29="","טרם נענה",IF($G29&lt;=$J29,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="20"/>
+      <c r="C30" s="22"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="10" t="str">
-        <f aca="false">IF(OR($C30="",$G30=""),"",ROUND(($G30-$C30)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I30" s="5"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="12" t="str">
+        <f aca="false">IF(OR($C30="",$H30=""),"",ROUND(($H30-$C30)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J30" s="23" t="str">
+        <f aca="false">IF(OR($C30="",$E30="",$E30="בקשה"),"",WORKDAY.INTL(INT($C30),IF($E30="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K30" s="24" t="str">
+        <f aca="false">IF($J30="","",IF($G30="","טרם נענה",IF($G30&lt;=$J30,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="20"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="10" t="str">
-        <f aca="false">IF(OR($C31="",$G31=""),"",ROUND(($G31-$C31)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I31" s="5"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="12" t="str">
+        <f aca="false">IF(OR($C31="",$H31=""),"",ROUND(($H31-$C31)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J31" s="23" t="str">
+        <f aca="false">IF(OR($C31="",$E31="",$E31="בקשה"),"",WORKDAY.INTL(INT($C31),IF($E31="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K31" s="24" t="str">
+        <f aca="false">IF($J31="","",IF($G31="","טרם נענה",IF($G31&lt;=$J31,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="20"/>
+      <c r="C32" s="22"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="10" t="str">
-        <f aca="false">IF(OR($C32="",$G32=""),"",ROUND(($G32-$C32)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I32" s="5"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="12" t="str">
+        <f aca="false">IF(OR($C32="",$H32=""),"",ROUND(($H32-$C32)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J32" s="23" t="str">
+        <f aca="false">IF(OR($C32="",$E32="",$E32="בקשה"),"",WORKDAY.INTL(INT($C32),IF($E32="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K32" s="24" t="str">
+        <f aca="false">IF($J32="","",IF($G32="","טרם נענה",IF($G32&lt;=$J32,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="20"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="10" t="str">
-        <f aca="false">IF(OR($C33="",$G33=""),"",ROUND(($G33-$C33)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I33" s="5"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="12" t="str">
+        <f aca="false">IF(OR($C33="",$H33=""),"",ROUND(($H33-$C33)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J33" s="23" t="str">
+        <f aca="false">IF(OR($C33="",$E33="",$E33="בקשה"),"",WORKDAY.INTL(INT($C33),IF($E33="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K33" s="24" t="str">
+        <f aca="false">IF($J33="","",IF($G33="","טרם נענה",IF($G33&lt;=$J33,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="20"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="10" t="str">
-        <f aca="false">IF(OR($C34="",$G34=""),"",ROUND(($G34-$C34)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I34" s="5"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="12" t="str">
+        <f aca="false">IF(OR($C34="",$H34=""),"",ROUND(($H34-$C34)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J34" s="23" t="str">
+        <f aca="false">IF(OR($C34="",$E34="",$E34="בקשה"),"",WORKDAY.INTL(INT($C34),IF($E34="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K34" s="24" t="str">
+        <f aca="false">IF($J34="","",IF($G34="","טרם נענה",IF($G34&lt;=$J34,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="20"/>
+      <c r="C35" s="22"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="10" t="str">
-        <f aca="false">IF(OR($C35="",$G35=""),"",ROUND(($G35-$C35)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I35" s="5"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="12" t="str">
+        <f aca="false">IF(OR($C35="",$H35=""),"",ROUND(($H35-$C35)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J35" s="23" t="str">
+        <f aca="false">IF(OR($C35="",$E35="",$E35="בקשה"),"",WORKDAY.INTL(INT($C35),IF($E35="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K35" s="24" t="str">
+        <f aca="false">IF($J35="","",IF($G35="","טרם נענה",IF($G35&lt;=$J35,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="20"/>
+      <c r="C36" s="22"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="10" t="str">
-        <f aca="false">IF(OR($C36="",$G36=""),"",ROUND(($G36-$C36)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I36" s="5"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="12" t="str">
+        <f aca="false">IF(OR($C36="",$H36=""),"",ROUND(($H36-$C36)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J36" s="23" t="str">
+        <f aca="false">IF(OR($C36="",$E36="",$E36="בקשה"),"",WORKDAY.INTL(INT($C36),IF($E36="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K36" s="24" t="str">
+        <f aca="false">IF($J36="","",IF($G36="","טרם נענה",IF($G36&lt;=$J36,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="20"/>
+      <c r="C37" s="22"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="10" t="str">
-        <f aca="false">IF(OR($C37="",$G37=""),"",ROUND(($G37-$C37)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I37" s="5"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="12" t="str">
+        <f aca="false">IF(OR($C37="",$H37=""),"",ROUND(($H37-$C37)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J37" s="23" t="str">
+        <f aca="false">IF(OR($C37="",$E37="",$E37="בקשה"),"",WORKDAY.INTL(INT($C37),IF($E37="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K37" s="24" t="str">
+        <f aca="false">IF($J37="","",IF($G37="","טרם נענה",IF($G37&lt;=$J37,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="22"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="10" t="str">
-        <f aca="false">IF(OR($C38="",$G38=""),"",ROUND(($G38-$C38)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I38" s="5"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="12" t="str">
+        <f aca="false">IF(OR($C38="",$H38=""),"",ROUND(($H38-$C38)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J38" s="23" t="str">
+        <f aca="false">IF(OR($C38="",$E38="",$E38="בקשה"),"",WORKDAY.INTL(INT($C38),IF($E38="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K38" s="24" t="str">
+        <f aca="false">IF($J38="","",IF($G38="","טרם נענה",IF($G38&lt;=$J38,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="20"/>
+      <c r="C39" s="22"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="10" t="str">
-        <f aca="false">IF(OR($C39="",$G39=""),"",ROUND(($G39-$C39)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I39" s="5"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="12" t="str">
+        <f aca="false">IF(OR($C39="",$H39=""),"",ROUND(($H39-$C39)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J39" s="23" t="str">
+        <f aca="false">IF(OR($C39="",$E39="",$E39="בקשה"),"",WORKDAY.INTL(INT($C39),IF($E39="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K39" s="24" t="str">
+        <f aca="false">IF($J39="","",IF($G39="","טרם נענה",IF($G39&lt;=$J39,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="20"/>
+      <c r="C40" s="22"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="10" t="str">
-        <f aca="false">IF(OR($C40="",$G40=""),"",ROUND(($G40-$C40)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I40" s="5"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="12" t="str">
+        <f aca="false">IF(OR($C40="",$H40=""),"",ROUND(($H40-$C40)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J40" s="23" t="str">
+        <f aca="false">IF(OR($C40="",$E40="",$E40="בקשה"),"",WORKDAY.INTL(INT($C40),IF($E40="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K40" s="24" t="str">
+        <f aca="false">IF($J40="","",IF($G40="","טרם נענה",IF($G40&lt;=$J40,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="20"/>
+      <c r="C41" s="22"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="10" t="str">
-        <f aca="false">IF(OR($C41="",$G41=""),"",ROUND(($G41-$C41)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I41" s="5"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="12" t="str">
+        <f aca="false">IF(OR($C41="",$H41=""),"",ROUND(($H41-$C41)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J41" s="23" t="str">
+        <f aca="false">IF(OR($C41="",$E41="",$E41="בקשה"),"",WORKDAY.INTL(INT($C41),IF($E41="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K41" s="24" t="str">
+        <f aca="false">IF($J41="","",IF($G41="","טרם נענה",IF($G41&lt;=$J41,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="20"/>
+      <c r="C42" s="22"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="10" t="str">
-        <f aca="false">IF(OR($C42="",$G42=""),"",ROUND(($G42-$C42)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I42" s="5"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="12" t="str">
+        <f aca="false">IF(OR($C42="",$H42=""),"",ROUND(($H42-$C42)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J42" s="23" t="str">
+        <f aca="false">IF(OR($C42="",$E42="",$E42="בקשה"),"",WORKDAY.INTL(INT($C42),IF($E42="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K42" s="24" t="str">
+        <f aca="false">IF($J42="","",IF($G42="","טרם נענה",IF($G42&lt;=$J42,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="20"/>
+      <c r="C43" s="22"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="10" t="str">
-        <f aca="false">IF(OR($C43="",$G43=""),"",ROUND(($G43-$C43)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I43" s="5"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="12" t="str">
+        <f aca="false">IF(OR($C43="",$H43=""),"",ROUND(($H43-$C43)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J43" s="23" t="str">
+        <f aca="false">IF(OR($C43="",$E43="",$E43="בקשה"),"",WORKDAY.INTL(INT($C43),IF($E43="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K43" s="24" t="str">
+        <f aca="false">IF($J43="","",IF($G43="","טרם נענה",IF($G43&lt;=$J43,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="20"/>
+      <c r="C44" s="22"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="10" t="str">
-        <f aca="false">IF(OR($C44="",$G44=""),"",ROUND(($G44-$C44)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I44" s="5"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="12" t="str">
+        <f aca="false">IF(OR($C44="",$H44=""),"",ROUND(($H44-$C44)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J44" s="23" t="str">
+        <f aca="false">IF(OR($C44="",$E44="",$E44="בקשה"),"",WORKDAY.INTL(INT($C44),IF($E44="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K44" s="24" t="str">
+        <f aca="false">IF($J44="","",IF($G44="","טרם נענה",IF($G44&lt;=$J44,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="20"/>
+      <c r="C45" s="22"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="10" t="str">
-        <f aca="false">IF(OR($C45="",$G45=""),"",ROUND(($G45-$C45)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I45" s="5"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="12" t="str">
+        <f aca="false">IF(OR($C45="",$H45=""),"",ROUND(($H45-$C45)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J45" s="23" t="str">
+        <f aca="false">IF(OR($C45="",$E45="",$E45="בקשה"),"",WORKDAY.INTL(INT($C45),IF($E45="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K45" s="24" t="str">
+        <f aca="false">IF($J45="","",IF($G45="","טרם נענה",IF($G45&lt;=$J45,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="20"/>
+      <c r="C46" s="22"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="10" t="str">
-        <f aca="false">IF(OR($C46="",$G46=""),"",ROUND(($G46-$C46)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I46" s="5"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="12" t="str">
+        <f aca="false">IF(OR($C46="",$H46=""),"",ROUND(($H46-$C46)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J46" s="23" t="str">
+        <f aca="false">IF(OR($C46="",$E46="",$E46="בקשה"),"",WORKDAY.INTL(INT($C46),IF($E46="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K46" s="24" t="str">
+        <f aca="false">IF($J46="","",IF($G46="","טרם נענה",IF($G46&lt;=$J46,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="20"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="10" t="str">
-        <f aca="false">IF(OR($C47="",$G47=""),"",ROUND(($G47-$C47)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I47" s="5"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="12" t="str">
+        <f aca="false">IF(OR($C47="",$H47=""),"",ROUND(($H47-$C47)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J47" s="23" t="str">
+        <f aca="false">IF(OR($C47="",$E47="",$E47="בקשה"),"",WORKDAY.INTL(INT($C47),IF($E47="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K47" s="24" t="str">
+        <f aca="false">IF($J47="","",IF($G47="","טרם נענה",IF($G47&lt;=$J47,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="20"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="10" t="str">
-        <f aca="false">IF(OR($C48="",$G48=""),"",ROUND(($G48-$C48)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I48" s="5"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="12" t="str">
+        <f aca="false">IF(OR($C48="",$H48=""),"",ROUND(($H48-$C48)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J48" s="23" t="str">
+        <f aca="false">IF(OR($C48="",$E48="",$E48="בקשה"),"",WORKDAY.INTL(INT($C48),IF($E48="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K48" s="24" t="str">
+        <f aca="false">IF($J48="","",IF($G48="","טרם נענה",IF($G48&lt;=$J48,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="20"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="10" t="str">
-        <f aca="false">IF(OR($C49="",$G49=""),"",ROUND(($G49-$C49)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I49" s="5"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="12" t="str">
+        <f aca="false">IF(OR($C49="",$H49=""),"",ROUND(($H49-$C49)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J49" s="23" t="str">
+        <f aca="false">IF(OR($C49="",$E49="",$E49="בקשה"),"",WORKDAY.INTL(INT($C49),IF($E49="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K49" s="24" t="str">
+        <f aca="false">IF($J49="","",IF($G49="","טרם נענה",IF($G49&lt;=$J49,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="20"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="10" t="str">
-        <f aca="false">IF(OR($C50="",$G50=""),"",ROUND(($G50-$C50)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I50" s="5"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="12" t="str">
+        <f aca="false">IF(OR($C50="",$H50=""),"",ROUND(($H50-$C50)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J50" s="23" t="str">
+        <f aca="false">IF(OR($C50="",$E50="",$E50="בקשה"),"",WORKDAY.INTL(INT($C50),IF($E50="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K50" s="24" t="str">
+        <f aca="false">IF($J50="","",IF($G50="","טרם נענה",IF($G50&lt;=$J50,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="20"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="10" t="str">
-        <f aca="false">IF(OR($C51="",$G51=""),"",ROUND(($G51-$C51)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I51" s="5"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="12" t="str">
+        <f aca="false">IF(OR($C51="",$H51=""),"",ROUND(($H51-$C51)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J51" s="23" t="str">
+        <f aca="false">IF(OR($C51="",$E51="",$E51="בקשה"),"",WORKDAY.INTL(INT($C51),IF($E51="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K51" s="24" t="str">
+        <f aca="false">IF($J51="","",IF($G51="","טרם נענה",IF($G51&lt;=$J51,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="20"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="10" t="str">
-        <f aca="false">IF(OR($C52="",$G52=""),"",ROUND(($G52-$C52)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I52" s="5"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="12" t="str">
+        <f aca="false">IF(OR($C52="",$H52=""),"",ROUND(($H52-$C52)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J52" s="23" t="str">
+        <f aca="false">IF(OR($C52="",$E52="",$E52="בקשה"),"",WORKDAY.INTL(INT($C52),IF($E52="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K52" s="24" t="str">
+        <f aca="false">IF($J52="","",IF($G52="","טרם נענה",IF($G52&lt;=$J52,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="20"/>
+      <c r="C53" s="22"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="10" t="str">
-        <f aca="false">IF(OR($C53="",$G53=""),"",ROUND(($G53-$C53)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I53" s="5"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="12" t="str">
+        <f aca="false">IF(OR($C53="",$H53=""),"",ROUND(($H53-$C53)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J53" s="23" t="str">
+        <f aca="false">IF(OR($C53="",$E53="",$E53="בקשה"),"",WORKDAY.INTL(INT($C53),IF($E53="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K53" s="24" t="str">
+        <f aca="false">IF($J53="","",IF($G53="","טרם נענה",IF($G53&lt;=$J53,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="20"/>
+      <c r="C54" s="22"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="10" t="str">
-        <f aca="false">IF(OR($C54="",$G54=""),"",ROUND(($G54-$C54)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I54" s="5"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="12" t="str">
+        <f aca="false">IF(OR($C54="",$H54=""),"",ROUND(($H54-$C54)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J54" s="23" t="str">
+        <f aca="false">IF(OR($C54="",$E54="",$E54="בקשה"),"",WORKDAY.INTL(INT($C54),IF($E54="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K54" s="24" t="str">
+        <f aca="false">IF($J54="","",IF($G54="","טרם נענה",IF($G54&lt;=$J54,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="20"/>
+      <c r="C55" s="22"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="10" t="str">
-        <f aca="false">IF(OR($C55="",$G55=""),"",ROUND(($G55-$C55)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I55" s="5"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="12" t="str">
+        <f aca="false">IF(OR($C55="",$H55=""),"",ROUND(($H55-$C55)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J55" s="23" t="str">
+        <f aca="false">IF(OR($C55="",$E55="",$E55="בקשה"),"",WORKDAY.INTL(INT($C55),IF($E55="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K55" s="24" t="str">
+        <f aca="false">IF($J55="","",IF($G55="","טרם נענה",IF($G55&lt;=$J55,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="20"/>
+      <c r="C56" s="22"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="10" t="str">
-        <f aca="false">IF(OR($C56="",$G56=""),"",ROUND(($G56-$C56)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I56" s="5"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="12" t="str">
+        <f aca="false">IF(OR($C56="",$H56=""),"",ROUND(($H56-$C56)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J56" s="23" t="str">
+        <f aca="false">IF(OR($C56="",$E56="",$E56="בקשה"),"",WORKDAY.INTL(INT($C56),IF($E56="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K56" s="24" t="str">
+        <f aca="false">IF($J56="","",IF($G56="","טרם נענה",IF($G56&lt;=$J56,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="20"/>
+      <c r="C57" s="22"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="10" t="str">
-        <f aca="false">IF(OR($C57="",$G57=""),"",ROUND(($G57-$C57)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I57" s="5"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="12" t="str">
+        <f aca="false">IF(OR($C57="",$H57=""),"",ROUND(($H57-$C57)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J57" s="23" t="str">
+        <f aca="false">IF(OR($C57="",$E57="",$E57="בקשה"),"",WORKDAY.INTL(INT($C57),IF($E57="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K57" s="24" t="str">
+        <f aca="false">IF($J57="","",IF($G57="","טרם נענה",IF($G57&lt;=$J57,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="20"/>
+      <c r="C58" s="22"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="10" t="str">
-        <f aca="false">IF(OR($C58="",$G58=""),"",ROUND(($G58-$C58)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I58" s="5"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="12" t="str">
+        <f aca="false">IF(OR($C58="",$H58=""),"",ROUND(($H58-$C58)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J58" s="23" t="str">
+        <f aca="false">IF(OR($C58="",$E58="",$E58="בקשה"),"",WORKDAY.INTL(INT($C58),IF($E58="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K58" s="24" t="str">
+        <f aca="false">IF($J58="","",IF($G58="","טרם נענה",IF($G58&lt;=$J58,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="20"/>
+      <c r="C59" s="22"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="10" t="str">
-        <f aca="false">IF(OR($C59="",$G59=""),"",ROUND(($G59-$C59)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I59" s="5"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="12" t="str">
+        <f aca="false">IF(OR($C59="",$H59=""),"",ROUND(($H59-$C59)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J59" s="23" t="str">
+        <f aca="false">IF(OR($C59="",$E59="",$E59="בקשה"),"",WORKDAY.INTL(INT($C59),IF($E59="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K59" s="24" t="str">
+        <f aca="false">IF($J59="","",IF($G59="","טרם נענה",IF($G59&lt;=$J59,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="20"/>
+      <c r="C60" s="22"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="10" t="str">
-        <f aca="false">IF(OR($C60="",$G60=""),"",ROUND(($G60-$C60)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I60" s="5"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="12" t="str">
+        <f aca="false">IF(OR($C60="",$H60=""),"",ROUND(($H60-$C60)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J60" s="23" t="str">
+        <f aca="false">IF(OR($C60="",$E60="",$E60="בקשה"),"",WORKDAY.INTL(INT($C60),IF($E60="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K60" s="24" t="str">
+        <f aca="false">IF($J60="","",IF($G60="","טרם נענה",IF($G60&lt;=$J60,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="20"/>
+      <c r="C61" s="22"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="10" t="str">
-        <f aca="false">IF(OR($C61="",$G61=""),"",ROUND(($G61-$C61)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I61" s="5"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="12" t="str">
+        <f aca="false">IF(OR($C61="",$H61=""),"",ROUND(($H61-$C61)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J61" s="23" t="str">
+        <f aca="false">IF(OR($C61="",$E61="",$E61="בקשה"),"",WORKDAY.INTL(INT($C61),IF($E61="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K61" s="24" t="str">
+        <f aca="false">IF($J61="","",IF($G61="","טרם נענה",IF($G61&lt;=$J61,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="20"/>
+      <c r="C62" s="22"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="10" t="str">
-        <f aca="false">IF(OR($C62="",$G62=""),"",ROUND(($G62-$C62)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I62" s="5"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="12" t="str">
+        <f aca="false">IF(OR($C62="",$H62=""),"",ROUND(($H62-$C62)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J62" s="23" t="str">
+        <f aca="false">IF(OR($C62="",$E62="",$E62="בקשה"),"",WORKDAY.INTL(INT($C62),IF($E62="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K62" s="24" t="str">
+        <f aca="false">IF($J62="","",IF($G62="","טרם נענה",IF($G62&lt;=$J62,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="20"/>
+      <c r="C63" s="22"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="10" t="str">
-        <f aca="false">IF(OR($C63="",$G63=""),"",ROUND(($G63-$C63)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I63" s="5"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="12" t="str">
+        <f aca="false">IF(OR($C63="",$H63=""),"",ROUND(($H63-$C63)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J63" s="23" t="str">
+        <f aca="false">IF(OR($C63="",$E63="",$E63="בקשה"),"",WORKDAY.INTL(INT($C63),IF($E63="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K63" s="24" t="str">
+        <f aca="false">IF($J63="","",IF($G63="","טרם נענה",IF($G63&lt;=$J63,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="20"/>
+      <c r="C64" s="22"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="10" t="str">
-        <f aca="false">IF(OR($C64="",$G64=""),"",ROUND(($G64-$C64)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I64" s="5"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="12" t="str">
+        <f aca="false">IF(OR($C64="",$H64=""),"",ROUND(($H64-$C64)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J64" s="23" t="str">
+        <f aca="false">IF(OR($C64="",$E64="",$E64="בקשה"),"",WORKDAY.INTL(INT($C64),IF($E64="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K64" s="24" t="str">
+        <f aca="false">IF($J64="","",IF($G64="","טרם נענה",IF($G64&lt;=$J64,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="20"/>
+      <c r="C65" s="22"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="10" t="str">
-        <f aca="false">IF(OR($C65="",$G65=""),"",ROUND(($G65-$C65)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I65" s="5"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="12" t="str">
+        <f aca="false">IF(OR($C65="",$H65=""),"",ROUND(($H65-$C65)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J65" s="23" t="str">
+        <f aca="false">IF(OR($C65="",$E65="",$E65="בקשה"),"",WORKDAY.INTL(INT($C65),IF($E65="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K65" s="24" t="str">
+        <f aca="false">IF($J65="","",IF($G65="","טרם נענה",IF($G65&lt;=$J65,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="20"/>
+      <c r="C66" s="22"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="10" t="str">
-        <f aca="false">IF(OR($C66="",$G66=""),"",ROUND(($G66-$C66)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I66" s="5"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="12" t="str">
+        <f aca="false">IF(OR($C66="",$H66=""),"",ROUND(($H66-$C66)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J66" s="23" t="str">
+        <f aca="false">IF(OR($C66="",$E66="",$E66="בקשה"),"",WORKDAY.INTL(INT($C66),IF($E66="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K66" s="24" t="str">
+        <f aca="false">IF($J66="","",IF($G66="","טרם נענה",IF($G66&lt;=$J66,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="20"/>
+      <c r="C67" s="22"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="10" t="str">
-        <f aca="false">IF(OR($C67="",$G67=""),"",ROUND(($G67-$C67)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I67" s="5"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="12" t="str">
+        <f aca="false">IF(OR($C67="",$H67=""),"",ROUND(($H67-$C67)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J67" s="23" t="str">
+        <f aca="false">IF(OR($C67="",$E67="",$E67="בקשה"),"",WORKDAY.INTL(INT($C67),IF($E67="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K67" s="24" t="str">
+        <f aca="false">IF($J67="","",IF($G67="","טרם נענה",IF($G67&lt;=$J67,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="20"/>
+      <c r="C68" s="22"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="10" t="str">
-        <f aca="false">IF(OR($C68="",$G68=""),"",ROUND(($G68-$C68)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I68" s="5"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="12" t="str">
+        <f aca="false">IF(OR($C68="",$H68=""),"",ROUND(($H68-$C68)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J68" s="23" t="str">
+        <f aca="false">IF(OR($C68="",$E68="",$E68="בקשה"),"",WORKDAY.INTL(INT($C68),IF($E68="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K68" s="24" t="str">
+        <f aca="false">IF($J68="","",IF($G68="","טרם נענה",IF($G68&lt;=$J68,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="20"/>
+      <c r="C69" s="22"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="10" t="str">
-        <f aca="false">IF(OR($C69="",$G69=""),"",ROUND(($G69-$C69)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I69" s="5"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="12" t="str">
+        <f aca="false">IF(OR($C69="",$H69=""),"",ROUND(($H69-$C69)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J69" s="23" t="str">
+        <f aca="false">IF(OR($C69="",$E69="",$E69="בקשה"),"",WORKDAY.INTL(INT($C69),IF($E69="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K69" s="24" t="str">
+        <f aca="false">IF($J69="","",IF($G69="","טרם נענה",IF($G69&lt;=$J69,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="20"/>
+      <c r="C70" s="22"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="10" t="str">
-        <f aca="false">IF(OR($C70="",$G70=""),"",ROUND(($G70-$C70)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I70" s="5"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="12" t="str">
+        <f aca="false">IF(OR($C70="",$H70=""),"",ROUND(($H70-$C70)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J70" s="23" t="str">
+        <f aca="false">IF(OR($C70="",$E70="",$E70="בקשה"),"",WORKDAY.INTL(INT($C70),IF($E70="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K70" s="24" t="str">
+        <f aca="false">IF($J70="","",IF($G70="","טרם נענה",IF($G70&lt;=$J70,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="20"/>
+      <c r="C71" s="22"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="10" t="str">
-        <f aca="false">IF(OR($C71="",$G71=""),"",ROUND(($G71-$C71)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I71" s="5"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="12" t="str">
+        <f aca="false">IF(OR($C71="",$H71=""),"",ROUND(($H71-$C71)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J71" s="23" t="str">
+        <f aca="false">IF(OR($C71="",$E71="",$E71="בקשה"),"",WORKDAY.INTL(INT($C71),IF($E71="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K71" s="24" t="str">
+        <f aca="false">IF($J71="","",IF($G71="","טרם נענה",IF($G71&lt;=$J71,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="20"/>
+      <c r="C72" s="22"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="10" t="str">
-        <f aca="false">IF(OR($C72="",$G72=""),"",ROUND(($G72-$C72)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I72" s="5"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="12" t="str">
+        <f aca="false">IF(OR($C72="",$H72=""),"",ROUND(($H72-$C72)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J72" s="23" t="str">
+        <f aca="false">IF(OR($C72="",$E72="",$E72="בקשה"),"",WORKDAY.INTL(INT($C72),IF($E72="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K72" s="24" t="str">
+        <f aca="false">IF($J72="","",IF($G72="","טרם נענה",IF($G72&lt;=$J72,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="20"/>
+      <c r="C73" s="22"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="10" t="str">
-        <f aca="false">IF(OR($C73="",$G73=""),"",ROUND(($G73-$C73)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I73" s="5"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="12" t="str">
+        <f aca="false">IF(OR($C73="",$H73=""),"",ROUND(($H73-$C73)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J73" s="23" t="str">
+        <f aca="false">IF(OR($C73="",$E73="",$E73="בקשה"),"",WORKDAY.INTL(INT($C73),IF($E73="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K73" s="24" t="str">
+        <f aca="false">IF($J73="","",IF($G73="","טרם נענה",IF($G73&lt;=$J73,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="20"/>
+      <c r="C74" s="22"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="10" t="str">
-        <f aca="false">IF(OR($C74="",$G74=""),"",ROUND(($G74-$C74)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I74" s="5"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="12" t="str">
+        <f aca="false">IF(OR($C74="",$H74=""),"",ROUND(($H74-$C74)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J74" s="23" t="str">
+        <f aca="false">IF(OR($C74="",$E74="",$E74="בקשה"),"",WORKDAY.INTL(INT($C74),IF($E74="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K74" s="24" t="str">
+        <f aca="false">IF($J74="","",IF($G74="","טרם נענה",IF($G74&lt;=$J74,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="20"/>
+      <c r="C75" s="22"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="10" t="str">
-        <f aca="false">IF(OR($C75="",$G75=""),"",ROUND(($G75-$C75)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I75" s="5"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="12" t="str">
+        <f aca="false">IF(OR($C75="",$H75=""),"",ROUND(($H75-$C75)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J75" s="23" t="str">
+        <f aca="false">IF(OR($C75="",$E75="",$E75="בקשה"),"",WORKDAY.INTL(INT($C75),IF($E75="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K75" s="24" t="str">
+        <f aca="false">IF($J75="","",IF($G75="","טרם נענה",IF($G75&lt;=$J75,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="20"/>
+      <c r="C76" s="22"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="10" t="str">
-        <f aca="false">IF(OR($C76="",$G76=""),"",ROUND(($G76-$C76)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I76" s="5"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="12" t="str">
+        <f aca="false">IF(OR($C76="",$H76=""),"",ROUND(($H76-$C76)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J76" s="23" t="str">
+        <f aca="false">IF(OR($C76="",$E76="",$E76="בקשה"),"",WORKDAY.INTL(INT($C76),IF($E76="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K76" s="24" t="str">
+        <f aca="false">IF($J76="","",IF($G76="","טרם נענה",IF($G76&lt;=$J76,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="20"/>
+      <c r="C77" s="22"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="10" t="str">
-        <f aca="false">IF(OR($C77="",$G77=""),"",ROUND(($G77-$C77)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I77" s="5"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="12" t="str">
+        <f aca="false">IF(OR($C77="",$H77=""),"",ROUND(($H77-$C77)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J77" s="23" t="str">
+        <f aca="false">IF(OR($C77="",$E77="",$E77="בקשה"),"",WORKDAY.INTL(INT($C77),IF($E77="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K77" s="24" t="str">
+        <f aca="false">IF($J77="","",IF($G77="","טרם נענה",IF($G77&lt;=$J77,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="20"/>
+      <c r="C78" s="22"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="10" t="str">
-        <f aca="false">IF(OR($C78="",$G78=""),"",ROUND(($G78-$C78)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I78" s="5"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="12" t="str">
+        <f aca="false">IF(OR($C78="",$H78=""),"",ROUND(($H78-$C78)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J78" s="23" t="str">
+        <f aca="false">IF(OR($C78="",$E78="",$E78="בקשה"),"",WORKDAY.INTL(INT($C78),IF($E78="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K78" s="24" t="str">
+        <f aca="false">IF($J78="","",IF($G78="","טרם נענה",IF($G78&lt;=$J78,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="20"/>
+      <c r="C79" s="22"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="10" t="str">
-        <f aca="false">IF(OR($C79="",$G79=""),"",ROUND(($G79-$C79)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I79" s="5"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="12" t="str">
+        <f aca="false">IF(OR($C79="",$H79=""),"",ROUND(($H79-$C79)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J79" s="23" t="str">
+        <f aca="false">IF(OR($C79="",$E79="",$E79="בקשה"),"",WORKDAY.INTL(INT($C79),IF($E79="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K79" s="24" t="str">
+        <f aca="false">IF($J79="","",IF($G79="","טרם נענה",IF($G79&lt;=$J79,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="20"/>
+      <c r="C80" s="22"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="10" t="str">
-        <f aca="false">IF(OR($C80="",$G80=""),"",ROUND(($G80-$C80)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I80" s="5"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="12" t="str">
+        <f aca="false">IF(OR($C80="",$H80=""),"",ROUND(($H80-$C80)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J80" s="23" t="str">
+        <f aca="false">IF(OR($C80="",$E80="",$E80="בקשה"),"",WORKDAY.INTL(INT($C80),IF($E80="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K80" s="24" t="str">
+        <f aca="false">IF($J80="","",IF($G80="","טרם נענה",IF($G80&lt;=$J80,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L80" s="5"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="20"/>
+      <c r="C81" s="22"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="10" t="str">
-        <f aca="false">IF(OR($C81="",$G81=""),"",ROUND(($G81-$C81)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I81" s="5"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="12" t="str">
+        <f aca="false">IF(OR($C81="",$H81=""),"",ROUND(($H81-$C81)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J81" s="23" t="str">
+        <f aca="false">IF(OR($C81="",$E81="",$E81="בקשה"),"",WORKDAY.INTL(INT($C81),IF($E81="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K81" s="24" t="str">
+        <f aca="false">IF($J81="","",IF($G81="","טרם נענה",IF($G81&lt;=$J81,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="20"/>
+      <c r="C82" s="22"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="10" t="str">
-        <f aca="false">IF(OR($C82="",$G82=""),"",ROUND(($G82-$C82)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I82" s="5"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="12" t="str">
+        <f aca="false">IF(OR($C82="",$H82=""),"",ROUND(($H82-$C82)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J82" s="23" t="str">
+        <f aca="false">IF(OR($C82="",$E82="",$E82="בקשה"),"",WORKDAY.INTL(INT($C82),IF($E82="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K82" s="24" t="str">
+        <f aca="false">IF($J82="","",IF($G82="","טרם נענה",IF($G82&lt;=$J82,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="20"/>
+      <c r="C83" s="22"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="10" t="str">
-        <f aca="false">IF(OR($C83="",$G83=""),"",ROUND(($G83-$C83)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I83" s="5"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="12" t="str">
+        <f aca="false">IF(OR($C83="",$H83=""),"",ROUND(($H83-$C83)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J83" s="23" t="str">
+        <f aca="false">IF(OR($C83="",$E83="",$E83="בקשה"),"",WORKDAY.INTL(INT($C83),IF($E83="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K83" s="24" t="str">
+        <f aca="false">IF($J83="","",IF($G83="","טרם נענה",IF($G83&lt;=$J83,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="20"/>
+      <c r="C84" s="22"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="10" t="str">
-        <f aca="false">IF(OR($C84="",$G84=""),"",ROUND(($G84-$C84)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I84" s="5"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="12" t="str">
+        <f aca="false">IF(OR($C84="",$H84=""),"",ROUND(($H84-$C84)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J84" s="23" t="str">
+        <f aca="false">IF(OR($C84="",$E84="",$E84="בקשה"),"",WORKDAY.INTL(INT($C84),IF($E84="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K84" s="24" t="str">
+        <f aca="false">IF($J84="","",IF($G84="","טרם נענה",IF($G84&lt;=$J84,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="20"/>
+      <c r="C85" s="22"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="10" t="str">
-        <f aca="false">IF(OR($C85="",$G85=""),"",ROUND(($G85-$C85)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I85" s="5"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="12" t="str">
+        <f aca="false">IF(OR($C85="",$H85=""),"",ROUND(($H85-$C85)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J85" s="23" t="str">
+        <f aca="false">IF(OR($C85="",$E85="",$E85="בקשה"),"",WORKDAY.INTL(INT($C85),IF($E85="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K85" s="24" t="str">
+        <f aca="false">IF($J85="","",IF($G85="","טרם נענה",IF($G85&lt;=$J85,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
-      <c r="C86" s="20"/>
+      <c r="C86" s="22"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="10" t="str">
-        <f aca="false">IF(OR($C86="",$G86=""),"",ROUND(($G86-$C86)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I86" s="5"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="12" t="str">
+        <f aca="false">IF(OR($C86="",$H86=""),"",ROUND(($H86-$C86)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J86" s="23" t="str">
+        <f aca="false">IF(OR($C86="",$E86="",$E86="בקשה"),"",WORKDAY.INTL(INT($C86),IF($E86="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K86" s="24" t="str">
+        <f aca="false">IF($J86="","",IF($G86="","טרם נענה",IF($G86&lt;=$J86,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
-      <c r="C87" s="20"/>
+      <c r="C87" s="22"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="10" t="str">
-        <f aca="false">IF(OR($C87="",$G87=""),"",ROUND(($G87-$C87)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I87" s="5"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="12" t="str">
+        <f aca="false">IF(OR($C87="",$H87=""),"",ROUND(($H87-$C87)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J87" s="23" t="str">
+        <f aca="false">IF(OR($C87="",$E87="",$E87="בקשה"),"",WORKDAY.INTL(INT($C87),IF($E87="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K87" s="24" t="str">
+        <f aca="false">IF($J87="","",IF($G87="","טרם נענה",IF($G87&lt;=$J87,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="20"/>
+      <c r="C88" s="22"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="10" t="str">
-        <f aca="false">IF(OR($C88="",$G88=""),"",ROUND(($G88-$C88)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I88" s="5"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="12" t="str">
+        <f aca="false">IF(OR($C88="",$H88=""),"",ROUND(($H88-$C88)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J88" s="23" t="str">
+        <f aca="false">IF(OR($C88="",$E88="",$E88="בקשה"),"",WORKDAY.INTL(INT($C88),IF($E88="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K88" s="24" t="str">
+        <f aca="false">IF($J88="","",IF($G88="","טרם נענה",IF($G88&lt;=$J88,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
-      <c r="C89" s="20"/>
+      <c r="C89" s="22"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="20"/>
-      <c r="H89" s="10" t="str">
-        <f aca="false">IF(OR($C89="",$G89=""),"",ROUND(($G89-$C89)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I89" s="5"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="12" t="str">
+        <f aca="false">IF(OR($C89="",$H89=""),"",ROUND(($H89-$C89)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J89" s="23" t="str">
+        <f aca="false">IF(OR($C89="",$E89="",$E89="בקשה"),"",WORKDAY.INTL(INT($C89),IF($E89="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K89" s="24" t="str">
+        <f aca="false">IF($J89="","",IF($G89="","טרם נענה",IF($G89&lt;=$J89,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
-      <c r="C90" s="20"/>
+      <c r="C90" s="22"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="10" t="str">
-        <f aca="false">IF(OR($C90="",$G90=""),"",ROUND(($G90-$C90)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I90" s="5"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="12" t="str">
+        <f aca="false">IF(OR($C90="",$H90=""),"",ROUND(($H90-$C90)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J90" s="23" t="str">
+        <f aca="false">IF(OR($C90="",$E90="",$E90="בקשה"),"",WORKDAY.INTL(INT($C90),IF($E90="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K90" s="24" t="str">
+        <f aca="false">IF($J90="","",IF($G90="","טרם נענה",IF($G90&lt;=$J90,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
-      <c r="C91" s="20"/>
+      <c r="C91" s="22"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="10" t="str">
-        <f aca="false">IF(OR($C91="",$G91=""),"",ROUND(($G91-$C91)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I91" s="5"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="22"/>
+      <c r="I91" s="12" t="str">
+        <f aca="false">IF(OR($C91="",$H91=""),"",ROUND(($H91-$C91)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J91" s="23" t="str">
+        <f aca="false">IF(OR($C91="",$E91="",$E91="בקשה"),"",WORKDAY.INTL(INT($C91),IF($E91="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K91" s="24" t="str">
+        <f aca="false">IF($J91="","",IF($G91="","טרם נענה",IF($G91&lt;=$J91,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L91" s="5"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
-      <c r="C92" s="20"/>
+      <c r="C92" s="22"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="10" t="str">
-        <f aca="false">IF(OR($C92="",$G92=""),"",ROUND(($G92-$C92)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I92" s="5"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="12" t="str">
+        <f aca="false">IF(OR($C92="",$H92=""),"",ROUND(($H92-$C92)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J92" s="23" t="str">
+        <f aca="false">IF(OR($C92="",$E92="",$E92="בקשה"),"",WORKDAY.INTL(INT($C92),IF($E92="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K92" s="24" t="str">
+        <f aca="false">IF($J92="","",IF($G92="","טרם נענה",IF($G92&lt;=$J92,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
-      <c r="C93" s="20"/>
+      <c r="C93" s="22"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="10" t="str">
-        <f aca="false">IF(OR($C93="",$G93=""),"",ROUND(($G93-$C93)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I93" s="5"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="12" t="str">
+        <f aca="false">IF(OR($C93="",$H93=""),"",ROUND(($H93-$C93)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J93" s="23" t="str">
+        <f aca="false">IF(OR($C93="",$E93="",$E93="בקשה"),"",WORKDAY.INTL(INT($C93),IF($E93="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K93" s="24" t="str">
+        <f aca="false">IF($J93="","",IF($G93="","טרם נענה",IF($G93&lt;=$J93,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L93" s="5"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
-      <c r="C94" s="20"/>
+      <c r="C94" s="22"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="20"/>
-      <c r="H94" s="10" t="str">
-        <f aca="false">IF(OR($C94="",$G94=""),"",ROUND(($G94-$C94)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I94" s="5"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="12" t="str">
+        <f aca="false">IF(OR($C94="",$H94=""),"",ROUND(($H94-$C94)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J94" s="23" t="str">
+        <f aca="false">IF(OR($C94="",$E94="",$E94="בקשה"),"",WORKDAY.INTL(INT($C94),IF($E94="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K94" s="24" t="str">
+        <f aca="false">IF($J94="","",IF($G94="","טרם נענה",IF($G94&lt;=$J94,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L94" s="5"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
-      <c r="C95" s="20"/>
+      <c r="C95" s="22"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="10" t="str">
-        <f aca="false">IF(OR($C95="",$G95=""),"",ROUND(($G95-$C95)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I95" s="5"/>
+      <c r="G95" s="22"/>
+      <c r="H95" s="22"/>
+      <c r="I95" s="12" t="str">
+        <f aca="false">IF(OR($C95="",$H95=""),"",ROUND(($H95-$C95)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J95" s="23" t="str">
+        <f aca="false">IF(OR($C95="",$E95="",$E95="בקשה"),"",WORKDAY.INTL(INT($C95),IF($E95="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K95" s="24" t="str">
+        <f aca="false">IF($J95="","",IF($G95="","טרם נענה",IF($G95&lt;=$J95,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
-      <c r="C96" s="20"/>
+      <c r="C96" s="22"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="20"/>
-      <c r="H96" s="10" t="str">
-        <f aca="false">IF(OR($C96="",$G96=""),"",ROUND(($G96-$C96)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I96" s="5"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="22"/>
+      <c r="I96" s="12" t="str">
+        <f aca="false">IF(OR($C96="",$H96=""),"",ROUND(($H96-$C96)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J96" s="23" t="str">
+        <f aca="false">IF(OR($C96="",$E96="",$E96="בקשה"),"",WORKDAY.INTL(INT($C96),IF($E96="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K96" s="24" t="str">
+        <f aca="false">IF($J96="","",IF($G96="","טרם נענה",IF($G96&lt;=$J96,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
-      <c r="C97" s="20"/>
+      <c r="C97" s="22"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="10" t="str">
-        <f aca="false">IF(OR($C97="",$G97=""),"",ROUND(($G97-$C97)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I97" s="5"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="12" t="str">
+        <f aca="false">IF(OR($C97="",$H97=""),"",ROUND(($H97-$C97)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J97" s="23" t="str">
+        <f aca="false">IF(OR($C97="",$E97="",$E97="בקשה"),"",WORKDAY.INTL(INT($C97),IF($E97="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K97" s="24" t="str">
+        <f aca="false">IF($J97="","",IF($G97="","טרם נענה",IF($G97&lt;=$J97,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L97" s="5"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
-      <c r="C98" s="20"/>
+      <c r="C98" s="22"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="20"/>
-      <c r="H98" s="10" t="str">
-        <f aca="false">IF(OR($C98="",$G98=""),"",ROUND(($G98-$C98)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I98" s="5"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="12" t="str">
+        <f aca="false">IF(OR($C98="",$H98=""),"",ROUND(($H98-$C98)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J98" s="23" t="str">
+        <f aca="false">IF(OR($C98="",$E98="",$E98="בקשה"),"",WORKDAY.INTL(INT($C98),IF($E98="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K98" s="24" t="str">
+        <f aca="false">IF($J98="","",IF($G98="","טרם נענה",IF($G98&lt;=$J98,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="5"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
-      <c r="C99" s="20"/>
+      <c r="C99" s="22"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="10" t="str">
-        <f aca="false">IF(OR($C99="",$G99=""),"",ROUND(($G99-$C99)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I99" s="5"/>
+      <c r="G99" s="22"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="12" t="str">
+        <f aca="false">IF(OR($C99="",$H99=""),"",ROUND(($H99-$C99)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J99" s="23" t="str">
+        <f aca="false">IF(OR($C99="",$E99="",$E99="בקשה"),"",WORKDAY.INTL(INT($C99),IF($E99="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K99" s="24" t="str">
+        <f aca="false">IF($J99="","",IF($G99="","טרם נענה",IF($G99&lt;=$J99,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
-      <c r="C100" s="20"/>
+      <c r="C100" s="22"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="10" t="str">
-        <f aca="false">IF(OR($C100="",$G100=""),"",ROUND(($G100-$C100)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I100" s="5"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="12" t="str">
+        <f aca="false">IF(OR($C100="",$H100=""),"",ROUND(($H100-$C100)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J100" s="23" t="str">
+        <f aca="false">IF(OR($C100="",$E100="",$E100="בקשה"),"",WORKDAY.INTL(INT($C100),IF($E100="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K100" s="24" t="str">
+        <f aca="false">IF($J100="","",IF($G100="","טרם נענה",IF($G100&lt;=$J100,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="5"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
-      <c r="C101" s="20"/>
+      <c r="C101" s="22"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="10" t="str">
-        <f aca="false">IF(OR($C101="",$G101=""),"",ROUND(($G101-$C101)*24,1))</f>
-        <v/>
-      </c>
-      <c r="I101" s="5"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="12" t="str">
+        <f aca="false">IF(OR($C101="",$H101=""),"",ROUND(($H101-$C101)*24,1))</f>
+        <v/>
+      </c>
+      <c r="J101" s="23" t="str">
+        <f aca="false">IF(OR($C101="",$E101="",$E101="בקשה"),"",WORKDAY.INTL(INT($C101),IF($E101="קריטי",1,3),7)+1-1/1440)</f>
+        <v/>
+      </c>
+      <c r="K101" s="24" t="str">
+        <f aca="false">IF($J101="","",IF($G101="","טרם נענה",IF($G101&lt;=$J101,"✓","✗")))</f>
+        <v/>
+      </c>
+      <c r="L101" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K101">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"✓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"✗"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E101" type="list">
-      <formula1>"קריטית,רגילה"</formula1>
+      <formula1>"קריטי,אזהרה,בקשה"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F101" type="list">
@@ -5177,6 +6835,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5185,101 +6844,119 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="22" t="n">
+      <c r="A2" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="26" t="n">
         <v>5700</v>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="26" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="22" t="n">
+      <c r="A3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="26" t="n">
         <v>8700</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="26" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="22" t="n">
+      <c r="A4" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="26" t="n">
         <v>13150</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="26" t="n">
         <v>350</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>132</v>
+      <c r="A6" s="20" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>133</v>
+      <c r="A8" s="27" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="25" t="n">
-        <f aca="false">COUNTIF(לקוחות!$L$2:$L$21,"פעיל")</f>
+      <c r="A9" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="29" t="n">
+        <f aca="false">COUNTIF(לקוחות!$N$2:$N$21,"פעיל")</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="26" t="n">
-        <f aca="false">SUMIFS(לקוחות!$G$2:$G$21,לקוחות!$L$2:$L$21,"פעיל")</f>
+      <c r="A10" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="30" t="n">
+        <f aca="false">SUMIFS(לקוחות!$G$2:$G$21,לקוחות!$N$2:$N$21,"פעיל")</f>
         <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="25" t="n">
+      <c r="A11" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="29" t="n">
         <f aca="false">COUNTIF(פניות!$F$2:$F$500,"פתוחה")</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="27" t="n">
-        <f aca="false">SUM(שעות!$D$2:$D$500)</f>
-        <v>15.5</v>
+      <c r="A12" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <f aca="false">COUNTIFS(פניות!$E$2:$E$500,"קריטי",פניות!$K$2:$K$500,"✗")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="31" t="n">
+        <f aca="false">SUM(שעות!$D$2:$D$500)-SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="31" t="n">
+        <f aca="false">SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
+++ b/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
@@ -30,7 +30,105 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="U1" authorId="0">
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">אחוז המקדמה נקבע בתא </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">E2 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">בלשונית חבילות (הצעה: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">50%).</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>70</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">לפי המדיניות המוצעת: לא מזמינים ציוד לפני שהמקדמה שולמה (בהרחבות — תשלום מלא)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>70</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-237</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="Z1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -119,7 +217,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="Z1" authorId="0">
+    <comment ref="AE1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -176,7 +274,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="AA1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -233,7 +331,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="AB1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -377,8 +475,75 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">הצעה מ-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20/09 (PRD 3, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">שאלה </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1): 50% בחתימה לפני הזמנת ציוד, היתרה באישור קבלה חתום. ממתין לבדיקה.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>-1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-385</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="163">
   <si>
     <t xml:space="preserve">OneHome — גיליון מעקב לקוחות (קובץ דוגמה)</t>
   </si>
@@ -395,7 +560,7 @@
     <t xml:space="preserve">הלשוניות</t>
   </si>
   <si>
-    <t xml:space="preserve">לקוחות — שורה לכל לקוח. נוסחאות מוכנות עד שורה 21. כולל מחיר בפועל, עלות חומרה וחשמלאי, רווח לשעה, שעות תמיכה ומזהה ניטור. שדות ה-IP, MAC, R2 ומזהה הניטור הם אלה ש-PRD 4 (כלי ניהול פנימי) יצטרך, כך שבהמשך אפשר לייבא אותם.</t>
+    <t xml:space="preserve">לקוחות — שורה לכל לקוח. נוסחאות מוכנות עד שורה 21. כולל מחיר בפועל, עלות חומרה וחשמלאי, רווח לשעה, שעות תמיכה ומזהה ניטור. כולל עמודות תשלום: מקדמה, אפשר להזמין ציוד, יתרה. שדות ה-IP, MAC, R2 ומזהה הניטור הם אלה ש-PRD 4 (כלי ניהול פנימי) יצטרך, כך שבהמשך אפשר לייבא אותם.</t>
   </si>
   <si>
     <t xml:space="preserve">Checklist — עמודה לכל לקוח, נמשכת אוטומטית מלשונית לקוחות (5 הלקוחות הראשונים). מבוסס על PRD 3, סעיפים B ו-D. "לא רלוונטי" לא נספר באחוז ההתקנה.</t>
@@ -425,10 +590,13 @@
     <t xml:space="preserve">4. תחילת ריטיינר = תאריך אישור קבלה חתום (החלטה ב-PRD 3, סעיף B).</t>
   </si>
   <si>
-    <t xml:space="preserve">5. "מזהה ניטור" הוא עמודה כללית — עוד לא הוחלט איזה כלי ניטור ישמש (Sentry, דופק או אחר).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. בדיקת ה-SLA מניחה ימי עסקים א׳–ה׳ בלי חגים, והיעד הוא סוף יום העסקים ה-N אחרי פתיחת הפנייה. אם שישי נחשב יום עסקים, לתקן את הנוסחה בעמודה "יעד SLA".</t>
+    <t xml:space="preserve">5. מקדמה (הצעה מ-20/09, ממתינה לבדיקה): 50% בחתימה לפני הזמנת ציוד, 50% באישור קבלה חתום. האחוז נקבע בתא E2 בלשונית חבילות. בהרחבות — תשלום מלא לפני הזמנת חומרה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. "מזהה ניטור" הוא עמודה כללית — עוד לא הוחלט איזה כלי ניטור ישמש (Sentry, דופק או אחר).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. בדיקת ה-SLA מניחה ימי עסקים א׳–ה׳ בלי חגים, והיעד הוא סוף יום העסקים ה-N אחרי פתיחת הפנייה. אם שישי נחשב יום עסקים, לתקן את הנוסחה בעמודה "יעד SLA".</t>
   </si>
   <si>
     <t xml:space="preserve">מזהה לקוח</t>
@@ -458,6 +626,21 @@
     <t xml:space="preserve">מחיר בפועל</t>
   </si>
   <si>
+    <t xml:space="preserve">מקדמה בחתימה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תאריך שולמה מקדמה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אפשר להזמין ציוד?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תאריך שולמה יתרה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יתרה לגבייה</t>
+  </si>
+  <si>
     <t xml:space="preserve">תאריך סקר בית</t>
   </si>
   <si>
@@ -815,6 +998,9 @@
     <t xml:space="preserve">ריטיינר חודשי (₪)</t>
   </si>
   <si>
+    <t xml:space="preserve">אחוז מקדמה בחתימה</t>
+  </si>
+  <si>
     <t xml:space="preserve">EcoHome</t>
   </si>
   <si>
@@ -840,6 +1026,9 @@
   </si>
   <si>
     <t xml:space="preserve">סה"כ שעות התקנה (ללא תמיכה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ יתרה לגבייה</t>
   </si>
   <si>
     <t xml:space="preserve">סה"כ שעות תמיכה</t>
@@ -849,16 +1038,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₪&quot;"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot; ₪&quot;;[RED]\-#,##0&quot; ₪&quot;"/>
     <numFmt numFmtId="168" formatCode="0%"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="General"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm"/>
-    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="171" formatCode="0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1057,6 +1245,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1070,10 +1262,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1109,15 +1297,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1129,6 +1313,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1137,7 +1325,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1424,7 +1612,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1461,7 +1649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1514,14 +1702,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1733,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1548,144 +1741,163 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="34" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="37" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL1" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F2" s="6" t="n">
         <f aca="false">IF($E2="","",IFERROR(INDEX(חבילות!$B$2:$B$4,MATCH($E2,חבילות!$A$2:$A$4,0)),""))</f>
@@ -1702,84 +1914,102 @@
         <f aca="false">IF(OR($A2="",$F2=""),"",$F2+N($H2))</f>
         <v>8700</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="6" t="n">
+        <f aca="false">IF($I2="","",ROUND($I2*חבילות!$E$2,0))</f>
+        <v>4350</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L2" s="9" t="str">
+        <f aca="false">IF($A2="","",IF($K2="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v>כן</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <f aca="false">IF($I2="","",$I2-IF($K2="",0,$J2)-IF($M2="",0,$I2-$J2))</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="8" t="n">
         <v>46300</v>
       </c>
-      <c r="K2" s="8" t="n">
+      <c r="P2" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="L2" s="8" t="n">
+      <c r="Q2" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="M2" s="9" t="n">
-        <f aca="false">IF($L2="","",$L2)</f>
+      <c r="R2" s="10" t="n">
+        <f aca="false">IF($Q2="","",$Q2)</f>
         <v>46314</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="S2" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="Y2" s="7" t="n">
+      <c r="AD2" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="Z2" s="10" t="n">
-        <f aca="false">IF(OR($A2="",$I2="",$X2=""),"",$I2-$X2-N($Y2))</f>
+      <c r="AE2" s="11" t="n">
+        <f aca="false">IF(OR($A2="",$I2="",$AC2=""),"",$I2-$AC2-N($AD2))</f>
         <v>3700</v>
       </c>
-      <c r="AA2" s="11" t="n">
+      <c r="AF2" s="12" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A2,Checklist!$C$1:$G$1,0)),""))</f>
         <v>1</v>
       </c>
-      <c r="AB2" s="12" t="n">
+      <c r="AG2" s="13" t="n">
         <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v>18.5</v>
       </c>
-      <c r="AC2" s="10" t="n">
-        <f aca="false">IF($A2="","",IFERROR($Z2/$AB2,""))</f>
+      <c r="AH2" s="11" t="n">
+        <f aca="false">IF($A2="","",IFERROR($AE2/$AG2,""))</f>
         <v>200</v>
       </c>
-      <c r="AD2" s="12" t="n">
+      <c r="AI2" s="13" t="n">
         <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v>1.5</v>
       </c>
-      <c r="AE2" s="13" t="n">
+      <c r="AJ2" s="9" t="n">
         <f aca="false">IF($A2="","",COUNTIFS(פניות!$B$2:$B$500,$A2,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v>1</v>
       </c>
-      <c r="AF2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG2" s="5" t="s">
-        <v>66</v>
+      <c r="AK2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1801,51 +2031,65 @@
         <f aca="false">IF(OR($A3="",$F3=""),"",$F3+N($H3))</f>
         <v/>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="6" t="str">
+        <f aca="false">IF($I3="","",ROUND($I3*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="9" t="str">
-        <f aca="false">IF($L3="","",$L3)</f>
-        <v/>
-      </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="L3" s="9" t="str">
+        <f aca="false">IF($A3="","",IF($K3="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="6" t="str">
+        <f aca="false">IF($I3="","",$I3-IF($K3="",0,$J3)-IF($M3="",0,$I3-$J3))</f>
+        <v/>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="10" t="str">
+        <f aca="false">IF($Q3="","",$Q3)</f>
+        <v/>
+      </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="10" t="str">
-        <f aca="false">IF(OR($A3="",$I3="",$X3=""),"",$I3-$X3-N($Y3))</f>
-        <v/>
-      </c>
-      <c r="AA3" s="11" t="str">
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="11" t="str">
+        <f aca="false">IF(OR($A3="",$I3="",$AC3=""),"",$I3-$AC3-N($AD3))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="12" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A3,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB3" s="12" t="str">
+      <c r="AG3" s="13" t="str">
         <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC3" s="10" t="str">
-        <f aca="false">IF($A3="","",IFERROR($Z3/$AB3,""))</f>
-        <v/>
-      </c>
-      <c r="AD3" s="12" t="str">
+      <c r="AH3" s="11" t="str">
+        <f aca="false">IF($A3="","",IFERROR($AE3/$AG3,""))</f>
+        <v/>
+      </c>
+      <c r="AI3" s="13" t="str">
         <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE3" s="13" t="str">
+      <c r="AJ3" s="9" t="str">
         <f aca="false">IF($A3="","",COUNTIFS(פניות!$B$2:$B$500,$A3,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
@@ -1866,51 +2110,65 @@
         <f aca="false">IF(OR($A4="",$F4=""),"",$F4+N($H4))</f>
         <v/>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="6" t="str">
+        <f aca="false">IF($I4="","",ROUND($I4*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="9" t="str">
-        <f aca="false">IF($L4="","",$L4)</f>
-        <v/>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
+      <c r="L4" s="9" t="str">
+        <f aca="false">IF($A4="","",IF($K4="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="6" t="str">
+        <f aca="false">IF($I4="","",$I4-IF($K4="",0,$J4)-IF($M4="",0,$I4-$J4))</f>
+        <v/>
+      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="10" t="str">
+        <f aca="false">IF($Q4="","",$Q4)</f>
+        <v/>
+      </c>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="10" t="str">
-        <f aca="false">IF(OR($A4="",$I4="",$X4=""),"",$I4-$X4-N($Y4))</f>
-        <v/>
-      </c>
-      <c r="AA4" s="11" t="str">
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="11" t="str">
+        <f aca="false">IF(OR($A4="",$I4="",$AC4=""),"",$I4-$AC4-N($AD4))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="12" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A4,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB4" s="12" t="str">
+      <c r="AG4" s="13" t="str">
         <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC4" s="10" t="str">
-        <f aca="false">IF($A4="","",IFERROR($Z4/$AB4,""))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="12" t="str">
+      <c r="AH4" s="11" t="str">
+        <f aca="false">IF($A4="","",IFERROR($AE4/$AG4,""))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="13" t="str">
         <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE4" s="13" t="str">
+      <c r="AJ4" s="9" t="str">
         <f aca="false">IF($A4="","",COUNTIFS(פניות!$B$2:$B$500,$A4,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -1931,51 +2189,65 @@
         <f aca="false">IF(OR($A5="",$F5=""),"",$F5+N($H5))</f>
         <v/>
       </c>
-      <c r="J5" s="8"/>
+      <c r="J5" s="6" t="str">
+        <f aca="false">IF($I5="","",ROUND($I5*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="9" t="str">
-        <f aca="false">IF($L5="","",$L5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="L5" s="9" t="str">
+        <f aca="false">IF($A5="","",IF($K5="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="6" t="str">
+        <f aca="false">IF($I5="","",$I5-IF($K5="",0,$J5)-IF($M5="",0,$I5-$J5))</f>
+        <v/>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="10" t="str">
+        <f aca="false">IF($Q5="","",$Q5)</f>
+        <v/>
+      </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="10" t="str">
-        <f aca="false">IF(OR($A5="",$I5="",$X5=""),"",$I5-$X5-N($Y5))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="11" t="str">
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="11" t="str">
+        <f aca="false">IF(OR($A5="",$I5="",$AC5=""),"",$I5-$AC5-N($AD5))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="12" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A5,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB5" s="12" t="str">
+      <c r="AG5" s="13" t="str">
         <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC5" s="10" t="str">
-        <f aca="false">IF($A5="","",IFERROR($Z5/$AB5,""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="12" t="str">
+      <c r="AH5" s="11" t="str">
+        <f aca="false">IF($A5="","",IFERROR($AE5/$AG5,""))</f>
+        <v/>
+      </c>
+      <c r="AI5" s="13" t="str">
         <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE5" s="13" t="str">
+      <c r="AJ5" s="9" t="str">
         <f aca="false">IF($A5="","",COUNTIFS(פניות!$B$2:$B$500,$A5,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -1996,51 +2268,65 @@
         <f aca="false">IF(OR($A6="",$F6=""),"",$F6+N($H6))</f>
         <v/>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="6" t="str">
+        <f aca="false">IF($I6="","",ROUND($I6*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="9" t="str">
-        <f aca="false">IF($L6="","",$L6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="L6" s="9" t="str">
+        <f aca="false">IF($A6="","",IF($K6="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="6" t="str">
+        <f aca="false">IF($I6="","",$I6-IF($K6="",0,$J6)-IF($M6="",0,$I6-$J6))</f>
+        <v/>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="10" t="str">
+        <f aca="false">IF($Q6="","",$Q6)</f>
+        <v/>
+      </c>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="10" t="str">
-        <f aca="false">IF(OR($A6="",$I6="",$X6=""),"",$I6-$X6-N($Y6))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="11" t="str">
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="11" t="str">
+        <f aca="false">IF(OR($A6="",$I6="",$AC6=""),"",$I6-$AC6-N($AD6))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="12" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A6,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB6" s="12" t="str">
+      <c r="AG6" s="13" t="str">
         <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC6" s="10" t="str">
-        <f aca="false">IF($A6="","",IFERROR($Z6/$AB6,""))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="12" t="str">
+      <c r="AH6" s="11" t="str">
+        <f aca="false">IF($A6="","",IFERROR($AE6/$AG6,""))</f>
+        <v/>
+      </c>
+      <c r="AI6" s="13" t="str">
         <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE6" s="13" t="str">
+      <c r="AJ6" s="9" t="str">
         <f aca="false">IF($A6="","",COUNTIFS(פניות!$B$2:$B$500,$A6,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -2061,51 +2347,65 @@
         <f aca="false">IF(OR($A7="",$F7=""),"",$F7+N($H7))</f>
         <v/>
       </c>
-      <c r="J7" s="8"/>
+      <c r="J7" s="6" t="str">
+        <f aca="false">IF($I7="","",ROUND($I7*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="9" t="str">
-        <f aca="false">IF($L7="","",$L7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="L7" s="9" t="str">
+        <f aca="false">IF($A7="","",IF($K7="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="6" t="str">
+        <f aca="false">IF($I7="","",$I7-IF($K7="",0,$J7)-IF($M7="",0,$I7-$J7))</f>
+        <v/>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="10" t="str">
+        <f aca="false">IF($Q7="","",$Q7)</f>
+        <v/>
+      </c>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="10" t="str">
-        <f aca="false">IF(OR($A7="",$I7="",$X7=""),"",$I7-$X7-N($Y7))</f>
-        <v/>
-      </c>
-      <c r="AA7" s="11" t="str">
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="11" t="str">
+        <f aca="false">IF(OR($A7="",$I7="",$AC7=""),"",$I7-$AC7-N($AD7))</f>
+        <v/>
+      </c>
+      <c r="AF7" s="12" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A7,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB7" s="12" t="str">
+      <c r="AG7" s="13" t="str">
         <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC7" s="10" t="str">
-        <f aca="false">IF($A7="","",IFERROR($Z7/$AB7,""))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="12" t="str">
+      <c r="AH7" s="11" t="str">
+        <f aca="false">IF($A7="","",IFERROR($AE7/$AG7,""))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="13" t="str">
         <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE7" s="13" t="str">
+      <c r="AJ7" s="9" t="str">
         <f aca="false">IF($A7="","",COUNTIFS(פניות!$B$2:$B$500,$A7,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -2126,51 +2426,65 @@
         <f aca="false">IF(OR($A8="",$F8=""),"",$F8+N($H8))</f>
         <v/>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="6" t="str">
+        <f aca="false">IF($I8="","",ROUND($I8*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="9" t="str">
-        <f aca="false">IF($L8="","",$L8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="L8" s="9" t="str">
+        <f aca="false">IF($A8="","",IF($K8="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="6" t="str">
+        <f aca="false">IF($I8="","",$I8-IF($K8="",0,$J8)-IF($M8="",0,$I8-$J8))</f>
+        <v/>
+      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="10" t="str">
+        <f aca="false">IF($Q8="","",$Q8)</f>
+        <v/>
+      </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="10" t="str">
-        <f aca="false">IF(OR($A8="",$I8="",$X8=""),"",$I8-$X8-N($Y8))</f>
-        <v/>
-      </c>
-      <c r="AA8" s="11" t="str">
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="11" t="str">
+        <f aca="false">IF(OR($A8="",$I8="",$AC8=""),"",$I8-$AC8-N($AD8))</f>
+        <v/>
+      </c>
+      <c r="AF8" s="12" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A8,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB8" s="12" t="str">
+      <c r="AG8" s="13" t="str">
         <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC8" s="10" t="str">
-        <f aca="false">IF($A8="","",IFERROR($Z8/$AB8,""))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="12" t="str">
+      <c r="AH8" s="11" t="str">
+        <f aca="false">IF($A8="","",IFERROR($AE8/$AG8,""))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="13" t="str">
         <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE8" s="13" t="str">
+      <c r="AJ8" s="9" t="str">
         <f aca="false">IF($A8="","",COUNTIFS(פניות!$B$2:$B$500,$A8,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -2191,51 +2505,65 @@
         <f aca="false">IF(OR($A9="",$F9=""),"",$F9+N($H9))</f>
         <v/>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" s="6" t="str">
+        <f aca="false">IF($I9="","",ROUND($I9*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="9" t="str">
-        <f aca="false">IF($L9="","",$L9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
+      <c r="L9" s="9" t="str">
+        <f aca="false">IF($A9="","",IF($K9="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="6" t="str">
+        <f aca="false">IF($I9="","",$I9-IF($K9="",0,$J9)-IF($M9="",0,$I9-$J9))</f>
+        <v/>
+      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="10" t="str">
+        <f aca="false">IF($Q9="","",$Q9)</f>
+        <v/>
+      </c>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="10" t="str">
-        <f aca="false">IF(OR($A9="",$I9="",$X9=""),"",$I9-$X9-N($Y9))</f>
-        <v/>
-      </c>
-      <c r="AA9" s="11" t="str">
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="11" t="str">
+        <f aca="false">IF(OR($A9="",$I9="",$AC9=""),"",$I9-$AC9-N($AD9))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="12" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A9,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB9" s="12" t="str">
+      <c r="AG9" s="13" t="str">
         <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC9" s="10" t="str">
-        <f aca="false">IF($A9="","",IFERROR($Z9/$AB9,""))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="12" t="str">
+      <c r="AH9" s="11" t="str">
+        <f aca="false">IF($A9="","",IFERROR($AE9/$AG9,""))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="13" t="str">
         <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE9" s="13" t="str">
+      <c r="AJ9" s="9" t="str">
         <f aca="false">IF($A9="","",COUNTIFS(פניות!$B$2:$B$500,$A9,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -2256,51 +2584,65 @@
         <f aca="false">IF(OR($A10="",$F10=""),"",$F10+N($H10))</f>
         <v/>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="6" t="str">
+        <f aca="false">IF($I10="","",ROUND($I10*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="9" t="str">
-        <f aca="false">IF($L10="","",$L10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
+      <c r="L10" s="9" t="str">
+        <f aca="false">IF($A10="","",IF($K10="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="6" t="str">
+        <f aca="false">IF($I10="","",$I10-IF($K10="",0,$J10)-IF($M10="",0,$I10-$J10))</f>
+        <v/>
+      </c>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="10" t="str">
+        <f aca="false">IF($Q10="","",$Q10)</f>
+        <v/>
+      </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="10" t="str">
-        <f aca="false">IF(OR($A10="",$I10="",$X10=""),"",$I10-$X10-N($Y10))</f>
-        <v/>
-      </c>
-      <c r="AA10" s="11" t="str">
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="11" t="str">
+        <f aca="false">IF(OR($A10="",$I10="",$AC10=""),"",$I10-$AC10-N($AD10))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="12" t="str">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A10,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB10" s="12" t="str">
+      <c r="AG10" s="13" t="str">
         <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC10" s="10" t="str">
-        <f aca="false">IF($A10="","",IFERROR($Z10/$AB10,""))</f>
-        <v/>
-      </c>
-      <c r="AD10" s="12" t="str">
+      <c r="AH10" s="11" t="str">
+        <f aca="false">IF($A10="","",IFERROR($AE10/$AG10,""))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="13" t="str">
         <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE10" s="13" t="str">
+      <c r="AJ10" s="9" t="str">
         <f aca="false">IF($A10="","",COUNTIFS(פניות!$B$2:$B$500,$A10,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -2321,51 +2663,65 @@
         <f aca="false">IF(OR($A11="",$F11=""),"",$F11+N($H11))</f>
         <v/>
       </c>
-      <c r="J11" s="8"/>
+      <c r="J11" s="6" t="str">
+        <f aca="false">IF($I11="","",ROUND($I11*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="9" t="str">
-        <f aca="false">IF($L11="","",$L11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
+      <c r="L11" s="9" t="str">
+        <f aca="false">IF($A11="","",IF($K11="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="6" t="str">
+        <f aca="false">IF($I11="","",$I11-IF($K11="",0,$J11)-IF($M11="",0,$I11-$J11))</f>
+        <v/>
+      </c>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="10" t="str">
+        <f aca="false">IF($Q11="","",$Q11)</f>
+        <v/>
+      </c>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="10" t="str">
-        <f aca="false">IF(OR($A11="",$I11="",$X11=""),"",$I11-$X11-N($Y11))</f>
-        <v/>
-      </c>
-      <c r="AA11" s="11" t="str">
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="11" t="str">
+        <f aca="false">IF(OR($A11="",$I11="",$AC11=""),"",$I11-$AC11-N($AD11))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="12" t="str">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A11,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB11" s="12" t="str">
+      <c r="AG11" s="13" t="str">
         <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC11" s="10" t="str">
-        <f aca="false">IF($A11="","",IFERROR($Z11/$AB11,""))</f>
-        <v/>
-      </c>
-      <c r="AD11" s="12" t="str">
+      <c r="AH11" s="11" t="str">
+        <f aca="false">IF($A11="","",IFERROR($AE11/$AG11,""))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="13" t="str">
         <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE11" s="13" t="str">
+      <c r="AJ11" s="9" t="str">
         <f aca="false">IF($A11="","",COUNTIFS(פניות!$B$2:$B$500,$A11,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -2386,51 +2742,65 @@
         <f aca="false">IF(OR($A12="",$F12=""),"",$F12+N($H12))</f>
         <v/>
       </c>
-      <c r="J12" s="8"/>
+      <c r="J12" s="6" t="str">
+        <f aca="false">IF($I12="","",ROUND($I12*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="9" t="str">
-        <f aca="false">IF($L12="","",$L12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
+      <c r="L12" s="9" t="str">
+        <f aca="false">IF($A12="","",IF($K12="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="6" t="str">
+        <f aca="false">IF($I12="","",$I12-IF($K12="",0,$J12)-IF($M12="",0,$I12-$J12))</f>
+        <v/>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="10" t="str">
+        <f aca="false">IF($Q12="","",$Q12)</f>
+        <v/>
+      </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="10" t="str">
-        <f aca="false">IF(OR($A12="",$I12="",$X12=""),"",$I12-$X12-N($Y12))</f>
-        <v/>
-      </c>
-      <c r="AA12" s="11" t="str">
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="11" t="str">
+        <f aca="false">IF(OR($A12="",$I12="",$AC12=""),"",$I12-$AC12-N($AD12))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="12" t="str">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A12,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB12" s="12" t="str">
+      <c r="AG12" s="13" t="str">
         <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC12" s="10" t="str">
-        <f aca="false">IF($A12="","",IFERROR($Z12/$AB12,""))</f>
-        <v/>
-      </c>
-      <c r="AD12" s="12" t="str">
+      <c r="AH12" s="11" t="str">
+        <f aca="false">IF($A12="","",IFERROR($AE12/$AG12,""))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="13" t="str">
         <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE12" s="13" t="str">
+      <c r="AJ12" s="9" t="str">
         <f aca="false">IF($A12="","",COUNTIFS(פניות!$B$2:$B$500,$A12,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -2451,51 +2821,65 @@
         <f aca="false">IF(OR($A13="",$F13=""),"",$F13+N($H13))</f>
         <v/>
       </c>
-      <c r="J13" s="8"/>
+      <c r="J13" s="6" t="str">
+        <f aca="false">IF($I13="","",ROUND($I13*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="9" t="str">
-        <f aca="false">IF($L13="","",$L13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
+      <c r="L13" s="9" t="str">
+        <f aca="false">IF($A13="","",IF($K13="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="6" t="str">
+        <f aca="false">IF($I13="","",$I13-IF($K13="",0,$J13)-IF($M13="",0,$I13-$J13))</f>
+        <v/>
+      </c>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="10" t="str">
+        <f aca="false">IF($Q13="","",$Q13)</f>
+        <v/>
+      </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="10" t="str">
-        <f aca="false">IF(OR($A13="",$I13="",$X13=""),"",$I13-$X13-N($Y13))</f>
-        <v/>
-      </c>
-      <c r="AA13" s="11" t="str">
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="11" t="str">
+        <f aca="false">IF(OR($A13="",$I13="",$AC13=""),"",$I13-$AC13-N($AD13))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="12" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A13,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB13" s="12" t="str">
+      <c r="AG13" s="13" t="str">
         <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC13" s="10" t="str">
-        <f aca="false">IF($A13="","",IFERROR($Z13/$AB13,""))</f>
-        <v/>
-      </c>
-      <c r="AD13" s="12" t="str">
+      <c r="AH13" s="11" t="str">
+        <f aca="false">IF($A13="","",IFERROR($AE13/$AG13,""))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="13" t="str">
         <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE13" s="13" t="str">
+      <c r="AJ13" s="9" t="str">
         <f aca="false">IF($A13="","",COUNTIFS(פניות!$B$2:$B$500,$A13,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
+      <c r="AK13" s="5"/>
+      <c r="AL13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -2516,51 +2900,65 @@
         <f aca="false">IF(OR($A14="",$F14=""),"",$F14+N($H14))</f>
         <v/>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="6" t="str">
+        <f aca="false">IF($I14="","",ROUND($I14*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="9" t="str">
-        <f aca="false">IF($L14="","",$L14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
+      <c r="L14" s="9" t="str">
+        <f aca="false">IF($A14="","",IF($K14="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="6" t="str">
+        <f aca="false">IF($I14="","",$I14-IF($K14="",0,$J14)-IF($M14="",0,$I14-$J14))</f>
+        <v/>
+      </c>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="10" t="str">
+        <f aca="false">IF($Q14="","",$Q14)</f>
+        <v/>
+      </c>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="10" t="str">
-        <f aca="false">IF(OR($A14="",$I14="",$X14=""),"",$I14-$X14-N($Y14))</f>
-        <v/>
-      </c>
-      <c r="AA14" s="11" t="str">
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="11" t="str">
+        <f aca="false">IF(OR($A14="",$I14="",$AC14=""),"",$I14-$AC14-N($AD14))</f>
+        <v/>
+      </c>
+      <c r="AF14" s="12" t="str">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A14,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB14" s="12" t="str">
+      <c r="AG14" s="13" t="str">
         <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC14" s="10" t="str">
-        <f aca="false">IF($A14="","",IFERROR($Z14/$AB14,""))</f>
-        <v/>
-      </c>
-      <c r="AD14" s="12" t="str">
+      <c r="AH14" s="11" t="str">
+        <f aca="false">IF($A14="","",IFERROR($AE14/$AG14,""))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="13" t="str">
         <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE14" s="13" t="str">
+      <c r="AJ14" s="9" t="str">
         <f aca="false">IF($A14="","",COUNTIFS(פניות!$B$2:$B$500,$A14,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -2581,51 +2979,65 @@
         <f aca="false">IF(OR($A15="",$F15=""),"",$F15+N($H15))</f>
         <v/>
       </c>
-      <c r="J15" s="8"/>
+      <c r="J15" s="6" t="str">
+        <f aca="false">IF($I15="","",ROUND($I15*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="9" t="str">
-        <f aca="false">IF($L15="","",$L15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
+      <c r="L15" s="9" t="str">
+        <f aca="false">IF($A15="","",IF($K15="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="6" t="str">
+        <f aca="false">IF($I15="","",$I15-IF($K15="",0,$J15)-IF($M15="",0,$I15-$J15))</f>
+        <v/>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="10" t="str">
+        <f aca="false">IF($Q15="","",$Q15)</f>
+        <v/>
+      </c>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="10" t="str">
-        <f aca="false">IF(OR($A15="",$I15="",$X15=""),"",$I15-$X15-N($Y15))</f>
-        <v/>
-      </c>
-      <c r="AA15" s="11" t="str">
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="11" t="str">
+        <f aca="false">IF(OR($A15="",$I15="",$AC15=""),"",$I15-$AC15-N($AD15))</f>
+        <v/>
+      </c>
+      <c r="AF15" s="12" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A15,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB15" s="12" t="str">
+      <c r="AG15" s="13" t="str">
         <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC15" s="10" t="str">
-        <f aca="false">IF($A15="","",IFERROR($Z15/$AB15,""))</f>
-        <v/>
-      </c>
-      <c r="AD15" s="12" t="str">
+      <c r="AH15" s="11" t="str">
+        <f aca="false">IF($A15="","",IFERROR($AE15/$AG15,""))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="13" t="str">
         <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE15" s="13" t="str">
+      <c r="AJ15" s="9" t="str">
         <f aca="false">IF($A15="","",COUNTIFS(פניות!$B$2:$B$500,$A15,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
+      <c r="AK15" s="5"/>
+      <c r="AL15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -2646,51 +3058,65 @@
         <f aca="false">IF(OR($A16="",$F16=""),"",$F16+N($H16))</f>
         <v/>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="6" t="str">
+        <f aca="false">IF($I16="","",ROUND($I16*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="9" t="str">
-        <f aca="false">IF($L16="","",$L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
+      <c r="L16" s="9" t="str">
+        <f aca="false">IF($A16="","",IF($K16="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="6" t="str">
+        <f aca="false">IF($I16="","",$I16-IF($K16="",0,$J16)-IF($M16="",0,$I16-$J16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="10" t="str">
+        <f aca="false">IF($Q16="","",$Q16)</f>
+        <v/>
+      </c>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="10" t="str">
-        <f aca="false">IF(OR($A16="",$I16="",$X16=""),"",$I16-$X16-N($Y16))</f>
-        <v/>
-      </c>
-      <c r="AA16" s="11" t="str">
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="11" t="str">
+        <f aca="false">IF(OR($A16="",$I16="",$AC16=""),"",$I16-$AC16-N($AD16))</f>
+        <v/>
+      </c>
+      <c r="AF16" s="12" t="str">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A16,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB16" s="12" t="str">
+      <c r="AG16" s="13" t="str">
         <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC16" s="10" t="str">
-        <f aca="false">IF($A16="","",IFERROR($Z16/$AB16,""))</f>
-        <v/>
-      </c>
-      <c r="AD16" s="12" t="str">
+      <c r="AH16" s="11" t="str">
+        <f aca="false">IF($A16="","",IFERROR($AE16/$AG16,""))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="13" t="str">
         <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE16" s="13" t="str">
+      <c r="AJ16" s="9" t="str">
         <f aca="false">IF($A16="","",COUNTIFS(פניות!$B$2:$B$500,$A16,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="5"/>
+      <c r="AK16" s="5"/>
+      <c r="AL16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -2711,51 +3137,65 @@
         <f aca="false">IF(OR($A17="",$F17=""),"",$F17+N($H17))</f>
         <v/>
       </c>
-      <c r="J17" s="8"/>
+      <c r="J17" s="6" t="str">
+        <f aca="false">IF($I17="","",ROUND($I17*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="9" t="str">
-        <f aca="false">IF($L17="","",$L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
+      <c r="L17" s="9" t="str">
+        <f aca="false">IF($A17="","",IF($K17="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="6" t="str">
+        <f aca="false">IF($I17="","",$I17-IF($K17="",0,$J17)-IF($M17="",0,$I17-$J17))</f>
+        <v/>
+      </c>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="10" t="str">
+        <f aca="false">IF($Q17="","",$Q17)</f>
+        <v/>
+      </c>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="10" t="str">
-        <f aca="false">IF(OR($A17="",$I17="",$X17=""),"",$I17-$X17-N($Y17))</f>
-        <v/>
-      </c>
-      <c r="AA17" s="11" t="str">
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="11" t="str">
+        <f aca="false">IF(OR($A17="",$I17="",$AC17=""),"",$I17-$AC17-N($AD17))</f>
+        <v/>
+      </c>
+      <c r="AF17" s="12" t="str">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A17,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB17" s="12" t="str">
+      <c r="AG17" s="13" t="str">
         <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC17" s="10" t="str">
-        <f aca="false">IF($A17="","",IFERROR($Z17/$AB17,""))</f>
-        <v/>
-      </c>
-      <c r="AD17" s="12" t="str">
+      <c r="AH17" s="11" t="str">
+        <f aca="false">IF($A17="","",IFERROR($AE17/$AG17,""))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="13" t="str">
         <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE17" s="13" t="str">
+      <c r="AJ17" s="9" t="str">
         <f aca="false">IF($A17="","",COUNTIFS(פניות!$B$2:$B$500,$A17,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF17" s="5"/>
-      <c r="AG17" s="5"/>
+      <c r="AK17" s="5"/>
+      <c r="AL17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -2776,51 +3216,65 @@
         <f aca="false">IF(OR($A18="",$F18=""),"",$F18+N($H18))</f>
         <v/>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="6" t="str">
+        <f aca="false">IF($I18="","",ROUND($I18*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="9" t="str">
-        <f aca="false">IF($L18="","",$L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
+      <c r="L18" s="9" t="str">
+        <f aca="false">IF($A18="","",IF($K18="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="6" t="str">
+        <f aca="false">IF($I18="","",$I18-IF($K18="",0,$J18)-IF($M18="",0,$I18-$J18))</f>
+        <v/>
+      </c>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="10" t="str">
+        <f aca="false">IF($Q18="","",$Q18)</f>
+        <v/>
+      </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="10" t="str">
-        <f aca="false">IF(OR($A18="",$I18="",$X18=""),"",$I18-$X18-N($Y18))</f>
-        <v/>
-      </c>
-      <c r="AA18" s="11" t="str">
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="11" t="str">
+        <f aca="false">IF(OR($A18="",$I18="",$AC18=""),"",$I18-$AC18-N($AD18))</f>
+        <v/>
+      </c>
+      <c r="AF18" s="12" t="str">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A18,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB18" s="12" t="str">
+      <c r="AG18" s="13" t="str">
         <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC18" s="10" t="str">
-        <f aca="false">IF($A18="","",IFERROR($Z18/$AB18,""))</f>
-        <v/>
-      </c>
-      <c r="AD18" s="12" t="str">
+      <c r="AH18" s="11" t="str">
+        <f aca="false">IF($A18="","",IFERROR($AE18/$AG18,""))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="13" t="str">
         <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE18" s="13" t="str">
+      <c r="AJ18" s="9" t="str">
         <f aca="false">IF($A18="","",COUNTIFS(פניות!$B$2:$B$500,$A18,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -2841,51 +3295,65 @@
         <f aca="false">IF(OR($A19="",$F19=""),"",$F19+N($H19))</f>
         <v/>
       </c>
-      <c r="J19" s="8"/>
+      <c r="J19" s="6" t="str">
+        <f aca="false">IF($I19="","",ROUND($I19*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="9" t="str">
-        <f aca="false">IF($L19="","",$L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
+      <c r="L19" s="9" t="str">
+        <f aca="false">IF($A19="","",IF($K19="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="6" t="str">
+        <f aca="false">IF($I19="","",$I19-IF($K19="",0,$J19)-IF($M19="",0,$I19-$J19))</f>
+        <v/>
+      </c>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="10" t="str">
+        <f aca="false">IF($Q19="","",$Q19)</f>
+        <v/>
+      </c>
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="10" t="str">
-        <f aca="false">IF(OR($A19="",$I19="",$X19=""),"",$I19-$X19-N($Y19))</f>
-        <v/>
-      </c>
-      <c r="AA19" s="11" t="str">
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="11" t="str">
+        <f aca="false">IF(OR($A19="",$I19="",$AC19=""),"",$I19-$AC19-N($AD19))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="12" t="str">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A19,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB19" s="12" t="str">
+      <c r="AG19" s="13" t="str">
         <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC19" s="10" t="str">
-        <f aca="false">IF($A19="","",IFERROR($Z19/$AB19,""))</f>
-        <v/>
-      </c>
-      <c r="AD19" s="12" t="str">
+      <c r="AH19" s="11" t="str">
+        <f aca="false">IF($A19="","",IFERROR($AE19/$AG19,""))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="13" t="str">
         <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE19" s="13" t="str">
+      <c r="AJ19" s="9" t="str">
         <f aca="false">IF($A19="","",COUNTIFS(פניות!$B$2:$B$500,$A19,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -2906,51 +3374,65 @@
         <f aca="false">IF(OR($A20="",$F20=""),"",$F20+N($H20))</f>
         <v/>
       </c>
-      <c r="J20" s="8"/>
+      <c r="J20" s="6" t="str">
+        <f aca="false">IF($I20="","",ROUND($I20*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="9" t="str">
-        <f aca="false">IF($L20="","",$L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
+      <c r="L20" s="9" t="str">
+        <f aca="false">IF($A20="","",IF($K20="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M20" s="8"/>
+      <c r="N20" s="6" t="str">
+        <f aca="false">IF($I20="","",$I20-IF($K20="",0,$J20)-IF($M20="",0,$I20-$J20))</f>
+        <v/>
+      </c>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="10" t="str">
+        <f aca="false">IF($Q20="","",$Q20)</f>
+        <v/>
+      </c>
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="10" t="str">
-        <f aca="false">IF(OR($A20="",$I20="",$X20=""),"",$I20-$X20-N($Y20))</f>
-        <v/>
-      </c>
-      <c r="AA20" s="11" t="str">
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="11" t="str">
+        <f aca="false">IF(OR($A20="",$I20="",$AC20=""),"",$I20-$AC20-N($AD20))</f>
+        <v/>
+      </c>
+      <c r="AF20" s="12" t="str">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A20,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB20" s="12" t="str">
+      <c r="AG20" s="13" t="str">
         <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC20" s="10" t="str">
-        <f aca="false">IF($A20="","",IFERROR($Z20/$AB20,""))</f>
-        <v/>
-      </c>
-      <c r="AD20" s="12" t="str">
+      <c r="AH20" s="11" t="str">
+        <f aca="false">IF($A20="","",IFERROR($AE20/$AG20,""))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="13" t="str">
         <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE20" s="13" t="str">
+      <c r="AJ20" s="9" t="str">
         <f aca="false">IF($A20="","",COUNTIFS(פניות!$B$2:$B$500,$A20,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
+      <c r="AK20" s="5"/>
+      <c r="AL20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -2971,51 +3453,65 @@
         <f aca="false">IF(OR($A21="",$F21=""),"",$F21+N($H21))</f>
         <v/>
       </c>
-      <c r="J21" s="8"/>
+      <c r="J21" s="6" t="str">
+        <f aca="false">IF($I21="","",ROUND($I21*חבילות!$E$2,0))</f>
+        <v/>
+      </c>
       <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="9" t="str">
-        <f aca="false">IF($L21="","",$L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
+      <c r="L21" s="9" t="str">
+        <f aca="false">IF($A21="","",IF($K21="","לא — מקדמה טרם שולמה","כן"))</f>
+        <v/>
+      </c>
+      <c r="M21" s="8"/>
+      <c r="N21" s="6" t="str">
+        <f aca="false">IF($I21="","",$I21-IF($K21="",0,$J21)-IF($M21="",0,$I21-$J21))</f>
+        <v/>
+      </c>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="10" t="str">
+        <f aca="false">IF($Q21="","",$Q21)</f>
+        <v/>
+      </c>
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="10" t="str">
-        <f aca="false">IF(OR($A21="",$I21="",$X21=""),"",$I21-$X21-N($Y21))</f>
-        <v/>
-      </c>
-      <c r="AA21" s="11" t="str">
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="11" t="str">
+        <f aca="false">IF(OR($A21="",$I21="",$AC21=""),"",$I21-$AC21-N($AD21))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="12" t="str">
         <f aca="false">IF($A21="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A21,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AB21" s="12" t="str">
+      <c r="AG21" s="13" t="str">
         <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AC21" s="10" t="str">
-        <f aca="false">IF($A21="","",IFERROR($Z21/$AB21,""))</f>
-        <v/>
-      </c>
-      <c r="AD21" s="12" t="str">
+      <c r="AH21" s="11" t="str">
+        <f aca="false">IF($A21="","",IFERROR($AE21/$AG21,""))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="13" t="str">
         <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AE21" s="13" t="str">
+      <c r="AJ21" s="9" t="str">
         <f aca="false">IF($A21="","",COUNTIFS(פניות!$B$2:$B$500,$A21,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -3023,15 +3519,15 @@
       <formula1>חבילות!$A$2:$A$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S2:S21" type="list">
       <formula1>"ליד,סקר בית,הצעה נשלחה,הזמנת ציוד,התקנה,בדיקות קבלה,פעיל,מושהה,הופסק"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="W2:W21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="V2:V21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AA2:AA21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3062,10 +3558,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C1" s="4" t="str">
         <f aca="false">IF(לקוחות!$A2="","",לקוחות!$A2)</f>
@@ -3090,13 +3586,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -3105,13 +3601,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -3120,13 +3616,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -3135,13 +3631,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -3150,13 +3646,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
@@ -3165,13 +3661,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -3180,13 +3676,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -3195,13 +3691,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -3210,13 +3706,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -3225,13 +3721,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -3240,13 +3736,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
@@ -3255,13 +3751,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -3270,13 +3766,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
@@ -3285,13 +3781,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
@@ -3300,13 +3796,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
@@ -3315,13 +3811,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
@@ -3330,13 +3826,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -3345,13 +3841,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
@@ -3360,13 +3856,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
@@ -3375,13 +3871,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
@@ -3390,13 +3886,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
@@ -3405,13 +3901,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
@@ -3420,13 +3916,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
@@ -3435,13 +3931,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
@@ -3450,13 +3946,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
@@ -3465,13 +3961,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -3480,13 +3976,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -3495,13 +3991,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
@@ -3511,7 +4007,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17"/>
       <c r="B30" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">IF(C$1="","",COUNTIF(C2:C29,"✓")/MAX(1,ROWS(C2:C29)-COUNTIF(C2:C29,"לא רלוונטי")))</f>
@@ -3579,30 +4075,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C2" s="8" t="n">
         <v>46293</v>
@@ -3611,15 +4107,15 @@
         <v>1.5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>46293</v>
@@ -3631,10 +4127,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>46300</v>
@@ -3646,10 +4142,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>46300</v>
@@ -3661,10 +4157,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>46303</v>
@@ -3673,15 +4169,15 @@
         <v>1.5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>46309</v>
@@ -3690,15 +4186,15 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>46314</v>
@@ -3710,10 +4206,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>46314</v>
@@ -3725,10 +4221,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>46314</v>
@@ -3740,10 +4236,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>46314</v>
@@ -3755,10 +4251,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>46316</v>
@@ -3767,15 +4263,15 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>46328</v>
@@ -3784,7 +4280,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4441,60 +4937,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" s="22" t="n">
         <v>46316.3819444445</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G2" s="22" t="n">
         <v>46316.4027777778</v>
@@ -4502,7 +4998,7 @@
       <c r="H2" s="22" t="n">
         <v>46316.4861111111</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="13" t="n">
         <f aca="false">IF(OR($C2="",$H2=""),"",ROUND(($H2-$C2)*24,1))</f>
         <v>2.5</v>
       </c>
@@ -4510,36 +5006,36 @@
         <f aca="false">IF(OR($C2="",$E2="",$E2="בקשה"),"",WORKDAY.INTL(INT($C2),IF($E2="קריטי",1,3),7)+1-1/1440)</f>
         <v>46317.9993055556</v>
       </c>
-      <c r="K2" s="24" t="str">
+      <c r="K2" s="9" t="str">
         <f aca="false">IF($J2="","",IF($G2="","טרם נענה",IF($G2&lt;=$J2,"✓","✗")))</f>
         <v>✓</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C3" s="22" t="n">
         <v>46328.75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
-      <c r="I3" s="12" t="str">
+      <c r="I3" s="13" t="str">
         <f aca="false">IF(OR($C3="",$H3=""),"",ROUND(($H3-$C3)*24,1))</f>
         <v/>
       </c>
@@ -4547,12 +5043,12 @@
         <f aca="false">IF(OR($C3="",$E3="",$E3="בקשה"),"",WORKDAY.INTL(INT($C3),IF($E3="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K3" s="24" t="str">
+      <c r="K3" s="9" t="str">
         <f aca="false">IF($J3="","",IF($G3="","טרם נענה",IF($G3&lt;=$J3,"✓","✗")))</f>
         <v/>
       </c>
       <c r="L3" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4564,7 +5060,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
-      <c r="I4" s="12" t="str">
+      <c r="I4" s="13" t="str">
         <f aca="false">IF(OR($C4="",$H4=""),"",ROUND(($H4-$C4)*24,1))</f>
         <v/>
       </c>
@@ -4572,7 +5068,7 @@
         <f aca="false">IF(OR($C4="",$E4="",$E4="בקשה"),"",WORKDAY.INTL(INT($C4),IF($E4="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K4" s="24" t="str">
+      <c r="K4" s="9" t="str">
         <f aca="false">IF($J4="","",IF($G4="","טרם נענה",IF($G4&lt;=$J4,"✓","✗")))</f>
         <v/>
       </c>
@@ -4587,7 +5083,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
-      <c r="I5" s="12" t="str">
+      <c r="I5" s="13" t="str">
         <f aca="false">IF(OR($C5="",$H5=""),"",ROUND(($H5-$C5)*24,1))</f>
         <v/>
       </c>
@@ -4595,7 +5091,7 @@
         <f aca="false">IF(OR($C5="",$E5="",$E5="בקשה"),"",WORKDAY.INTL(INT($C5),IF($E5="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K5" s="24" t="str">
+      <c r="K5" s="9" t="str">
         <f aca="false">IF($J5="","",IF($G5="","טרם נענה",IF($G5&lt;=$J5,"✓","✗")))</f>
         <v/>
       </c>
@@ -4610,7 +5106,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
-      <c r="I6" s="12" t="str">
+      <c r="I6" s="13" t="str">
         <f aca="false">IF(OR($C6="",$H6=""),"",ROUND(($H6-$C6)*24,1))</f>
         <v/>
       </c>
@@ -4618,7 +5114,7 @@
         <f aca="false">IF(OR($C6="",$E6="",$E6="בקשה"),"",WORKDAY.INTL(INT($C6),IF($E6="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K6" s="24" t="str">
+      <c r="K6" s="9" t="str">
         <f aca="false">IF($J6="","",IF($G6="","טרם נענה",IF($G6&lt;=$J6,"✓","✗")))</f>
         <v/>
       </c>
@@ -4633,7 +5129,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
-      <c r="I7" s="12" t="str">
+      <c r="I7" s="13" t="str">
         <f aca="false">IF(OR($C7="",$H7=""),"",ROUND(($H7-$C7)*24,1))</f>
         <v/>
       </c>
@@ -4641,7 +5137,7 @@
         <f aca="false">IF(OR($C7="",$E7="",$E7="בקשה"),"",WORKDAY.INTL(INT($C7),IF($E7="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K7" s="24" t="str">
+      <c r="K7" s="9" t="str">
         <f aca="false">IF($J7="","",IF($G7="","טרם נענה",IF($G7&lt;=$J7,"✓","✗")))</f>
         <v/>
       </c>
@@ -4656,7 +5152,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
-      <c r="I8" s="12" t="str">
+      <c r="I8" s="13" t="str">
         <f aca="false">IF(OR($C8="",$H8=""),"",ROUND(($H8-$C8)*24,1))</f>
         <v/>
       </c>
@@ -4664,7 +5160,7 @@
         <f aca="false">IF(OR($C8="",$E8="",$E8="בקשה"),"",WORKDAY.INTL(INT($C8),IF($E8="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K8" s="24" t="str">
+      <c r="K8" s="9" t="str">
         <f aca="false">IF($J8="","",IF($G8="","טרם נענה",IF($G8&lt;=$J8,"✓","✗")))</f>
         <v/>
       </c>
@@ -4679,7 +5175,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
-      <c r="I9" s="12" t="str">
+      <c r="I9" s="13" t="str">
         <f aca="false">IF(OR($C9="",$H9=""),"",ROUND(($H9-$C9)*24,1))</f>
         <v/>
       </c>
@@ -4687,7 +5183,7 @@
         <f aca="false">IF(OR($C9="",$E9="",$E9="בקשה"),"",WORKDAY.INTL(INT($C9),IF($E9="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K9" s="24" t="str">
+      <c r="K9" s="9" t="str">
         <f aca="false">IF($J9="","",IF($G9="","טרם נענה",IF($G9&lt;=$J9,"✓","✗")))</f>
         <v/>
       </c>
@@ -4702,7 +5198,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
-      <c r="I10" s="12" t="str">
+      <c r="I10" s="13" t="str">
         <f aca="false">IF(OR($C10="",$H10=""),"",ROUND(($H10-$C10)*24,1))</f>
         <v/>
       </c>
@@ -4710,7 +5206,7 @@
         <f aca="false">IF(OR($C10="",$E10="",$E10="בקשה"),"",WORKDAY.INTL(INT($C10),IF($E10="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K10" s="24" t="str">
+      <c r="K10" s="9" t="str">
         <f aca="false">IF($J10="","",IF($G10="","טרם נענה",IF($G10&lt;=$J10,"✓","✗")))</f>
         <v/>
       </c>
@@ -4725,7 +5221,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="12" t="str">
+      <c r="I11" s="13" t="str">
         <f aca="false">IF(OR($C11="",$H11=""),"",ROUND(($H11-$C11)*24,1))</f>
         <v/>
       </c>
@@ -4733,7 +5229,7 @@
         <f aca="false">IF(OR($C11="",$E11="",$E11="בקשה"),"",WORKDAY.INTL(INT($C11),IF($E11="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K11" s="24" t="str">
+      <c r="K11" s="9" t="str">
         <f aca="false">IF($J11="","",IF($G11="","טרם נענה",IF($G11&lt;=$J11,"✓","✗")))</f>
         <v/>
       </c>
@@ -4748,7 +5244,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
-      <c r="I12" s="12" t="str">
+      <c r="I12" s="13" t="str">
         <f aca="false">IF(OR($C12="",$H12=""),"",ROUND(($H12-$C12)*24,1))</f>
         <v/>
       </c>
@@ -4756,7 +5252,7 @@
         <f aca="false">IF(OR($C12="",$E12="",$E12="בקשה"),"",WORKDAY.INTL(INT($C12),IF($E12="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K12" s="24" t="str">
+      <c r="K12" s="9" t="str">
         <f aca="false">IF($J12="","",IF($G12="","טרם נענה",IF($G12&lt;=$J12,"✓","✗")))</f>
         <v/>
       </c>
@@ -4771,7 +5267,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
-      <c r="I13" s="12" t="str">
+      <c r="I13" s="13" t="str">
         <f aca="false">IF(OR($C13="",$H13=""),"",ROUND(($H13-$C13)*24,1))</f>
         <v/>
       </c>
@@ -4779,7 +5275,7 @@
         <f aca="false">IF(OR($C13="",$E13="",$E13="בקשה"),"",WORKDAY.INTL(INT($C13),IF($E13="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K13" s="24" t="str">
+      <c r="K13" s="9" t="str">
         <f aca="false">IF($J13="","",IF($G13="","טרם נענה",IF($G13&lt;=$J13,"✓","✗")))</f>
         <v/>
       </c>
@@ -4794,7 +5290,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
-      <c r="I14" s="12" t="str">
+      <c r="I14" s="13" t="str">
         <f aca="false">IF(OR($C14="",$H14=""),"",ROUND(($H14-$C14)*24,1))</f>
         <v/>
       </c>
@@ -4802,7 +5298,7 @@
         <f aca="false">IF(OR($C14="",$E14="",$E14="בקשה"),"",WORKDAY.INTL(INT($C14),IF($E14="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K14" s="24" t="str">
+      <c r="K14" s="9" t="str">
         <f aca="false">IF($J14="","",IF($G14="","טרם נענה",IF($G14&lt;=$J14,"✓","✗")))</f>
         <v/>
       </c>
@@ -4817,7 +5313,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
-      <c r="I15" s="12" t="str">
+      <c r="I15" s="13" t="str">
         <f aca="false">IF(OR($C15="",$H15=""),"",ROUND(($H15-$C15)*24,1))</f>
         <v/>
       </c>
@@ -4825,7 +5321,7 @@
         <f aca="false">IF(OR($C15="",$E15="",$E15="בקשה"),"",WORKDAY.INTL(INT($C15),IF($E15="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K15" s="24" t="str">
+      <c r="K15" s="9" t="str">
         <f aca="false">IF($J15="","",IF($G15="","טרם נענה",IF($G15&lt;=$J15,"✓","✗")))</f>
         <v/>
       </c>
@@ -4840,7 +5336,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
-      <c r="I16" s="12" t="str">
+      <c r="I16" s="13" t="str">
         <f aca="false">IF(OR($C16="",$H16=""),"",ROUND(($H16-$C16)*24,1))</f>
         <v/>
       </c>
@@ -4848,7 +5344,7 @@
         <f aca="false">IF(OR($C16="",$E16="",$E16="בקשה"),"",WORKDAY.INTL(INT($C16),IF($E16="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K16" s="24" t="str">
+      <c r="K16" s="9" t="str">
         <f aca="false">IF($J16="","",IF($G16="","טרם נענה",IF($G16&lt;=$J16,"✓","✗")))</f>
         <v/>
       </c>
@@ -4863,7 +5359,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
-      <c r="I17" s="12" t="str">
+      <c r="I17" s="13" t="str">
         <f aca="false">IF(OR($C17="",$H17=""),"",ROUND(($H17-$C17)*24,1))</f>
         <v/>
       </c>
@@ -4871,7 +5367,7 @@
         <f aca="false">IF(OR($C17="",$E17="",$E17="בקשה"),"",WORKDAY.INTL(INT($C17),IF($E17="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K17" s="24" t="str">
+      <c r="K17" s="9" t="str">
         <f aca="false">IF($J17="","",IF($G17="","טרם נענה",IF($G17&lt;=$J17,"✓","✗")))</f>
         <v/>
       </c>
@@ -4886,7 +5382,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
-      <c r="I18" s="12" t="str">
+      <c r="I18" s="13" t="str">
         <f aca="false">IF(OR($C18="",$H18=""),"",ROUND(($H18-$C18)*24,1))</f>
         <v/>
       </c>
@@ -4894,7 +5390,7 @@
         <f aca="false">IF(OR($C18="",$E18="",$E18="בקשה"),"",WORKDAY.INTL(INT($C18),IF($E18="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K18" s="24" t="str">
+      <c r="K18" s="9" t="str">
         <f aca="false">IF($J18="","",IF($G18="","טרם נענה",IF($G18&lt;=$J18,"✓","✗")))</f>
         <v/>
       </c>
@@ -4909,7 +5405,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
-      <c r="I19" s="12" t="str">
+      <c r="I19" s="13" t="str">
         <f aca="false">IF(OR($C19="",$H19=""),"",ROUND(($H19-$C19)*24,1))</f>
         <v/>
       </c>
@@ -4917,7 +5413,7 @@
         <f aca="false">IF(OR($C19="",$E19="",$E19="בקשה"),"",WORKDAY.INTL(INT($C19),IF($E19="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K19" s="24" t="str">
+      <c r="K19" s="9" t="str">
         <f aca="false">IF($J19="","",IF($G19="","טרם נענה",IF($G19&lt;=$J19,"✓","✗")))</f>
         <v/>
       </c>
@@ -4932,7 +5428,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
-      <c r="I20" s="12" t="str">
+      <c r="I20" s="13" t="str">
         <f aca="false">IF(OR($C20="",$H20=""),"",ROUND(($H20-$C20)*24,1))</f>
         <v/>
       </c>
@@ -4940,7 +5436,7 @@
         <f aca="false">IF(OR($C20="",$E20="",$E20="בקשה"),"",WORKDAY.INTL(INT($C20),IF($E20="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K20" s="24" t="str">
+      <c r="K20" s="9" t="str">
         <f aca="false">IF($J20="","",IF($G20="","טרם נענה",IF($G20&lt;=$J20,"✓","✗")))</f>
         <v/>
       </c>
@@ -4955,7 +5451,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
-      <c r="I21" s="12" t="str">
+      <c r="I21" s="13" t="str">
         <f aca="false">IF(OR($C21="",$H21=""),"",ROUND(($H21-$C21)*24,1))</f>
         <v/>
       </c>
@@ -4963,7 +5459,7 @@
         <f aca="false">IF(OR($C21="",$E21="",$E21="בקשה"),"",WORKDAY.INTL(INT($C21),IF($E21="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K21" s="24" t="str">
+      <c r="K21" s="9" t="str">
         <f aca="false">IF($J21="","",IF($G21="","טרם נענה",IF($G21&lt;=$J21,"✓","✗")))</f>
         <v/>
       </c>
@@ -4978,7 +5474,7 @@
       <c r="F22" s="5"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
-      <c r="I22" s="12" t="str">
+      <c r="I22" s="13" t="str">
         <f aca="false">IF(OR($C22="",$H22=""),"",ROUND(($H22-$C22)*24,1))</f>
         <v/>
       </c>
@@ -4986,7 +5482,7 @@
         <f aca="false">IF(OR($C22="",$E22="",$E22="בקשה"),"",WORKDAY.INTL(INT($C22),IF($E22="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K22" s="24" t="str">
+      <c r="K22" s="9" t="str">
         <f aca="false">IF($J22="","",IF($G22="","טרם נענה",IF($G22&lt;=$J22,"✓","✗")))</f>
         <v/>
       </c>
@@ -5001,7 +5497,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
-      <c r="I23" s="12" t="str">
+      <c r="I23" s="13" t="str">
         <f aca="false">IF(OR($C23="",$H23=""),"",ROUND(($H23-$C23)*24,1))</f>
         <v/>
       </c>
@@ -5009,7 +5505,7 @@
         <f aca="false">IF(OR($C23="",$E23="",$E23="בקשה"),"",WORKDAY.INTL(INT($C23),IF($E23="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K23" s="24" t="str">
+      <c r="K23" s="9" t="str">
         <f aca="false">IF($J23="","",IF($G23="","טרם נענה",IF($G23&lt;=$J23,"✓","✗")))</f>
         <v/>
       </c>
@@ -5024,7 +5520,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
-      <c r="I24" s="12" t="str">
+      <c r="I24" s="13" t="str">
         <f aca="false">IF(OR($C24="",$H24=""),"",ROUND(($H24-$C24)*24,1))</f>
         <v/>
       </c>
@@ -5032,7 +5528,7 @@
         <f aca="false">IF(OR($C24="",$E24="",$E24="בקשה"),"",WORKDAY.INTL(INT($C24),IF($E24="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K24" s="24" t="str">
+      <c r="K24" s="9" t="str">
         <f aca="false">IF($J24="","",IF($G24="","טרם נענה",IF($G24&lt;=$J24,"✓","✗")))</f>
         <v/>
       </c>
@@ -5047,7 +5543,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="12" t="str">
+      <c r="I25" s="13" t="str">
         <f aca="false">IF(OR($C25="",$H25=""),"",ROUND(($H25-$C25)*24,1))</f>
         <v/>
       </c>
@@ -5055,7 +5551,7 @@
         <f aca="false">IF(OR($C25="",$E25="",$E25="בקשה"),"",WORKDAY.INTL(INT($C25),IF($E25="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K25" s="24" t="str">
+      <c r="K25" s="9" t="str">
         <f aca="false">IF($J25="","",IF($G25="","טרם נענה",IF($G25&lt;=$J25,"✓","✗")))</f>
         <v/>
       </c>
@@ -5070,7 +5566,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
-      <c r="I26" s="12" t="str">
+      <c r="I26" s="13" t="str">
         <f aca="false">IF(OR($C26="",$H26=""),"",ROUND(($H26-$C26)*24,1))</f>
         <v/>
       </c>
@@ -5078,7 +5574,7 @@
         <f aca="false">IF(OR($C26="",$E26="",$E26="בקשה"),"",WORKDAY.INTL(INT($C26),IF($E26="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K26" s="24" t="str">
+      <c r="K26" s="9" t="str">
         <f aca="false">IF($J26="","",IF($G26="","טרם נענה",IF($G26&lt;=$J26,"✓","✗")))</f>
         <v/>
       </c>
@@ -5093,7 +5589,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
-      <c r="I27" s="12" t="str">
+      <c r="I27" s="13" t="str">
         <f aca="false">IF(OR($C27="",$H27=""),"",ROUND(($H27-$C27)*24,1))</f>
         <v/>
       </c>
@@ -5101,7 +5597,7 @@
         <f aca="false">IF(OR($C27="",$E27="",$E27="בקשה"),"",WORKDAY.INTL(INT($C27),IF($E27="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K27" s="24" t="str">
+      <c r="K27" s="9" t="str">
         <f aca="false">IF($J27="","",IF($G27="","טרם נענה",IF($G27&lt;=$J27,"✓","✗")))</f>
         <v/>
       </c>
@@ -5116,7 +5612,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
-      <c r="I28" s="12" t="str">
+      <c r="I28" s="13" t="str">
         <f aca="false">IF(OR($C28="",$H28=""),"",ROUND(($H28-$C28)*24,1))</f>
         <v/>
       </c>
@@ -5124,7 +5620,7 @@
         <f aca="false">IF(OR($C28="",$E28="",$E28="בקשה"),"",WORKDAY.INTL(INT($C28),IF($E28="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K28" s="24" t="str">
+      <c r="K28" s="9" t="str">
         <f aca="false">IF($J28="","",IF($G28="","טרם נענה",IF($G28&lt;=$J28,"✓","✗")))</f>
         <v/>
       </c>
@@ -5139,7 +5635,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
-      <c r="I29" s="12" t="str">
+      <c r="I29" s="13" t="str">
         <f aca="false">IF(OR($C29="",$H29=""),"",ROUND(($H29-$C29)*24,1))</f>
         <v/>
       </c>
@@ -5147,7 +5643,7 @@
         <f aca="false">IF(OR($C29="",$E29="",$E29="בקשה"),"",WORKDAY.INTL(INT($C29),IF($E29="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K29" s="24" t="str">
+      <c r="K29" s="9" t="str">
         <f aca="false">IF($J29="","",IF($G29="","טרם נענה",IF($G29&lt;=$J29,"✓","✗")))</f>
         <v/>
       </c>
@@ -5162,7 +5658,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
-      <c r="I30" s="12" t="str">
+      <c r="I30" s="13" t="str">
         <f aca="false">IF(OR($C30="",$H30=""),"",ROUND(($H30-$C30)*24,1))</f>
         <v/>
       </c>
@@ -5170,7 +5666,7 @@
         <f aca="false">IF(OR($C30="",$E30="",$E30="בקשה"),"",WORKDAY.INTL(INT($C30),IF($E30="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K30" s="24" t="str">
+      <c r="K30" s="9" t="str">
         <f aca="false">IF($J30="","",IF($G30="","טרם נענה",IF($G30&lt;=$J30,"✓","✗")))</f>
         <v/>
       </c>
@@ -5185,7 +5681,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
-      <c r="I31" s="12" t="str">
+      <c r="I31" s="13" t="str">
         <f aca="false">IF(OR($C31="",$H31=""),"",ROUND(($H31-$C31)*24,1))</f>
         <v/>
       </c>
@@ -5193,7 +5689,7 @@
         <f aca="false">IF(OR($C31="",$E31="",$E31="בקשה"),"",WORKDAY.INTL(INT($C31),IF($E31="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K31" s="24" t="str">
+      <c r="K31" s="9" t="str">
         <f aca="false">IF($J31="","",IF($G31="","טרם נענה",IF($G31&lt;=$J31,"✓","✗")))</f>
         <v/>
       </c>
@@ -5208,7 +5704,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
-      <c r="I32" s="12" t="str">
+      <c r="I32" s="13" t="str">
         <f aca="false">IF(OR($C32="",$H32=""),"",ROUND(($H32-$C32)*24,1))</f>
         <v/>
       </c>
@@ -5216,7 +5712,7 @@
         <f aca="false">IF(OR($C32="",$E32="",$E32="בקשה"),"",WORKDAY.INTL(INT($C32),IF($E32="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K32" s="24" t="str">
+      <c r="K32" s="9" t="str">
         <f aca="false">IF($J32="","",IF($G32="","טרם נענה",IF($G32&lt;=$J32,"✓","✗")))</f>
         <v/>
       </c>
@@ -5231,7 +5727,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
-      <c r="I33" s="12" t="str">
+      <c r="I33" s="13" t="str">
         <f aca="false">IF(OR($C33="",$H33=""),"",ROUND(($H33-$C33)*24,1))</f>
         <v/>
       </c>
@@ -5239,7 +5735,7 @@
         <f aca="false">IF(OR($C33="",$E33="",$E33="בקשה"),"",WORKDAY.INTL(INT($C33),IF($E33="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K33" s="24" t="str">
+      <c r="K33" s="9" t="str">
         <f aca="false">IF($J33="","",IF($G33="","טרם נענה",IF($G33&lt;=$J33,"✓","✗")))</f>
         <v/>
       </c>
@@ -5254,7 +5750,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
-      <c r="I34" s="12" t="str">
+      <c r="I34" s="13" t="str">
         <f aca="false">IF(OR($C34="",$H34=""),"",ROUND(($H34-$C34)*24,1))</f>
         <v/>
       </c>
@@ -5262,7 +5758,7 @@
         <f aca="false">IF(OR($C34="",$E34="",$E34="בקשה"),"",WORKDAY.INTL(INT($C34),IF($E34="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K34" s="24" t="str">
+      <c r="K34" s="9" t="str">
         <f aca="false">IF($J34="","",IF($G34="","טרם נענה",IF($G34&lt;=$J34,"✓","✗")))</f>
         <v/>
       </c>
@@ -5277,7 +5773,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
-      <c r="I35" s="12" t="str">
+      <c r="I35" s="13" t="str">
         <f aca="false">IF(OR($C35="",$H35=""),"",ROUND(($H35-$C35)*24,1))</f>
         <v/>
       </c>
@@ -5285,7 +5781,7 @@
         <f aca="false">IF(OR($C35="",$E35="",$E35="בקשה"),"",WORKDAY.INTL(INT($C35),IF($E35="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K35" s="24" t="str">
+      <c r="K35" s="9" t="str">
         <f aca="false">IF($J35="","",IF($G35="","טרם נענה",IF($G35&lt;=$J35,"✓","✗")))</f>
         <v/>
       </c>
@@ -5300,7 +5796,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
-      <c r="I36" s="12" t="str">
+      <c r="I36" s="13" t="str">
         <f aca="false">IF(OR($C36="",$H36=""),"",ROUND(($H36-$C36)*24,1))</f>
         <v/>
       </c>
@@ -5308,7 +5804,7 @@
         <f aca="false">IF(OR($C36="",$E36="",$E36="בקשה"),"",WORKDAY.INTL(INT($C36),IF($E36="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K36" s="24" t="str">
+      <c r="K36" s="9" t="str">
         <f aca="false">IF($J36="","",IF($G36="","טרם נענה",IF($G36&lt;=$J36,"✓","✗")))</f>
         <v/>
       </c>
@@ -5323,7 +5819,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
-      <c r="I37" s="12" t="str">
+      <c r="I37" s="13" t="str">
         <f aca="false">IF(OR($C37="",$H37=""),"",ROUND(($H37-$C37)*24,1))</f>
         <v/>
       </c>
@@ -5331,7 +5827,7 @@
         <f aca="false">IF(OR($C37="",$E37="",$E37="בקשה"),"",WORKDAY.INTL(INT($C37),IF($E37="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K37" s="24" t="str">
+      <c r="K37" s="9" t="str">
         <f aca="false">IF($J37="","",IF($G37="","טרם נענה",IF($G37&lt;=$J37,"✓","✗")))</f>
         <v/>
       </c>
@@ -5346,7 +5842,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
-      <c r="I38" s="12" t="str">
+      <c r="I38" s="13" t="str">
         <f aca="false">IF(OR($C38="",$H38=""),"",ROUND(($H38-$C38)*24,1))</f>
         <v/>
       </c>
@@ -5354,7 +5850,7 @@
         <f aca="false">IF(OR($C38="",$E38="",$E38="בקשה"),"",WORKDAY.INTL(INT($C38),IF($E38="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K38" s="24" t="str">
+      <c r="K38" s="9" t="str">
         <f aca="false">IF($J38="","",IF($G38="","טרם נענה",IF($G38&lt;=$J38,"✓","✗")))</f>
         <v/>
       </c>
@@ -5369,7 +5865,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
-      <c r="I39" s="12" t="str">
+      <c r="I39" s="13" t="str">
         <f aca="false">IF(OR($C39="",$H39=""),"",ROUND(($H39-$C39)*24,1))</f>
         <v/>
       </c>
@@ -5377,7 +5873,7 @@
         <f aca="false">IF(OR($C39="",$E39="",$E39="בקשה"),"",WORKDAY.INTL(INT($C39),IF($E39="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K39" s="24" t="str">
+      <c r="K39" s="9" t="str">
         <f aca="false">IF($J39="","",IF($G39="","טרם נענה",IF($G39&lt;=$J39,"✓","✗")))</f>
         <v/>
       </c>
@@ -5392,7 +5888,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
-      <c r="I40" s="12" t="str">
+      <c r="I40" s="13" t="str">
         <f aca="false">IF(OR($C40="",$H40=""),"",ROUND(($H40-$C40)*24,1))</f>
         <v/>
       </c>
@@ -5400,7 +5896,7 @@
         <f aca="false">IF(OR($C40="",$E40="",$E40="בקשה"),"",WORKDAY.INTL(INT($C40),IF($E40="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K40" s="24" t="str">
+      <c r="K40" s="9" t="str">
         <f aca="false">IF($J40="","",IF($G40="","טרם נענה",IF($G40&lt;=$J40,"✓","✗")))</f>
         <v/>
       </c>
@@ -5415,7 +5911,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="22"/>
       <c r="H41" s="22"/>
-      <c r="I41" s="12" t="str">
+      <c r="I41" s="13" t="str">
         <f aca="false">IF(OR($C41="",$H41=""),"",ROUND(($H41-$C41)*24,1))</f>
         <v/>
       </c>
@@ -5423,7 +5919,7 @@
         <f aca="false">IF(OR($C41="",$E41="",$E41="בקשה"),"",WORKDAY.INTL(INT($C41),IF($E41="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K41" s="24" t="str">
+      <c r="K41" s="9" t="str">
         <f aca="false">IF($J41="","",IF($G41="","טרם נענה",IF($G41&lt;=$J41,"✓","✗")))</f>
         <v/>
       </c>
@@ -5438,7 +5934,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
-      <c r="I42" s="12" t="str">
+      <c r="I42" s="13" t="str">
         <f aca="false">IF(OR($C42="",$H42=""),"",ROUND(($H42-$C42)*24,1))</f>
         <v/>
       </c>
@@ -5446,7 +5942,7 @@
         <f aca="false">IF(OR($C42="",$E42="",$E42="בקשה"),"",WORKDAY.INTL(INT($C42),IF($E42="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K42" s="24" t="str">
+      <c r="K42" s="9" t="str">
         <f aca="false">IF($J42="","",IF($G42="","טרם נענה",IF($G42&lt;=$J42,"✓","✗")))</f>
         <v/>
       </c>
@@ -5461,7 +5957,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="22"/>
       <c r="H43" s="22"/>
-      <c r="I43" s="12" t="str">
+      <c r="I43" s="13" t="str">
         <f aca="false">IF(OR($C43="",$H43=""),"",ROUND(($H43-$C43)*24,1))</f>
         <v/>
       </c>
@@ -5469,7 +5965,7 @@
         <f aca="false">IF(OR($C43="",$E43="",$E43="בקשה"),"",WORKDAY.INTL(INT($C43),IF($E43="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K43" s="24" t="str">
+      <c r="K43" s="9" t="str">
         <f aca="false">IF($J43="","",IF($G43="","טרם נענה",IF($G43&lt;=$J43,"✓","✗")))</f>
         <v/>
       </c>
@@ -5484,7 +5980,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="22"/>
       <c r="H44" s="22"/>
-      <c r="I44" s="12" t="str">
+      <c r="I44" s="13" t="str">
         <f aca="false">IF(OR($C44="",$H44=""),"",ROUND(($H44-$C44)*24,1))</f>
         <v/>
       </c>
@@ -5492,7 +5988,7 @@
         <f aca="false">IF(OR($C44="",$E44="",$E44="בקשה"),"",WORKDAY.INTL(INT($C44),IF($E44="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K44" s="24" t="str">
+      <c r="K44" s="9" t="str">
         <f aca="false">IF($J44="","",IF($G44="","טרם נענה",IF($G44&lt;=$J44,"✓","✗")))</f>
         <v/>
       </c>
@@ -5507,7 +6003,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="22"/>
       <c r="H45" s="22"/>
-      <c r="I45" s="12" t="str">
+      <c r="I45" s="13" t="str">
         <f aca="false">IF(OR($C45="",$H45=""),"",ROUND(($H45-$C45)*24,1))</f>
         <v/>
       </c>
@@ -5515,7 +6011,7 @@
         <f aca="false">IF(OR($C45="",$E45="",$E45="בקשה"),"",WORKDAY.INTL(INT($C45),IF($E45="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K45" s="24" t="str">
+      <c r="K45" s="9" t="str">
         <f aca="false">IF($J45="","",IF($G45="","טרם נענה",IF($G45&lt;=$J45,"✓","✗")))</f>
         <v/>
       </c>
@@ -5530,7 +6026,7 @@
       <c r="F46" s="5"/>
       <c r="G46" s="22"/>
       <c r="H46" s="22"/>
-      <c r="I46" s="12" t="str">
+      <c r="I46" s="13" t="str">
         <f aca="false">IF(OR($C46="",$H46=""),"",ROUND(($H46-$C46)*24,1))</f>
         <v/>
       </c>
@@ -5538,7 +6034,7 @@
         <f aca="false">IF(OR($C46="",$E46="",$E46="בקשה"),"",WORKDAY.INTL(INT($C46),IF($E46="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K46" s="24" t="str">
+      <c r="K46" s="9" t="str">
         <f aca="false">IF($J46="","",IF($G46="","טרם נענה",IF($G46&lt;=$J46,"✓","✗")))</f>
         <v/>
       </c>
@@ -5553,7 +6049,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="22"/>
       <c r="H47" s="22"/>
-      <c r="I47" s="12" t="str">
+      <c r="I47" s="13" t="str">
         <f aca="false">IF(OR($C47="",$H47=""),"",ROUND(($H47-$C47)*24,1))</f>
         <v/>
       </c>
@@ -5561,7 +6057,7 @@
         <f aca="false">IF(OR($C47="",$E47="",$E47="בקשה"),"",WORKDAY.INTL(INT($C47),IF($E47="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K47" s="24" t="str">
+      <c r="K47" s="9" t="str">
         <f aca="false">IF($J47="","",IF($G47="","טרם נענה",IF($G47&lt;=$J47,"✓","✗")))</f>
         <v/>
       </c>
@@ -5576,7 +6072,7 @@
       <c r="F48" s="5"/>
       <c r="G48" s="22"/>
       <c r="H48" s="22"/>
-      <c r="I48" s="12" t="str">
+      <c r="I48" s="13" t="str">
         <f aca="false">IF(OR($C48="",$H48=""),"",ROUND(($H48-$C48)*24,1))</f>
         <v/>
       </c>
@@ -5584,7 +6080,7 @@
         <f aca="false">IF(OR($C48="",$E48="",$E48="בקשה"),"",WORKDAY.INTL(INT($C48),IF($E48="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K48" s="24" t="str">
+      <c r="K48" s="9" t="str">
         <f aca="false">IF($J48="","",IF($G48="","טרם נענה",IF($G48&lt;=$J48,"✓","✗")))</f>
         <v/>
       </c>
@@ -5599,7 +6095,7 @@
       <c r="F49" s="5"/>
       <c r="G49" s="22"/>
       <c r="H49" s="22"/>
-      <c r="I49" s="12" t="str">
+      <c r="I49" s="13" t="str">
         <f aca="false">IF(OR($C49="",$H49=""),"",ROUND(($H49-$C49)*24,1))</f>
         <v/>
       </c>
@@ -5607,7 +6103,7 @@
         <f aca="false">IF(OR($C49="",$E49="",$E49="בקשה"),"",WORKDAY.INTL(INT($C49),IF($E49="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K49" s="24" t="str">
+      <c r="K49" s="9" t="str">
         <f aca="false">IF($J49="","",IF($G49="","טרם נענה",IF($G49&lt;=$J49,"✓","✗")))</f>
         <v/>
       </c>
@@ -5622,7 +6118,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="22"/>
       <c r="H50" s="22"/>
-      <c r="I50" s="12" t="str">
+      <c r="I50" s="13" t="str">
         <f aca="false">IF(OR($C50="",$H50=""),"",ROUND(($H50-$C50)*24,1))</f>
         <v/>
       </c>
@@ -5630,7 +6126,7 @@
         <f aca="false">IF(OR($C50="",$E50="",$E50="בקשה"),"",WORKDAY.INTL(INT($C50),IF($E50="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K50" s="24" t="str">
+      <c r="K50" s="9" t="str">
         <f aca="false">IF($J50="","",IF($G50="","טרם נענה",IF($G50&lt;=$J50,"✓","✗")))</f>
         <v/>
       </c>
@@ -5645,7 +6141,7 @@
       <c r="F51" s="5"/>
       <c r="G51" s="22"/>
       <c r="H51" s="22"/>
-      <c r="I51" s="12" t="str">
+      <c r="I51" s="13" t="str">
         <f aca="false">IF(OR($C51="",$H51=""),"",ROUND(($H51-$C51)*24,1))</f>
         <v/>
       </c>
@@ -5653,7 +6149,7 @@
         <f aca="false">IF(OR($C51="",$E51="",$E51="בקשה"),"",WORKDAY.INTL(INT($C51),IF($E51="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K51" s="24" t="str">
+      <c r="K51" s="9" t="str">
         <f aca="false">IF($J51="","",IF($G51="","טרם נענה",IF($G51&lt;=$J51,"✓","✗")))</f>
         <v/>
       </c>
@@ -5668,7 +6164,7 @@
       <c r="F52" s="5"/>
       <c r="G52" s="22"/>
       <c r="H52" s="22"/>
-      <c r="I52" s="12" t="str">
+      <c r="I52" s="13" t="str">
         <f aca="false">IF(OR($C52="",$H52=""),"",ROUND(($H52-$C52)*24,1))</f>
         <v/>
       </c>
@@ -5676,7 +6172,7 @@
         <f aca="false">IF(OR($C52="",$E52="",$E52="בקשה"),"",WORKDAY.INTL(INT($C52),IF($E52="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K52" s="24" t="str">
+      <c r="K52" s="9" t="str">
         <f aca="false">IF($J52="","",IF($G52="","טרם נענה",IF($G52&lt;=$J52,"✓","✗")))</f>
         <v/>
       </c>
@@ -5691,7 +6187,7 @@
       <c r="F53" s="5"/>
       <c r="G53" s="22"/>
       <c r="H53" s="22"/>
-      <c r="I53" s="12" t="str">
+      <c r="I53" s="13" t="str">
         <f aca="false">IF(OR($C53="",$H53=""),"",ROUND(($H53-$C53)*24,1))</f>
         <v/>
       </c>
@@ -5699,7 +6195,7 @@
         <f aca="false">IF(OR($C53="",$E53="",$E53="בקשה"),"",WORKDAY.INTL(INT($C53),IF($E53="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K53" s="24" t="str">
+      <c r="K53" s="9" t="str">
         <f aca="false">IF($J53="","",IF($G53="","טרם נענה",IF($G53&lt;=$J53,"✓","✗")))</f>
         <v/>
       </c>
@@ -5714,7 +6210,7 @@
       <c r="F54" s="5"/>
       <c r="G54" s="22"/>
       <c r="H54" s="22"/>
-      <c r="I54" s="12" t="str">
+      <c r="I54" s="13" t="str">
         <f aca="false">IF(OR($C54="",$H54=""),"",ROUND(($H54-$C54)*24,1))</f>
         <v/>
       </c>
@@ -5722,7 +6218,7 @@
         <f aca="false">IF(OR($C54="",$E54="",$E54="בקשה"),"",WORKDAY.INTL(INT($C54),IF($E54="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K54" s="24" t="str">
+      <c r="K54" s="9" t="str">
         <f aca="false">IF($J54="","",IF($G54="","טרם נענה",IF($G54&lt;=$J54,"✓","✗")))</f>
         <v/>
       </c>
@@ -5737,7 +6233,7 @@
       <c r="F55" s="5"/>
       <c r="G55" s="22"/>
       <c r="H55" s="22"/>
-      <c r="I55" s="12" t="str">
+      <c r="I55" s="13" t="str">
         <f aca="false">IF(OR($C55="",$H55=""),"",ROUND(($H55-$C55)*24,1))</f>
         <v/>
       </c>
@@ -5745,7 +6241,7 @@
         <f aca="false">IF(OR($C55="",$E55="",$E55="בקשה"),"",WORKDAY.INTL(INT($C55),IF($E55="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K55" s="24" t="str">
+      <c r="K55" s="9" t="str">
         <f aca="false">IF($J55="","",IF($G55="","טרם נענה",IF($G55&lt;=$J55,"✓","✗")))</f>
         <v/>
       </c>
@@ -5760,7 +6256,7 @@
       <c r="F56" s="5"/>
       <c r="G56" s="22"/>
       <c r="H56" s="22"/>
-      <c r="I56" s="12" t="str">
+      <c r="I56" s="13" t="str">
         <f aca="false">IF(OR($C56="",$H56=""),"",ROUND(($H56-$C56)*24,1))</f>
         <v/>
       </c>
@@ -5768,7 +6264,7 @@
         <f aca="false">IF(OR($C56="",$E56="",$E56="בקשה"),"",WORKDAY.INTL(INT($C56),IF($E56="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K56" s="24" t="str">
+      <c r="K56" s="9" t="str">
         <f aca="false">IF($J56="","",IF($G56="","טרם נענה",IF($G56&lt;=$J56,"✓","✗")))</f>
         <v/>
       </c>
@@ -5783,7 +6279,7 @@
       <c r="F57" s="5"/>
       <c r="G57" s="22"/>
       <c r="H57" s="22"/>
-      <c r="I57" s="12" t="str">
+      <c r="I57" s="13" t="str">
         <f aca="false">IF(OR($C57="",$H57=""),"",ROUND(($H57-$C57)*24,1))</f>
         <v/>
       </c>
@@ -5791,7 +6287,7 @@
         <f aca="false">IF(OR($C57="",$E57="",$E57="בקשה"),"",WORKDAY.INTL(INT($C57),IF($E57="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K57" s="24" t="str">
+      <c r="K57" s="9" t="str">
         <f aca="false">IF($J57="","",IF($G57="","טרם נענה",IF($G57&lt;=$J57,"✓","✗")))</f>
         <v/>
       </c>
@@ -5806,7 +6302,7 @@
       <c r="F58" s="5"/>
       <c r="G58" s="22"/>
       <c r="H58" s="22"/>
-      <c r="I58" s="12" t="str">
+      <c r="I58" s="13" t="str">
         <f aca="false">IF(OR($C58="",$H58=""),"",ROUND(($H58-$C58)*24,1))</f>
         <v/>
       </c>
@@ -5814,7 +6310,7 @@
         <f aca="false">IF(OR($C58="",$E58="",$E58="בקשה"),"",WORKDAY.INTL(INT($C58),IF($E58="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K58" s="24" t="str">
+      <c r="K58" s="9" t="str">
         <f aca="false">IF($J58="","",IF($G58="","טרם נענה",IF($G58&lt;=$J58,"✓","✗")))</f>
         <v/>
       </c>
@@ -5829,7 +6325,7 @@
       <c r="F59" s="5"/>
       <c r="G59" s="22"/>
       <c r="H59" s="22"/>
-      <c r="I59" s="12" t="str">
+      <c r="I59" s="13" t="str">
         <f aca="false">IF(OR($C59="",$H59=""),"",ROUND(($H59-$C59)*24,1))</f>
         <v/>
       </c>
@@ -5837,7 +6333,7 @@
         <f aca="false">IF(OR($C59="",$E59="",$E59="בקשה"),"",WORKDAY.INTL(INT($C59),IF($E59="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K59" s="24" t="str">
+      <c r="K59" s="9" t="str">
         <f aca="false">IF($J59="","",IF($G59="","טרם נענה",IF($G59&lt;=$J59,"✓","✗")))</f>
         <v/>
       </c>
@@ -5852,7 +6348,7 @@
       <c r="F60" s="5"/>
       <c r="G60" s="22"/>
       <c r="H60" s="22"/>
-      <c r="I60" s="12" t="str">
+      <c r="I60" s="13" t="str">
         <f aca="false">IF(OR($C60="",$H60=""),"",ROUND(($H60-$C60)*24,1))</f>
         <v/>
       </c>
@@ -5860,7 +6356,7 @@
         <f aca="false">IF(OR($C60="",$E60="",$E60="בקשה"),"",WORKDAY.INTL(INT($C60),IF($E60="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K60" s="24" t="str">
+      <c r="K60" s="9" t="str">
         <f aca="false">IF($J60="","",IF($G60="","טרם נענה",IF($G60&lt;=$J60,"✓","✗")))</f>
         <v/>
       </c>
@@ -5875,7 +6371,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="22"/>
       <c r="H61" s="22"/>
-      <c r="I61" s="12" t="str">
+      <c r="I61" s="13" t="str">
         <f aca="false">IF(OR($C61="",$H61=""),"",ROUND(($H61-$C61)*24,1))</f>
         <v/>
       </c>
@@ -5883,7 +6379,7 @@
         <f aca="false">IF(OR($C61="",$E61="",$E61="בקשה"),"",WORKDAY.INTL(INT($C61),IF($E61="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K61" s="24" t="str">
+      <c r="K61" s="9" t="str">
         <f aca="false">IF($J61="","",IF($G61="","טרם נענה",IF($G61&lt;=$J61,"✓","✗")))</f>
         <v/>
       </c>
@@ -5898,7 +6394,7 @@
       <c r="F62" s="5"/>
       <c r="G62" s="22"/>
       <c r="H62" s="22"/>
-      <c r="I62" s="12" t="str">
+      <c r="I62" s="13" t="str">
         <f aca="false">IF(OR($C62="",$H62=""),"",ROUND(($H62-$C62)*24,1))</f>
         <v/>
       </c>
@@ -5906,7 +6402,7 @@
         <f aca="false">IF(OR($C62="",$E62="",$E62="בקשה"),"",WORKDAY.INTL(INT($C62),IF($E62="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K62" s="24" t="str">
+      <c r="K62" s="9" t="str">
         <f aca="false">IF($J62="","",IF($G62="","טרם נענה",IF($G62&lt;=$J62,"✓","✗")))</f>
         <v/>
       </c>
@@ -5921,7 +6417,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
-      <c r="I63" s="12" t="str">
+      <c r="I63" s="13" t="str">
         <f aca="false">IF(OR($C63="",$H63=""),"",ROUND(($H63-$C63)*24,1))</f>
         <v/>
       </c>
@@ -5929,7 +6425,7 @@
         <f aca="false">IF(OR($C63="",$E63="",$E63="בקשה"),"",WORKDAY.INTL(INT($C63),IF($E63="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K63" s="24" t="str">
+      <c r="K63" s="9" t="str">
         <f aca="false">IF($J63="","",IF($G63="","טרם נענה",IF($G63&lt;=$J63,"✓","✗")))</f>
         <v/>
       </c>
@@ -5944,7 +6440,7 @@
       <c r="F64" s="5"/>
       <c r="G64" s="22"/>
       <c r="H64" s="22"/>
-      <c r="I64" s="12" t="str">
+      <c r="I64" s="13" t="str">
         <f aca="false">IF(OR($C64="",$H64=""),"",ROUND(($H64-$C64)*24,1))</f>
         <v/>
       </c>
@@ -5952,7 +6448,7 @@
         <f aca="false">IF(OR($C64="",$E64="",$E64="בקשה"),"",WORKDAY.INTL(INT($C64),IF($E64="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K64" s="24" t="str">
+      <c r="K64" s="9" t="str">
         <f aca="false">IF($J64="","",IF($G64="","טרם נענה",IF($G64&lt;=$J64,"✓","✗")))</f>
         <v/>
       </c>
@@ -5967,7 +6463,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="22"/>
       <c r="H65" s="22"/>
-      <c r="I65" s="12" t="str">
+      <c r="I65" s="13" t="str">
         <f aca="false">IF(OR($C65="",$H65=""),"",ROUND(($H65-$C65)*24,1))</f>
         <v/>
       </c>
@@ -5975,7 +6471,7 @@
         <f aca="false">IF(OR($C65="",$E65="",$E65="בקשה"),"",WORKDAY.INTL(INT($C65),IF($E65="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K65" s="24" t="str">
+      <c r="K65" s="9" t="str">
         <f aca="false">IF($J65="","",IF($G65="","טרם נענה",IF($G65&lt;=$J65,"✓","✗")))</f>
         <v/>
       </c>
@@ -5990,7 +6486,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="22"/>
       <c r="H66" s="22"/>
-      <c r="I66" s="12" t="str">
+      <c r="I66" s="13" t="str">
         <f aca="false">IF(OR($C66="",$H66=""),"",ROUND(($H66-$C66)*24,1))</f>
         <v/>
       </c>
@@ -5998,7 +6494,7 @@
         <f aca="false">IF(OR($C66="",$E66="",$E66="בקשה"),"",WORKDAY.INTL(INT($C66),IF($E66="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K66" s="24" t="str">
+      <c r="K66" s="9" t="str">
         <f aca="false">IF($J66="","",IF($G66="","טרם נענה",IF($G66&lt;=$J66,"✓","✗")))</f>
         <v/>
       </c>
@@ -6013,7 +6509,7 @@
       <c r="F67" s="5"/>
       <c r="G67" s="22"/>
       <c r="H67" s="22"/>
-      <c r="I67" s="12" t="str">
+      <c r="I67" s="13" t="str">
         <f aca="false">IF(OR($C67="",$H67=""),"",ROUND(($H67-$C67)*24,1))</f>
         <v/>
       </c>
@@ -6021,7 +6517,7 @@
         <f aca="false">IF(OR($C67="",$E67="",$E67="בקשה"),"",WORKDAY.INTL(INT($C67),IF($E67="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K67" s="24" t="str">
+      <c r="K67" s="9" t="str">
         <f aca="false">IF($J67="","",IF($G67="","טרם נענה",IF($G67&lt;=$J67,"✓","✗")))</f>
         <v/>
       </c>
@@ -6036,7 +6532,7 @@
       <c r="F68" s="5"/>
       <c r="G68" s="22"/>
       <c r="H68" s="22"/>
-      <c r="I68" s="12" t="str">
+      <c r="I68" s="13" t="str">
         <f aca="false">IF(OR($C68="",$H68=""),"",ROUND(($H68-$C68)*24,1))</f>
         <v/>
       </c>
@@ -6044,7 +6540,7 @@
         <f aca="false">IF(OR($C68="",$E68="",$E68="בקשה"),"",WORKDAY.INTL(INT($C68),IF($E68="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K68" s="24" t="str">
+      <c r="K68" s="9" t="str">
         <f aca="false">IF($J68="","",IF($G68="","טרם נענה",IF($G68&lt;=$J68,"✓","✗")))</f>
         <v/>
       </c>
@@ -6059,7 +6555,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="22"/>
       <c r="H69" s="22"/>
-      <c r="I69" s="12" t="str">
+      <c r="I69" s="13" t="str">
         <f aca="false">IF(OR($C69="",$H69=""),"",ROUND(($H69-$C69)*24,1))</f>
         <v/>
       </c>
@@ -6067,7 +6563,7 @@
         <f aca="false">IF(OR($C69="",$E69="",$E69="בקשה"),"",WORKDAY.INTL(INT($C69),IF($E69="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K69" s="24" t="str">
+      <c r="K69" s="9" t="str">
         <f aca="false">IF($J69="","",IF($G69="","טרם נענה",IF($G69&lt;=$J69,"✓","✗")))</f>
         <v/>
       </c>
@@ -6082,7 +6578,7 @@
       <c r="F70" s="5"/>
       <c r="G70" s="22"/>
       <c r="H70" s="22"/>
-      <c r="I70" s="12" t="str">
+      <c r="I70" s="13" t="str">
         <f aca="false">IF(OR($C70="",$H70=""),"",ROUND(($H70-$C70)*24,1))</f>
         <v/>
       </c>
@@ -6090,7 +6586,7 @@
         <f aca="false">IF(OR($C70="",$E70="",$E70="בקשה"),"",WORKDAY.INTL(INT($C70),IF($E70="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K70" s="24" t="str">
+      <c r="K70" s="9" t="str">
         <f aca="false">IF($J70="","",IF($G70="","טרם נענה",IF($G70&lt;=$J70,"✓","✗")))</f>
         <v/>
       </c>
@@ -6105,7 +6601,7 @@
       <c r="F71" s="5"/>
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
-      <c r="I71" s="12" t="str">
+      <c r="I71" s="13" t="str">
         <f aca="false">IF(OR($C71="",$H71=""),"",ROUND(($H71-$C71)*24,1))</f>
         <v/>
       </c>
@@ -6113,7 +6609,7 @@
         <f aca="false">IF(OR($C71="",$E71="",$E71="בקשה"),"",WORKDAY.INTL(INT($C71),IF($E71="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K71" s="24" t="str">
+      <c r="K71" s="9" t="str">
         <f aca="false">IF($J71="","",IF($G71="","טרם נענה",IF($G71&lt;=$J71,"✓","✗")))</f>
         <v/>
       </c>
@@ -6128,7 +6624,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="22"/>
       <c r="H72" s="22"/>
-      <c r="I72" s="12" t="str">
+      <c r="I72" s="13" t="str">
         <f aca="false">IF(OR($C72="",$H72=""),"",ROUND(($H72-$C72)*24,1))</f>
         <v/>
       </c>
@@ -6136,7 +6632,7 @@
         <f aca="false">IF(OR($C72="",$E72="",$E72="בקשה"),"",WORKDAY.INTL(INT($C72),IF($E72="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K72" s="24" t="str">
+      <c r="K72" s="9" t="str">
         <f aca="false">IF($J72="","",IF($G72="","טרם נענה",IF($G72&lt;=$J72,"✓","✗")))</f>
         <v/>
       </c>
@@ -6151,7 +6647,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="22"/>
       <c r="H73" s="22"/>
-      <c r="I73" s="12" t="str">
+      <c r="I73" s="13" t="str">
         <f aca="false">IF(OR($C73="",$H73=""),"",ROUND(($H73-$C73)*24,1))</f>
         <v/>
       </c>
@@ -6159,7 +6655,7 @@
         <f aca="false">IF(OR($C73="",$E73="",$E73="בקשה"),"",WORKDAY.INTL(INT($C73),IF($E73="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K73" s="24" t="str">
+      <c r="K73" s="9" t="str">
         <f aca="false">IF($J73="","",IF($G73="","טרם נענה",IF($G73&lt;=$J73,"✓","✗")))</f>
         <v/>
       </c>
@@ -6174,7 +6670,7 @@
       <c r="F74" s="5"/>
       <c r="G74" s="22"/>
       <c r="H74" s="22"/>
-      <c r="I74" s="12" t="str">
+      <c r="I74" s="13" t="str">
         <f aca="false">IF(OR($C74="",$H74=""),"",ROUND(($H74-$C74)*24,1))</f>
         <v/>
       </c>
@@ -6182,7 +6678,7 @@
         <f aca="false">IF(OR($C74="",$E74="",$E74="בקשה"),"",WORKDAY.INTL(INT($C74),IF($E74="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K74" s="24" t="str">
+      <c r="K74" s="9" t="str">
         <f aca="false">IF($J74="","",IF($G74="","טרם נענה",IF($G74&lt;=$J74,"✓","✗")))</f>
         <v/>
       </c>
@@ -6197,7 +6693,7 @@
       <c r="F75" s="5"/>
       <c r="G75" s="22"/>
       <c r="H75" s="22"/>
-      <c r="I75" s="12" t="str">
+      <c r="I75" s="13" t="str">
         <f aca="false">IF(OR($C75="",$H75=""),"",ROUND(($H75-$C75)*24,1))</f>
         <v/>
       </c>
@@ -6205,7 +6701,7 @@
         <f aca="false">IF(OR($C75="",$E75="",$E75="בקשה"),"",WORKDAY.INTL(INT($C75),IF($E75="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K75" s="24" t="str">
+      <c r="K75" s="9" t="str">
         <f aca="false">IF($J75="","",IF($G75="","טרם נענה",IF($G75&lt;=$J75,"✓","✗")))</f>
         <v/>
       </c>
@@ -6220,7 +6716,7 @@
       <c r="F76" s="5"/>
       <c r="G76" s="22"/>
       <c r="H76" s="22"/>
-      <c r="I76" s="12" t="str">
+      <c r="I76" s="13" t="str">
         <f aca="false">IF(OR($C76="",$H76=""),"",ROUND(($H76-$C76)*24,1))</f>
         <v/>
       </c>
@@ -6228,7 +6724,7 @@
         <f aca="false">IF(OR($C76="",$E76="",$E76="בקשה"),"",WORKDAY.INTL(INT($C76),IF($E76="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K76" s="24" t="str">
+      <c r="K76" s="9" t="str">
         <f aca="false">IF($J76="","",IF($G76="","טרם נענה",IF($G76&lt;=$J76,"✓","✗")))</f>
         <v/>
       </c>
@@ -6243,7 +6739,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="22"/>
       <c r="H77" s="22"/>
-      <c r="I77" s="12" t="str">
+      <c r="I77" s="13" t="str">
         <f aca="false">IF(OR($C77="",$H77=""),"",ROUND(($H77-$C77)*24,1))</f>
         <v/>
       </c>
@@ -6251,7 +6747,7 @@
         <f aca="false">IF(OR($C77="",$E77="",$E77="בקשה"),"",WORKDAY.INTL(INT($C77),IF($E77="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K77" s="24" t="str">
+      <c r="K77" s="9" t="str">
         <f aca="false">IF($J77="","",IF($G77="","טרם נענה",IF($G77&lt;=$J77,"✓","✗")))</f>
         <v/>
       </c>
@@ -6266,7 +6762,7 @@
       <c r="F78" s="5"/>
       <c r="G78" s="22"/>
       <c r="H78" s="22"/>
-      <c r="I78" s="12" t="str">
+      <c r="I78" s="13" t="str">
         <f aca="false">IF(OR($C78="",$H78=""),"",ROUND(($H78-$C78)*24,1))</f>
         <v/>
       </c>
@@ -6274,7 +6770,7 @@
         <f aca="false">IF(OR($C78="",$E78="",$E78="בקשה"),"",WORKDAY.INTL(INT($C78),IF($E78="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K78" s="24" t="str">
+      <c r="K78" s="9" t="str">
         <f aca="false">IF($J78="","",IF($G78="","טרם נענה",IF($G78&lt;=$J78,"✓","✗")))</f>
         <v/>
       </c>
@@ -6289,7 +6785,7 @@
       <c r="F79" s="5"/>
       <c r="G79" s="22"/>
       <c r="H79" s="22"/>
-      <c r="I79" s="12" t="str">
+      <c r="I79" s="13" t="str">
         <f aca="false">IF(OR($C79="",$H79=""),"",ROUND(($H79-$C79)*24,1))</f>
         <v/>
       </c>
@@ -6297,7 +6793,7 @@
         <f aca="false">IF(OR($C79="",$E79="",$E79="בקשה"),"",WORKDAY.INTL(INT($C79),IF($E79="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K79" s="24" t="str">
+      <c r="K79" s="9" t="str">
         <f aca="false">IF($J79="","",IF($G79="","טרם נענה",IF($G79&lt;=$J79,"✓","✗")))</f>
         <v/>
       </c>
@@ -6312,7 +6808,7 @@
       <c r="F80" s="5"/>
       <c r="G80" s="22"/>
       <c r="H80" s="22"/>
-      <c r="I80" s="12" t="str">
+      <c r="I80" s="13" t="str">
         <f aca="false">IF(OR($C80="",$H80=""),"",ROUND(($H80-$C80)*24,1))</f>
         <v/>
       </c>
@@ -6320,7 +6816,7 @@
         <f aca="false">IF(OR($C80="",$E80="",$E80="בקשה"),"",WORKDAY.INTL(INT($C80),IF($E80="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K80" s="24" t="str">
+      <c r="K80" s="9" t="str">
         <f aca="false">IF($J80="","",IF($G80="","טרם נענה",IF($G80&lt;=$J80,"✓","✗")))</f>
         <v/>
       </c>
@@ -6335,7 +6831,7 @@
       <c r="F81" s="5"/>
       <c r="G81" s="22"/>
       <c r="H81" s="22"/>
-      <c r="I81" s="12" t="str">
+      <c r="I81" s="13" t="str">
         <f aca="false">IF(OR($C81="",$H81=""),"",ROUND(($H81-$C81)*24,1))</f>
         <v/>
       </c>
@@ -6343,7 +6839,7 @@
         <f aca="false">IF(OR($C81="",$E81="",$E81="בקשה"),"",WORKDAY.INTL(INT($C81),IF($E81="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K81" s="24" t="str">
+      <c r="K81" s="9" t="str">
         <f aca="false">IF($J81="","",IF($G81="","טרם נענה",IF($G81&lt;=$J81,"✓","✗")))</f>
         <v/>
       </c>
@@ -6358,7 +6854,7 @@
       <c r="F82" s="5"/>
       <c r="G82" s="22"/>
       <c r="H82" s="22"/>
-      <c r="I82" s="12" t="str">
+      <c r="I82" s="13" t="str">
         <f aca="false">IF(OR($C82="",$H82=""),"",ROUND(($H82-$C82)*24,1))</f>
         <v/>
       </c>
@@ -6366,7 +6862,7 @@
         <f aca="false">IF(OR($C82="",$E82="",$E82="בקשה"),"",WORKDAY.INTL(INT($C82),IF($E82="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K82" s="24" t="str">
+      <c r="K82" s="9" t="str">
         <f aca="false">IF($J82="","",IF($G82="","טרם נענה",IF($G82&lt;=$J82,"✓","✗")))</f>
         <v/>
       </c>
@@ -6381,7 +6877,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="22"/>
       <c r="H83" s="22"/>
-      <c r="I83" s="12" t="str">
+      <c r="I83" s="13" t="str">
         <f aca="false">IF(OR($C83="",$H83=""),"",ROUND(($H83-$C83)*24,1))</f>
         <v/>
       </c>
@@ -6389,7 +6885,7 @@
         <f aca="false">IF(OR($C83="",$E83="",$E83="בקשה"),"",WORKDAY.INTL(INT($C83),IF($E83="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K83" s="24" t="str">
+      <c r="K83" s="9" t="str">
         <f aca="false">IF($J83="","",IF($G83="","טרם נענה",IF($G83&lt;=$J83,"✓","✗")))</f>
         <v/>
       </c>
@@ -6404,7 +6900,7 @@
       <c r="F84" s="5"/>
       <c r="G84" s="22"/>
       <c r="H84" s="22"/>
-      <c r="I84" s="12" t="str">
+      <c r="I84" s="13" t="str">
         <f aca="false">IF(OR($C84="",$H84=""),"",ROUND(($H84-$C84)*24,1))</f>
         <v/>
       </c>
@@ -6412,7 +6908,7 @@
         <f aca="false">IF(OR($C84="",$E84="",$E84="בקשה"),"",WORKDAY.INTL(INT($C84),IF($E84="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K84" s="24" t="str">
+      <c r="K84" s="9" t="str">
         <f aca="false">IF($J84="","",IF($G84="","טרם נענה",IF($G84&lt;=$J84,"✓","✗")))</f>
         <v/>
       </c>
@@ -6427,7 +6923,7 @@
       <c r="F85" s="5"/>
       <c r="G85" s="22"/>
       <c r="H85" s="22"/>
-      <c r="I85" s="12" t="str">
+      <c r="I85" s="13" t="str">
         <f aca="false">IF(OR($C85="",$H85=""),"",ROUND(($H85-$C85)*24,1))</f>
         <v/>
       </c>
@@ -6435,7 +6931,7 @@
         <f aca="false">IF(OR($C85="",$E85="",$E85="בקשה"),"",WORKDAY.INTL(INT($C85),IF($E85="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K85" s="24" t="str">
+      <c r="K85" s="9" t="str">
         <f aca="false">IF($J85="","",IF($G85="","טרם נענה",IF($G85&lt;=$J85,"✓","✗")))</f>
         <v/>
       </c>
@@ -6450,7 +6946,7 @@
       <c r="F86" s="5"/>
       <c r="G86" s="22"/>
       <c r="H86" s="22"/>
-      <c r="I86" s="12" t="str">
+      <c r="I86" s="13" t="str">
         <f aca="false">IF(OR($C86="",$H86=""),"",ROUND(($H86-$C86)*24,1))</f>
         <v/>
       </c>
@@ -6458,7 +6954,7 @@
         <f aca="false">IF(OR($C86="",$E86="",$E86="בקשה"),"",WORKDAY.INTL(INT($C86),IF($E86="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K86" s="24" t="str">
+      <c r="K86" s="9" t="str">
         <f aca="false">IF($J86="","",IF($G86="","טרם נענה",IF($G86&lt;=$J86,"✓","✗")))</f>
         <v/>
       </c>
@@ -6473,7 +6969,7 @@
       <c r="F87" s="5"/>
       <c r="G87" s="22"/>
       <c r="H87" s="22"/>
-      <c r="I87" s="12" t="str">
+      <c r="I87" s="13" t="str">
         <f aca="false">IF(OR($C87="",$H87=""),"",ROUND(($H87-$C87)*24,1))</f>
         <v/>
       </c>
@@ -6481,7 +6977,7 @@
         <f aca="false">IF(OR($C87="",$E87="",$E87="בקשה"),"",WORKDAY.INTL(INT($C87),IF($E87="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K87" s="24" t="str">
+      <c r="K87" s="9" t="str">
         <f aca="false">IF($J87="","",IF($G87="","טרם נענה",IF($G87&lt;=$J87,"✓","✗")))</f>
         <v/>
       </c>
@@ -6496,7 +6992,7 @@
       <c r="F88" s="5"/>
       <c r="G88" s="22"/>
       <c r="H88" s="22"/>
-      <c r="I88" s="12" t="str">
+      <c r="I88" s="13" t="str">
         <f aca="false">IF(OR($C88="",$H88=""),"",ROUND(($H88-$C88)*24,1))</f>
         <v/>
       </c>
@@ -6504,7 +7000,7 @@
         <f aca="false">IF(OR($C88="",$E88="",$E88="בקשה"),"",WORKDAY.INTL(INT($C88),IF($E88="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K88" s="24" t="str">
+      <c r="K88" s="9" t="str">
         <f aca="false">IF($J88="","",IF($G88="","טרם נענה",IF($G88&lt;=$J88,"✓","✗")))</f>
         <v/>
       </c>
@@ -6519,7 +7015,7 @@
       <c r="F89" s="5"/>
       <c r="G89" s="22"/>
       <c r="H89" s="22"/>
-      <c r="I89" s="12" t="str">
+      <c r="I89" s="13" t="str">
         <f aca="false">IF(OR($C89="",$H89=""),"",ROUND(($H89-$C89)*24,1))</f>
         <v/>
       </c>
@@ -6527,7 +7023,7 @@
         <f aca="false">IF(OR($C89="",$E89="",$E89="בקשה"),"",WORKDAY.INTL(INT($C89),IF($E89="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K89" s="24" t="str">
+      <c r="K89" s="9" t="str">
         <f aca="false">IF($J89="","",IF($G89="","טרם נענה",IF($G89&lt;=$J89,"✓","✗")))</f>
         <v/>
       </c>
@@ -6542,7 +7038,7 @@
       <c r="F90" s="5"/>
       <c r="G90" s="22"/>
       <c r="H90" s="22"/>
-      <c r="I90" s="12" t="str">
+      <c r="I90" s="13" t="str">
         <f aca="false">IF(OR($C90="",$H90=""),"",ROUND(($H90-$C90)*24,1))</f>
         <v/>
       </c>
@@ -6550,7 +7046,7 @@
         <f aca="false">IF(OR($C90="",$E90="",$E90="בקשה"),"",WORKDAY.INTL(INT($C90),IF($E90="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K90" s="24" t="str">
+      <c r="K90" s="9" t="str">
         <f aca="false">IF($J90="","",IF($G90="","טרם נענה",IF($G90&lt;=$J90,"✓","✗")))</f>
         <v/>
       </c>
@@ -6565,7 +7061,7 @@
       <c r="F91" s="5"/>
       <c r="G91" s="22"/>
       <c r="H91" s="22"/>
-      <c r="I91" s="12" t="str">
+      <c r="I91" s="13" t="str">
         <f aca="false">IF(OR($C91="",$H91=""),"",ROUND(($H91-$C91)*24,1))</f>
         <v/>
       </c>
@@ -6573,7 +7069,7 @@
         <f aca="false">IF(OR($C91="",$E91="",$E91="בקשה"),"",WORKDAY.INTL(INT($C91),IF($E91="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K91" s="24" t="str">
+      <c r="K91" s="9" t="str">
         <f aca="false">IF($J91="","",IF($G91="","טרם נענה",IF($G91&lt;=$J91,"✓","✗")))</f>
         <v/>
       </c>
@@ -6588,7 +7084,7 @@
       <c r="F92" s="5"/>
       <c r="G92" s="22"/>
       <c r="H92" s="22"/>
-      <c r="I92" s="12" t="str">
+      <c r="I92" s="13" t="str">
         <f aca="false">IF(OR($C92="",$H92=""),"",ROUND(($H92-$C92)*24,1))</f>
         <v/>
       </c>
@@ -6596,7 +7092,7 @@
         <f aca="false">IF(OR($C92="",$E92="",$E92="בקשה"),"",WORKDAY.INTL(INT($C92),IF($E92="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K92" s="24" t="str">
+      <c r="K92" s="9" t="str">
         <f aca="false">IF($J92="","",IF($G92="","טרם נענה",IF($G92&lt;=$J92,"✓","✗")))</f>
         <v/>
       </c>
@@ -6611,7 +7107,7 @@
       <c r="F93" s="5"/>
       <c r="G93" s="22"/>
       <c r="H93" s="22"/>
-      <c r="I93" s="12" t="str">
+      <c r="I93" s="13" t="str">
         <f aca="false">IF(OR($C93="",$H93=""),"",ROUND(($H93-$C93)*24,1))</f>
         <v/>
       </c>
@@ -6619,7 +7115,7 @@
         <f aca="false">IF(OR($C93="",$E93="",$E93="בקשה"),"",WORKDAY.INTL(INT($C93),IF($E93="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K93" s="24" t="str">
+      <c r="K93" s="9" t="str">
         <f aca="false">IF($J93="","",IF($G93="","טרם נענה",IF($G93&lt;=$J93,"✓","✗")))</f>
         <v/>
       </c>
@@ -6634,7 +7130,7 @@
       <c r="F94" s="5"/>
       <c r="G94" s="22"/>
       <c r="H94" s="22"/>
-      <c r="I94" s="12" t="str">
+      <c r="I94" s="13" t="str">
         <f aca="false">IF(OR($C94="",$H94=""),"",ROUND(($H94-$C94)*24,1))</f>
         <v/>
       </c>
@@ -6642,7 +7138,7 @@
         <f aca="false">IF(OR($C94="",$E94="",$E94="בקשה"),"",WORKDAY.INTL(INT($C94),IF($E94="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K94" s="24" t="str">
+      <c r="K94" s="9" t="str">
         <f aca="false">IF($J94="","",IF($G94="","טרם נענה",IF($G94&lt;=$J94,"✓","✗")))</f>
         <v/>
       </c>
@@ -6657,7 +7153,7 @@
       <c r="F95" s="5"/>
       <c r="G95" s="22"/>
       <c r="H95" s="22"/>
-      <c r="I95" s="12" t="str">
+      <c r="I95" s="13" t="str">
         <f aca="false">IF(OR($C95="",$H95=""),"",ROUND(($H95-$C95)*24,1))</f>
         <v/>
       </c>
@@ -6665,7 +7161,7 @@
         <f aca="false">IF(OR($C95="",$E95="",$E95="בקשה"),"",WORKDAY.INTL(INT($C95),IF($E95="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K95" s="24" t="str">
+      <c r="K95" s="9" t="str">
         <f aca="false">IF($J95="","",IF($G95="","טרם נענה",IF($G95&lt;=$J95,"✓","✗")))</f>
         <v/>
       </c>
@@ -6680,7 +7176,7 @@
       <c r="F96" s="5"/>
       <c r="G96" s="22"/>
       <c r="H96" s="22"/>
-      <c r="I96" s="12" t="str">
+      <c r="I96" s="13" t="str">
         <f aca="false">IF(OR($C96="",$H96=""),"",ROUND(($H96-$C96)*24,1))</f>
         <v/>
       </c>
@@ -6688,7 +7184,7 @@
         <f aca="false">IF(OR($C96="",$E96="",$E96="בקשה"),"",WORKDAY.INTL(INT($C96),IF($E96="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K96" s="24" t="str">
+      <c r="K96" s="9" t="str">
         <f aca="false">IF($J96="","",IF($G96="","טרם נענה",IF($G96&lt;=$J96,"✓","✗")))</f>
         <v/>
       </c>
@@ -6703,7 +7199,7 @@
       <c r="F97" s="5"/>
       <c r="G97" s="22"/>
       <c r="H97" s="22"/>
-      <c r="I97" s="12" t="str">
+      <c r="I97" s="13" t="str">
         <f aca="false">IF(OR($C97="",$H97=""),"",ROUND(($H97-$C97)*24,1))</f>
         <v/>
       </c>
@@ -6711,7 +7207,7 @@
         <f aca="false">IF(OR($C97="",$E97="",$E97="בקשה"),"",WORKDAY.INTL(INT($C97),IF($E97="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K97" s="24" t="str">
+      <c r="K97" s="9" t="str">
         <f aca="false">IF($J97="","",IF($G97="","טרם נענה",IF($G97&lt;=$J97,"✓","✗")))</f>
         <v/>
       </c>
@@ -6726,7 +7222,7 @@
       <c r="F98" s="5"/>
       <c r="G98" s="22"/>
       <c r="H98" s="22"/>
-      <c r="I98" s="12" t="str">
+      <c r="I98" s="13" t="str">
         <f aca="false">IF(OR($C98="",$H98=""),"",ROUND(($H98-$C98)*24,1))</f>
         <v/>
       </c>
@@ -6734,7 +7230,7 @@
         <f aca="false">IF(OR($C98="",$E98="",$E98="בקשה"),"",WORKDAY.INTL(INT($C98),IF($E98="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K98" s="24" t="str">
+      <c r="K98" s="9" t="str">
         <f aca="false">IF($J98="","",IF($G98="","טרם נענה",IF($G98&lt;=$J98,"✓","✗")))</f>
         <v/>
       </c>
@@ -6749,7 +7245,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="22"/>
       <c r="H99" s="22"/>
-      <c r="I99" s="12" t="str">
+      <c r="I99" s="13" t="str">
         <f aca="false">IF(OR($C99="",$H99=""),"",ROUND(($H99-$C99)*24,1))</f>
         <v/>
       </c>
@@ -6757,7 +7253,7 @@
         <f aca="false">IF(OR($C99="",$E99="",$E99="בקשה"),"",WORKDAY.INTL(INT($C99),IF($E99="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K99" s="24" t="str">
+      <c r="K99" s="9" t="str">
         <f aca="false">IF($J99="","",IF($G99="","טרם נענה",IF($G99&lt;=$J99,"✓","✗")))</f>
         <v/>
       </c>
@@ -6772,7 +7268,7 @@
       <c r="F100" s="5"/>
       <c r="G100" s="22"/>
       <c r="H100" s="22"/>
-      <c r="I100" s="12" t="str">
+      <c r="I100" s="13" t="str">
         <f aca="false">IF(OR($C100="",$H100=""),"",ROUND(($H100-$C100)*24,1))</f>
         <v/>
       </c>
@@ -6780,7 +7276,7 @@
         <f aca="false">IF(OR($C100="",$E100="",$E100="בקשה"),"",WORKDAY.INTL(INT($C100),IF($E100="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K100" s="24" t="str">
+      <c r="K100" s="9" t="str">
         <f aca="false">IF($J100="","",IF($G100="","טרם נענה",IF($G100&lt;=$J100,"✓","✗")))</f>
         <v/>
       </c>
@@ -6795,7 +7291,7 @@
       <c r="F101" s="5"/>
       <c r="G101" s="22"/>
       <c r="H101" s="22"/>
-      <c r="I101" s="12" t="str">
+      <c r="I101" s="13" t="str">
         <f aca="false">IF(OR($C101="",$H101=""),"",ROUND(($H101-$C101)*24,1))</f>
         <v/>
       </c>
@@ -6803,7 +7299,7 @@
         <f aca="false">IF(OR($C101="",$E101="",$E101="בקשה"),"",WORKDAY.INTL(INT($C101),IF($E101="קריטי",1,3),7)+1-1/1440)</f>
         <v/>
       </c>
-      <c r="K101" s="24" t="str">
+      <c r="K101" s="9" t="str">
         <f aca="false">IF($J101="","",IF($G101="","טרם נענה",IF($G101&lt;=$J101,"✓","✗")))</f>
         <v/>
       </c>
@@ -6844,88 +7340,95 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="26" t="n">
+      <c r="A2" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="25" t="n">
         <v>5700</v>
       </c>
-      <c r="C2" s="26" t="n">
+      <c r="C2" s="25" t="n">
         <v>160</v>
       </c>
+      <c r="E2" s="26" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="26" t="n">
+      <c r="A3" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="25" t="n">
         <v>8700</v>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="25" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="26" t="n">
+      <c r="A4" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="25" t="n">
         <v>13150</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="25" t="n">
         <v>350</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B9" s="29" t="n">
-        <f aca="false">COUNTIF(לקוחות!$N$2:$N$21,"פעיל")</f>
+        <f aca="false">COUNTIF(לקוחות!$S$2:$S$21,"פעיל")</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B10" s="30" t="n">
-        <f aca="false">SUMIFS(לקוחות!$G$2:$G$21,לקוחות!$N$2:$N$21,"פעיל")</f>
+        <f aca="false">SUMIFS(לקוחות!$G$2:$G$21,לקוחות!$S$2:$S$21,"פעיל")</f>
         <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B11" s="29" t="n">
         <f aca="false">COUNTIF(פניות!$F$2:$F$500,"פתוחה")</f>
@@ -6934,7 +7437,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B12" s="29" t="n">
         <f aca="false">COUNTIFS(פניות!$E$2:$E$500,"קריטי",פניות!$K$2:$K$500,"✗")</f>
@@ -6943,7 +7446,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">SUM(שעות!$D$2:$D$500)-SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
@@ -6952,9 +7455,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14" s="31" t="n">
+        <v>161</v>
+      </c>
+      <c r="B14" s="30" t="n">
+        <f aca="false">SUM(לקוחות!$N$2:$N$21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="31" t="n">
         <f aca="false">SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
         <v>1.5</v>
       </c>
@@ -6967,5 +7479,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
+++ b/customer-tracker/onehome_customer_tracker_SAMPLE.xlsx
@@ -128,7 +128,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="Z1" authorId="0">
+    <comment ref="AA1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -274,7 +274,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="AG1" authorId="0">
+    <comment ref="AH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="165">
   <si>
     <t xml:space="preserve">OneHome — גיליון מעקב לקוחות (קובץ דוגמה)</t>
   </si>
@@ -599,6 +599,9 @@
     <t xml:space="preserve">7. בדיקת ה-SLA מניחה ימי עסקים א׳–ה׳ בלי חגים, והיעד הוא סוף יום העסקים ה-N אחרי פתיחת הפנייה. אם שישי נחשב יום עסקים, לתקן את הנוסחה בעמודה "יעד SLA".</t>
   </si>
   <si>
+    <t xml:space="preserve">8. "הערות רשת" — רושמים רק חריגות ממוסכמת הסיומות (HA ב-50, Shelly ב-60 עד 79 וכו' — ראו plan-site/kb.html), למשל "50 תפוסה, ה-HA ב-51" או "הראוטר לא מאפשר reservation". אם אין חריגה, כותבים "—".</t>
+  </si>
+  <si>
     <t xml:space="preserve">מזהה לקוח</t>
   </si>
   <si>
@@ -662,6 +665,9 @@
     <t xml:space="preserve">MAC של ה-HA</t>
   </si>
   <si>
+    <t xml:space="preserve">הערות רשת (חריגות IP)</t>
+  </si>
+  <si>
     <t xml:space="preserve">גרסת HA</t>
   </si>
   <si>
@@ -737,13 +743,13 @@
     <t xml:space="preserve">AA:BB:CC:DD:EE:FF</t>
   </si>
   <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026.9.3</t>
   </si>
   <si>
     <t xml:space="preserve">לא</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">onehome-c001-backups</t>
@@ -1612,7 +1618,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1715,6 +1721,11 @@
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1744,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:AM21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1751,153 +1762,157 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="34" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="37" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="35" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="38" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AK1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AL1" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AM1" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" s="6" t="n">
         <f aca="false">IF($E2="","",IFERROR(INDEX(חבילות!$B$2:$B$4,MATCH($E2,חבילות!$A$2:$A$4,0)),""))</f>
@@ -1946,70 +1961,73 @@
         <v>46314</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="X2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="Z2" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC2" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="AD2" s="7" t="n">
+      <c r="AE2" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="AE2" s="11" t="n">
-        <f aca="false">IF(OR($A2="",$I2="",$AC2=""),"",$I2-$AC2-N($AD2))</f>
+      <c r="AF2" s="11" t="n">
+        <f aca="false">IF(OR($A2="",$I2="",$AD2=""),"",$I2-$AD2-N($AE2))</f>
         <v>3700</v>
       </c>
-      <c r="AF2" s="12" t="n">
+      <c r="AG2" s="12" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A2,Checklist!$C$1:$G$1,0)),""))</f>
         <v>1</v>
       </c>
-      <c r="AG2" s="13" t="n">
+      <c r="AH2" s="13" t="n">
         <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v>18.5</v>
       </c>
-      <c r="AH2" s="11" t="n">
-        <f aca="false">IF($A2="","",IFERROR($AE2/$AG2,""))</f>
+      <c r="AI2" s="11" t="n">
+        <f aca="false">IF($A2="","",IFERROR($AF2/$AH2,""))</f>
         <v>200</v>
       </c>
-      <c r="AI2" s="13" t="n">
+      <c r="AJ2" s="13" t="n">
         <f aca="false">IF($A2="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A2,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v>1.5</v>
       </c>
-      <c r="AJ2" s="9" t="n">
+      <c r="AK2" s="9" t="n">
         <f aca="false">IF($A2="","",COUNTIFS(פניות!$B$2:$B$500,$A2,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v>1</v>
       </c>
-      <c r="AK2" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="AL2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2062,34 +2080,35 @@
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="7"/>
+      <c r="AC3" s="5"/>
       <c r="AD3" s="7"/>
-      <c r="AE3" s="11" t="str">
-        <f aca="false">IF(OR($A3="",$I3="",$AC3=""),"",$I3-$AC3-N($AD3))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="12" t="str">
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="11" t="str">
+        <f aca="false">IF(OR($A3="",$I3="",$AD3=""),"",$I3-$AD3-N($AE3))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="12" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A3,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG3" s="13" t="str">
+      <c r="AH3" s="13" t="str">
         <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH3" s="11" t="str">
-        <f aca="false">IF($A3="","",IFERROR($AE3/$AG3,""))</f>
-        <v/>
-      </c>
-      <c r="AI3" s="13" t="str">
+      <c r="AI3" s="11" t="str">
+        <f aca="false">IF($A3="","",IFERROR($AF3/$AH3,""))</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="13" t="str">
         <f aca="false">IF($A3="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A3,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ3" s="9" t="str">
+      <c r="AK3" s="9" t="str">
         <f aca="false">IF($A3="","",COUNTIFS(פניות!$B$2:$B$500,$A3,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
@@ -2141,34 +2160,35 @@
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
-      <c r="AC4" s="7"/>
+      <c r="AC4" s="5"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="11" t="str">
-        <f aca="false">IF(OR($A4="",$I4="",$AC4=""),"",$I4-$AC4-N($AD4))</f>
-        <v/>
-      </c>
-      <c r="AF4" s="12" t="str">
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="11" t="str">
+        <f aca="false">IF(OR($A4="",$I4="",$AD4=""),"",$I4-$AD4-N($AE4))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="12" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A4,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG4" s="13" t="str">
+      <c r="AH4" s="13" t="str">
         <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH4" s="11" t="str">
-        <f aca="false">IF($A4="","",IFERROR($AE4/$AG4,""))</f>
-        <v/>
-      </c>
-      <c r="AI4" s="13" t="str">
+      <c r="AI4" s="11" t="str">
+        <f aca="false">IF($A4="","",IFERROR($AF4/$AH4,""))</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="13" t="str">
         <f aca="false">IF($A4="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A4,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ4" s="9" t="str">
+      <c r="AK4" s="9" t="str">
         <f aca="false">IF($A4="","",COUNTIFS(פניות!$B$2:$B$500,$A4,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -2220,34 +2240,35 @@
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
-      <c r="AC5" s="7"/>
+      <c r="AC5" s="5"/>
       <c r="AD5" s="7"/>
-      <c r="AE5" s="11" t="str">
-        <f aca="false">IF(OR($A5="",$I5="",$AC5=""),"",$I5-$AC5-N($AD5))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="12" t="str">
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="11" t="str">
+        <f aca="false">IF(OR($A5="",$I5="",$AD5=""),"",$I5-$AD5-N($AE5))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="12" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A5,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG5" s="13" t="str">
+      <c r="AH5" s="13" t="str">
         <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH5" s="11" t="str">
-        <f aca="false">IF($A5="","",IFERROR($AE5/$AG5,""))</f>
-        <v/>
-      </c>
-      <c r="AI5" s="13" t="str">
+      <c r="AI5" s="11" t="str">
+        <f aca="false">IF($A5="","",IFERROR($AF5/$AH5,""))</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="13" t="str">
         <f aca="false">IF($A5="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A5,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="str">
+      <c r="AK5" s="9" t="str">
         <f aca="false">IF($A5="","",COUNTIFS(פניות!$B$2:$B$500,$A5,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK5" s="5"/>
       <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -2299,34 +2320,35 @@
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
-      <c r="AC6" s="7"/>
+      <c r="AC6" s="5"/>
       <c r="AD6" s="7"/>
-      <c r="AE6" s="11" t="str">
-        <f aca="false">IF(OR($A6="",$I6="",$AC6=""),"",$I6-$AC6-N($AD6))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="12" t="str">
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="11" t="str">
+        <f aca="false">IF(OR($A6="",$I6="",$AD6=""),"",$I6-$AD6-N($AE6))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="12" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A6,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG6" s="13" t="str">
+      <c r="AH6" s="13" t="str">
         <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH6" s="11" t="str">
-        <f aca="false">IF($A6="","",IFERROR($AE6/$AG6,""))</f>
-        <v/>
-      </c>
-      <c r="AI6" s="13" t="str">
+      <c r="AI6" s="11" t="str">
+        <f aca="false">IF($A6="","",IFERROR($AF6/$AH6,""))</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="13" t="str">
         <f aca="false">IF($A6="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A6,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="str">
+      <c r="AK6" s="9" t="str">
         <f aca="false">IF($A6="","",COUNTIFS(פניות!$B$2:$B$500,$A6,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK6" s="5"/>
       <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -2378,34 +2400,35 @@
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
-      <c r="AC7" s="7"/>
+      <c r="AC7" s="5"/>
       <c r="AD7" s="7"/>
-      <c r="AE7" s="11" t="str">
-        <f aca="false">IF(OR($A7="",$I7="",$AC7=""),"",$I7-$AC7-N($AD7))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="12" t="str">
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="11" t="str">
+        <f aca="false">IF(OR($A7="",$I7="",$AD7=""),"",$I7-$AD7-N($AE7))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="12" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A7,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG7" s="13" t="str">
+      <c r="AH7" s="13" t="str">
         <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH7" s="11" t="str">
-        <f aca="false">IF($A7="","",IFERROR($AE7/$AG7,""))</f>
-        <v/>
-      </c>
-      <c r="AI7" s="13" t="str">
+      <c r="AI7" s="11" t="str">
+        <f aca="false">IF($A7="","",IFERROR($AF7/$AH7,""))</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="13" t="str">
         <f aca="false">IF($A7="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A7,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="str">
+      <c r="AK7" s="9" t="str">
         <f aca="false">IF($A7="","",COUNTIFS(פניות!$B$2:$B$500,$A7,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -2457,34 +2480,35 @@
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
-      <c r="AC8" s="7"/>
+      <c r="AC8" s="5"/>
       <c r="AD8" s="7"/>
-      <c r="AE8" s="11" t="str">
-        <f aca="false">IF(OR($A8="",$I8="",$AC8=""),"",$I8-$AC8-N($AD8))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="12" t="str">
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="11" t="str">
+        <f aca="false">IF(OR($A8="",$I8="",$AD8=""),"",$I8-$AD8-N($AE8))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="12" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A8,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG8" s="13" t="str">
+      <c r="AH8" s="13" t="str">
         <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH8" s="11" t="str">
-        <f aca="false">IF($A8="","",IFERROR($AE8/$AG8,""))</f>
-        <v/>
-      </c>
-      <c r="AI8" s="13" t="str">
+      <c r="AI8" s="11" t="str">
+        <f aca="false">IF($A8="","",IFERROR($AF8/$AH8,""))</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="13" t="str">
         <f aca="false">IF($A8="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A8,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="str">
+      <c r="AK8" s="9" t="str">
         <f aca="false">IF($A8="","",COUNTIFS(פניות!$B$2:$B$500,$A8,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK8" s="5"/>
       <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -2536,34 +2560,35 @@
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
-      <c r="AC9" s="7"/>
+      <c r="AC9" s="5"/>
       <c r="AD9" s="7"/>
-      <c r="AE9" s="11" t="str">
-        <f aca="false">IF(OR($A9="",$I9="",$AC9=""),"",$I9-$AC9-N($AD9))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="12" t="str">
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="11" t="str">
+        <f aca="false">IF(OR($A9="",$I9="",$AD9=""),"",$I9-$AD9-N($AE9))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="12" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A9,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG9" s="13" t="str">
+      <c r="AH9" s="13" t="str">
         <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH9" s="11" t="str">
-        <f aca="false">IF($A9="","",IFERROR($AE9/$AG9,""))</f>
-        <v/>
-      </c>
-      <c r="AI9" s="13" t="str">
+      <c r="AI9" s="11" t="str">
+        <f aca="false">IF($A9="","",IFERROR($AF9/$AH9,""))</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="13" t="str">
         <f aca="false">IF($A9="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A9,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="str">
+      <c r="AK9" s="9" t="str">
         <f aca="false">IF($A9="","",COUNTIFS(פניות!$B$2:$B$500,$A9,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK9" s="5"/>
       <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -2615,34 +2640,35 @@
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
       <c r="AB10" s="5"/>
-      <c r="AC10" s="7"/>
+      <c r="AC10" s="5"/>
       <c r="AD10" s="7"/>
-      <c r="AE10" s="11" t="str">
-        <f aca="false">IF(OR($A10="",$I10="",$AC10=""),"",$I10-$AC10-N($AD10))</f>
-        <v/>
-      </c>
-      <c r="AF10" s="12" t="str">
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="11" t="str">
+        <f aca="false">IF(OR($A10="",$I10="",$AD10=""),"",$I10-$AD10-N($AE10))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="12" t="str">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A10,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG10" s="13" t="str">
+      <c r="AH10" s="13" t="str">
         <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH10" s="11" t="str">
-        <f aca="false">IF($A10="","",IFERROR($AE10/$AG10,""))</f>
-        <v/>
-      </c>
-      <c r="AI10" s="13" t="str">
+      <c r="AI10" s="11" t="str">
+        <f aca="false">IF($A10="","",IFERROR($AF10/$AH10,""))</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="13" t="str">
         <f aca="false">IF($A10="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A10,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="str">
+      <c r="AK10" s="9" t="str">
         <f aca="false">IF($A10="","",COUNTIFS(פניות!$B$2:$B$500,$A10,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK10" s="5"/>
       <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -2694,34 +2720,35 @@
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
       <c r="AB11" s="5"/>
-      <c r="AC11" s="7"/>
+      <c r="AC11" s="5"/>
       <c r="AD11" s="7"/>
-      <c r="AE11" s="11" t="str">
-        <f aca="false">IF(OR($A11="",$I11="",$AC11=""),"",$I11-$AC11-N($AD11))</f>
-        <v/>
-      </c>
-      <c r="AF11" s="12" t="str">
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="11" t="str">
+        <f aca="false">IF(OR($A11="",$I11="",$AD11=""),"",$I11-$AD11-N($AE11))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="12" t="str">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A11,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG11" s="13" t="str">
+      <c r="AH11" s="13" t="str">
         <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH11" s="11" t="str">
-        <f aca="false">IF($A11="","",IFERROR($AE11/$AG11,""))</f>
-        <v/>
-      </c>
-      <c r="AI11" s="13" t="str">
+      <c r="AI11" s="11" t="str">
+        <f aca="false">IF($A11="","",IFERROR($AF11/$AH11,""))</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="13" t="str">
         <f aca="false">IF($A11="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A11,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ11" s="9" t="str">
+      <c r="AK11" s="9" t="str">
         <f aca="false">IF($A11="","",COUNTIFS(פניות!$B$2:$B$500,$A11,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK11" s="5"/>
       <c r="AL11" s="5"/>
+      <c r="AM11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -2773,34 +2800,35 @@
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
-      <c r="AC12" s="7"/>
+      <c r="AC12" s="5"/>
       <c r="AD12" s="7"/>
-      <c r="AE12" s="11" t="str">
-        <f aca="false">IF(OR($A12="",$I12="",$AC12=""),"",$I12-$AC12-N($AD12))</f>
-        <v/>
-      </c>
-      <c r="AF12" s="12" t="str">
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="11" t="str">
+        <f aca="false">IF(OR($A12="",$I12="",$AD12=""),"",$I12-$AD12-N($AE12))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="12" t="str">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A12,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG12" s="13" t="str">
+      <c r="AH12" s="13" t="str">
         <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH12" s="11" t="str">
-        <f aca="false">IF($A12="","",IFERROR($AE12/$AG12,""))</f>
-        <v/>
-      </c>
-      <c r="AI12" s="13" t="str">
+      <c r="AI12" s="11" t="str">
+        <f aca="false">IF($A12="","",IFERROR($AF12/$AH12,""))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="13" t="str">
         <f aca="false">IF($A12="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A12,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ12" s="9" t="str">
+      <c r="AK12" s="9" t="str">
         <f aca="false">IF($A12="","",COUNTIFS(פניות!$B$2:$B$500,$A12,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK12" s="5"/>
       <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -2852,34 +2880,35 @@
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
-      <c r="AC13" s="7"/>
+      <c r="AC13" s="5"/>
       <c r="AD13" s="7"/>
-      <c r="AE13" s="11" t="str">
-        <f aca="false">IF(OR($A13="",$I13="",$AC13=""),"",$I13-$AC13-N($AD13))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="12" t="str">
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="11" t="str">
+        <f aca="false">IF(OR($A13="",$I13="",$AD13=""),"",$I13-$AD13-N($AE13))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="12" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A13,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG13" s="13" t="str">
+      <c r="AH13" s="13" t="str">
         <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH13" s="11" t="str">
-        <f aca="false">IF($A13="","",IFERROR($AE13/$AG13,""))</f>
-        <v/>
-      </c>
-      <c r="AI13" s="13" t="str">
+      <c r="AI13" s="11" t="str">
+        <f aca="false">IF($A13="","",IFERROR($AF13/$AH13,""))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="13" t="str">
         <f aca="false">IF($A13="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A13,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ13" s="9" t="str">
+      <c r="AK13" s="9" t="str">
         <f aca="false">IF($A13="","",COUNTIFS(פניות!$B$2:$B$500,$A13,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK13" s="5"/>
       <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -2931,34 +2960,35 @@
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
-      <c r="AC14" s="7"/>
+      <c r="AC14" s="5"/>
       <c r="AD14" s="7"/>
-      <c r="AE14" s="11" t="str">
-        <f aca="false">IF(OR($A14="",$I14="",$AC14=""),"",$I14-$AC14-N($AD14))</f>
-        <v/>
-      </c>
-      <c r="AF14" s="12" t="str">
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="11" t="str">
+        <f aca="false">IF(OR($A14="",$I14="",$AD14=""),"",$I14-$AD14-N($AE14))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="12" t="str">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A14,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG14" s="13" t="str">
+      <c r="AH14" s="13" t="str">
         <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH14" s="11" t="str">
-        <f aca="false">IF($A14="","",IFERROR($AE14/$AG14,""))</f>
-        <v/>
-      </c>
-      <c r="AI14" s="13" t="str">
+      <c r="AI14" s="11" t="str">
+        <f aca="false">IF($A14="","",IFERROR($AF14/$AH14,""))</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="13" t="str">
         <f aca="false">IF($A14="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A14,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ14" s="9" t="str">
+      <c r="AK14" s="9" t="str">
         <f aca="false">IF($A14="","",COUNTIFS(פניות!$B$2:$B$500,$A14,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK14" s="5"/>
       <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -3010,34 +3040,35 @@
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
       <c r="AB15" s="5"/>
-      <c r="AC15" s="7"/>
+      <c r="AC15" s="5"/>
       <c r="AD15" s="7"/>
-      <c r="AE15" s="11" t="str">
-        <f aca="false">IF(OR($A15="",$I15="",$AC15=""),"",$I15-$AC15-N($AD15))</f>
-        <v/>
-      </c>
-      <c r="AF15" s="12" t="str">
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="11" t="str">
+        <f aca="false">IF(OR($A15="",$I15="",$AD15=""),"",$I15-$AD15-N($AE15))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="12" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A15,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG15" s="13" t="str">
+      <c r="AH15" s="13" t="str">
         <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH15" s="11" t="str">
-        <f aca="false">IF($A15="","",IFERROR($AE15/$AG15,""))</f>
-        <v/>
-      </c>
-      <c r="AI15" s="13" t="str">
+      <c r="AI15" s="11" t="str">
+        <f aca="false">IF($A15="","",IFERROR($AF15/$AH15,""))</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="13" t="str">
         <f aca="false">IF($A15="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A15,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ15" s="9" t="str">
+      <c r="AK15" s="9" t="str">
         <f aca="false">IF($A15="","",COUNTIFS(פניות!$B$2:$B$500,$A15,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK15" s="5"/>
       <c r="AL15" s="5"/>
+      <c r="AM15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -3089,34 +3120,35 @@
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
-      <c r="AC16" s="7"/>
+      <c r="AC16" s="5"/>
       <c r="AD16" s="7"/>
-      <c r="AE16" s="11" t="str">
-        <f aca="false">IF(OR($A16="",$I16="",$AC16=""),"",$I16-$AC16-N($AD16))</f>
-        <v/>
-      </c>
-      <c r="AF16" s="12" t="str">
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="11" t="str">
+        <f aca="false">IF(OR($A16="",$I16="",$AD16=""),"",$I16-$AD16-N($AE16))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="12" t="str">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A16,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG16" s="13" t="str">
+      <c r="AH16" s="13" t="str">
         <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH16" s="11" t="str">
-        <f aca="false">IF($A16="","",IFERROR($AE16/$AG16,""))</f>
-        <v/>
-      </c>
-      <c r="AI16" s="13" t="str">
+      <c r="AI16" s="11" t="str">
+        <f aca="false">IF($A16="","",IFERROR($AF16/$AH16,""))</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="13" t="str">
         <f aca="false">IF($A16="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A16,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ16" s="9" t="str">
+      <c r="AK16" s="9" t="str">
         <f aca="false">IF($A16="","",COUNTIFS(פניות!$B$2:$B$500,$A16,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK16" s="5"/>
       <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -3168,34 +3200,35 @@
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
       <c r="AB17" s="5"/>
-      <c r="AC17" s="7"/>
+      <c r="AC17" s="5"/>
       <c r="AD17" s="7"/>
-      <c r="AE17" s="11" t="str">
-        <f aca="false">IF(OR($A17="",$I17="",$AC17=""),"",$I17-$AC17-N($AD17))</f>
-        <v/>
-      </c>
-      <c r="AF17" s="12" t="str">
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="11" t="str">
+        <f aca="false">IF(OR($A17="",$I17="",$AD17=""),"",$I17-$AD17-N($AE17))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="12" t="str">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A17,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG17" s="13" t="str">
+      <c r="AH17" s="13" t="str">
         <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH17" s="11" t="str">
-        <f aca="false">IF($A17="","",IFERROR($AE17/$AG17,""))</f>
-        <v/>
-      </c>
-      <c r="AI17" s="13" t="str">
+      <c r="AI17" s="11" t="str">
+        <f aca="false">IF($A17="","",IFERROR($AF17/$AH17,""))</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="13" t="str">
         <f aca="false">IF($A17="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A17,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ17" s="9" t="str">
+      <c r="AK17" s="9" t="str">
         <f aca="false">IF($A17="","",COUNTIFS(פניות!$B$2:$B$500,$A17,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK17" s="5"/>
       <c r="AL17" s="5"/>
+      <c r="AM17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -3247,34 +3280,35 @@
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5"/>
-      <c r="AC18" s="7"/>
+      <c r="AC18" s="5"/>
       <c r="AD18" s="7"/>
-      <c r="AE18" s="11" t="str">
-        <f aca="false">IF(OR($A18="",$I18="",$AC18=""),"",$I18-$AC18-N($AD18))</f>
-        <v/>
-      </c>
-      <c r="AF18" s="12" t="str">
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="11" t="str">
+        <f aca="false">IF(OR($A18="",$I18="",$AD18=""),"",$I18-$AD18-N($AE18))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="12" t="str">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A18,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG18" s="13" t="str">
+      <c r="AH18" s="13" t="str">
         <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH18" s="11" t="str">
-        <f aca="false">IF($A18="","",IFERROR($AE18/$AG18,""))</f>
-        <v/>
-      </c>
-      <c r="AI18" s="13" t="str">
+      <c r="AI18" s="11" t="str">
+        <f aca="false">IF($A18="","",IFERROR($AF18/$AH18,""))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="13" t="str">
         <f aca="false">IF($A18="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A18,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ18" s="9" t="str">
+      <c r="AK18" s="9" t="str">
         <f aca="false">IF($A18="","",COUNTIFS(פניות!$B$2:$B$500,$A18,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK18" s="5"/>
       <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -3326,34 +3360,35 @@
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
-      <c r="AC19" s="7"/>
+      <c r="AC19" s="5"/>
       <c r="AD19" s="7"/>
-      <c r="AE19" s="11" t="str">
-        <f aca="false">IF(OR($A19="",$I19="",$AC19=""),"",$I19-$AC19-N($AD19))</f>
-        <v/>
-      </c>
-      <c r="AF19" s="12" t="str">
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="11" t="str">
+        <f aca="false">IF(OR($A19="",$I19="",$AD19=""),"",$I19-$AD19-N($AE19))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="12" t="str">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A19,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG19" s="13" t="str">
+      <c r="AH19" s="13" t="str">
         <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH19" s="11" t="str">
-        <f aca="false">IF($A19="","",IFERROR($AE19/$AG19,""))</f>
-        <v/>
-      </c>
-      <c r="AI19" s="13" t="str">
+      <c r="AI19" s="11" t="str">
+        <f aca="false">IF($A19="","",IFERROR($AF19/$AH19,""))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="13" t="str">
         <f aca="false">IF($A19="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A19,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ19" s="9" t="str">
+      <c r="AK19" s="9" t="str">
         <f aca="false">IF($A19="","",COUNTIFS(פניות!$B$2:$B$500,$A19,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK19" s="5"/>
       <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -3405,34 +3440,35 @@
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
       <c r="AB20" s="5"/>
-      <c r="AC20" s="7"/>
+      <c r="AC20" s="5"/>
       <c r="AD20" s="7"/>
-      <c r="AE20" s="11" t="str">
-        <f aca="false">IF(OR($A20="",$I20="",$AC20=""),"",$I20-$AC20-N($AD20))</f>
-        <v/>
-      </c>
-      <c r="AF20" s="12" t="str">
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="11" t="str">
+        <f aca="false">IF(OR($A20="",$I20="",$AD20=""),"",$I20-$AD20-N($AE20))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="12" t="str">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A20,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG20" s="13" t="str">
+      <c r="AH20" s="13" t="str">
         <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH20" s="11" t="str">
-        <f aca="false">IF($A20="","",IFERROR($AE20/$AG20,""))</f>
-        <v/>
-      </c>
-      <c r="AI20" s="13" t="str">
+      <c r="AI20" s="11" t="str">
+        <f aca="false">IF($A20="","",IFERROR($AF20/$AH20,""))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="13" t="str">
         <f aca="false">IF($A20="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A20,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ20" s="9" t="str">
+      <c r="AK20" s="9" t="str">
         <f aca="false">IF($A20="","",COUNTIFS(פניות!$B$2:$B$500,$A20,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK20" s="5"/>
       <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -3484,34 +3520,35 @@
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
       <c r="AB21" s="5"/>
-      <c r="AC21" s="7"/>
+      <c r="AC21" s="5"/>
       <c r="AD21" s="7"/>
-      <c r="AE21" s="11" t="str">
-        <f aca="false">IF(OR($A21="",$I21="",$AC21=""),"",$I21-$AC21-N($AD21))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="12" t="str">
+      <c r="AE21" s="7"/>
+      <c r="AF21" s="11" t="str">
+        <f aca="false">IF(OR($A21="",$I21="",$AD21=""),"",$I21-$AD21-N($AE21))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="12" t="str">
         <f aca="false">IF($A21="","",IFERROR(INDEX(Checklist!$C$30:$G$30,MATCH($A21,Checklist!$C$1:$G$1,0)),""))</f>
         <v/>
       </c>
-      <c r="AG21" s="13" t="str">
+      <c r="AH21" s="13" t="str">
         <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21)-SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AH21" s="11" t="str">
-        <f aca="false">IF($A21="","",IFERROR($AE21/$AG21,""))</f>
-        <v/>
-      </c>
-      <c r="AI21" s="13" t="str">
+      <c r="AI21" s="11" t="str">
+        <f aca="false">IF($A21="","",IFERROR($AF21/$AH21,""))</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="13" t="str">
         <f aca="false">IF($A21="","",SUMIFS(שעות!$D$2:$D$500,שעות!$A$2:$A$500,$A21,שעות!$B$2:$B$500,"תמיכה (ריטיינר)"))</f>
         <v/>
       </c>
-      <c r="AJ21" s="9" t="str">
+      <c r="AK21" s="9" t="str">
         <f aca="false">IF($A21="","",COUNTIFS(פניות!$B$2:$B$500,$A21,פניות!$F$2:$F$500,"פתוחה"))</f>
         <v/>
       </c>
-      <c r="AK21" s="5"/>
       <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -3523,11 +3560,11 @@
       <formula1>"ליד,סקר בית,הצעה נשלחה,הזמנת ציוד,התקנה,בדיקות קבלה,פעיל,מושהה,הופסק"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="W2:W21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="X2:X21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AA2:AA21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AB2:AB21" type="list">
       <formula1>"כן,לא"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3558,10 +3595,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="4" t="str">
         <f aca="false">IF(לקוחות!$A2="","",לקוחות!$A2)</f>
@@ -3586,13 +3623,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -3601,13 +3638,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -3616,13 +3653,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>77</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -3631,13 +3668,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -3646,13 +3683,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
@@ -3661,13 +3698,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -3676,13 +3713,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -3691,13 +3728,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -3706,13 +3743,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -3721,13 +3758,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -3736,13 +3773,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
@@ -3751,13 +3788,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -3766,13 +3803,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
@@ -3781,13 +3818,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
@@ -3796,13 +3833,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
@@ -3811,13 +3848,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
@@ -3826,13 +3863,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -3841,13 +3878,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
@@ -3856,13 +3893,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
@@ -3871,13 +3908,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
@@ -3886,13 +3923,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
@@ -3901,13 +3938,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
@@ -3916,13 +3953,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
@@ -3931,13 +3968,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
@@ -3946,13 +3983,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
@@ -3961,13 +3998,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -3976,13 +4013,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -3991,13 +4028,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
@@ -4007,7 +4044,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17"/>
       <c r="B30" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">IF(C$1="","",COUNTIF(C2:C29,"✓")/MAX(1,ROWS(C2:C29)-COUNTIF(C2:C29,"לא רלוונטי")))</f>
@@ -4075,30 +4112,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C2" s="8" t="n">
         <v>46293</v>
@@ -4107,15 +4144,15 @@
         <v>1.5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>46293</v>
@@ -4127,10 +4164,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>46300</v>
@@ -4142,10 +4179,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>46300</v>
@@ -4157,10 +4194,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>46303</v>
@@ -4169,15 +4206,15 @@
         <v>1.5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>46309</v>
@@ -4186,15 +4223,15 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>46314</v>
@@ -4206,10 +4243,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>46314</v>
@@ -4221,10 +4258,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>46314</v>
@@ -4236,10 +4273,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>46314</v>
@@ -4251,10 +4288,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>46316</v>
@@ -4263,15 +4300,15 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>46328</v>
@@ -4280,7 +4317,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4937,60 +4974,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" s="22" t="n">
         <v>46316.3819444445</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G2" s="22" t="n">
         <v>46316.4027777778</v>
@@ -5011,27 +5048,27 @@
         <v>✓</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" s="22" t="n">
         <v>46328.75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
@@ -5048,7 +5085,7 @@
         <v/>
       </c>
       <c r="L3" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7350,21 +7387,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B2" s="25" t="n">
         <v>5700</v>
@@ -7378,7 +7415,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" s="25" t="n">
         <v>8700</v>
@@ -7389,7 +7426,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" s="25" t="n">
         <v>13150</v>
@@ -7400,17 +7437,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTIF(לקוחות!$S$2:$S$21,"פעיל")</f>
@@ -7419,7 +7456,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="30" t="n">
         <f aca="false">SUMIFS(לקוחות!$G$2:$G$21,לקוחות!$S$2:$S$21,"פעיל")</f>
@@ -7428,7 +7465,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B11" s="29" t="n">
         <f aca="false">COUNTIF(פניות!$F$2:$F$500,"פתוחה")</f>
@@ -7437,7 +7474,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B12" s="29" t="n">
         <f aca="false">COUNTIFS(פניות!$E$2:$E$500,"קריטי",פניות!$K$2:$K$500,"✗")</f>
@@ -7446,7 +7483,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">SUM(שעות!$D$2:$D$500)-SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
@@ -7455,7 +7492,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">SUM(לקוחות!$N$2:$N$21)</f>
@@ -7464,7 +7501,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B15" s="31" t="n">
         <f aca="false">SUMIFS(שעות!$D$2:$D$500,שעות!$B$2:$B$500,"תמיכה (ריטיינר)")</f>
